--- a/resources/Formato_Dinamico_.xlsx
+++ b/resources/Formato_Dinamico_.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santiago/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santiago/Desktop/creacion activo SAP py/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0831BF54-0CE7-434F-9C7E-DB770D5C8B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C90E71-D4EA-874E-B665-80C62C1D563F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" firstSheet="4" activeTab="9" xr2:uid="{CA7242B3-F58B-4D52-905C-F122405A1A29}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="7" xr2:uid="{CA7242B3-F58B-4D52-905C-F122405A1A29}"/>
   </bookViews>
   <sheets>
     <sheet name="Sociedades" sheetId="7" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Criterio " sheetId="2" r:id="rId3"/>
     <sheet name="Ceco" sheetId="3" r:id="rId4"/>
     <sheet name="Emplazamiento" sheetId="4" r:id="rId5"/>
-    <sheet name="_ListasClase" sheetId="8" state="hidden" r:id="rId6"/>
+    <sheet name="_ListasClase" sheetId="8" r:id="rId6"/>
     <sheet name="_Requeridos" sheetId="9" r:id="rId7"/>
     <sheet name="Check list" sheetId="11" r:id="rId8"/>
     <sheet name="Formato" sheetId="5" r:id="rId9"/>
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7880" uniqueCount="1532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7844" uniqueCount="1533">
   <si>
     <t xml:space="preserve">Sociedad </t>
   </si>
@@ -4653,28 +4653,10 @@
     <t>NO</t>
   </si>
   <si>
-    <t>PAÍS</t>
-  </si>
-  <si>
     <t>Preguntas</t>
   </si>
   <si>
     <t>Respuesta</t>
-  </si>
-  <si>
-    <t>¿El activo supera el valor de 1/4 de UIT (Unidad Impositiva Tributaria)?</t>
-  </si>
-  <si>
-    <t>¿Pertenece a un proyecto?</t>
-  </si>
-  <si>
-    <t>¿El equipo va a ser reemplazado en alguna concesión?</t>
-  </si>
-  <si>
-    <t>¿Se compra a través de una orden estadística según tipo de activo (diversos, inmuebles)?</t>
-  </si>
-  <si>
-    <t>¿El activo no está sincronizado AA-PM por la fecha de montaje y esta se reporta al Ministerio/Osinerming?</t>
   </si>
   <si>
     <r>
@@ -4762,9 +4744,6 @@
     <t>Países</t>
   </si>
   <si>
-    <t>¿Es de interés para la organización, de tal forma que esté dispuesta a realizarle seguimiento y control como propiedad, planta y equipo?</t>
-  </si>
-  <si>
     <t>CONFIGURACIÓN PREGUNTAS CHECKLIST POR PAÍS</t>
   </si>
   <si>
@@ -4810,25 +4789,49 @@
     <t>P11</t>
   </si>
   <si>
-    <t>¿El activo es un recurso tangible controlado por la compañía?</t>
-  </si>
-  <si>
-    <t>¿Se espera que el activo sea utilizado en el giro normal del negocio por más de un año?</t>
-  </si>
-  <si>
-    <t>¿Es probable que el activo genere beneficios económicos o apoye funciones administrativas?</t>
-  </si>
-  <si>
-    <t>¿Su valor puede ser medido de forma confiable y razonable?</t>
-  </si>
-  <si>
-    <t>¿El valor del activo supera 2.5 Salarios Mínimos Mensuales Legales Vigentes (SMMLV)?</t>
-  </si>
-  <si>
     <t>¿PUEDE SER CREADO COMO ACTIVO FIJO?</t>
   </si>
   <si>
     <t>UN</t>
+  </si>
+  <si>
+    <t>FILIAL</t>
+  </si>
+  <si>
+    <t>1. ¿El activo es un recurso tangible controlado por la compañía?</t>
+  </si>
+  <si>
+    <t>2. ¿Se espera que el activo sea utilizado en el giro normal del negocio por más de un año?</t>
+  </si>
+  <si>
+    <t>3. ¿Es probable que el activo genere beneficios económicos o apoye funciones administrativas?</t>
+  </si>
+  <si>
+    <t>4. ¿Su valor puede ser medido de forma confiable y razonable?</t>
+  </si>
+  <si>
+    <t>5. ¿El valor del activo supera 2.5 Salarios Mínimos Mensuales Legales Vigentes (SMMLV)?</t>
+  </si>
+  <si>
+    <t>6. ¿Es de interés para la organización, de tal forma que esté dispuesta a realizarle seguimiento y control como propiedad, planta y equipo?</t>
+  </si>
+  <si>
+    <t>7. ¿El activo supera el valor de 1/4 de UIT (Unidad Impositiva Tributaria)?</t>
+  </si>
+  <si>
+    <t>8. ¿El equipo va a ser reemplazado en alguna concesión?</t>
+  </si>
+  <si>
+    <t>9. ¿Pertenece a un proyecto?</t>
+  </si>
+  <si>
+    <t>10. ¿Se compra a través de una orden estadística según tipo de activo (diversos, inmuebles)?</t>
+  </si>
+  <si>
+    <t>11. ¿El activo no está sincronizado AA-PM por la fecha de montaje y esta se reporta al Ministerio/Osinerming?</t>
+  </si>
+  <si>
+    <t>EXCLUSIVO PARA FILIALES DE PERÚ</t>
   </si>
 </sst>
 </file>
@@ -5638,6 +5641,21 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -5670,28 +5688,39 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 4" xfId="1" xr:uid="{3283983A-646C-44C7-A2FC-29FE31B28852}"/>
     <cellStyle name="Porcentaje 2" xfId="2" xr:uid="{57290B1F-A1BC-40FC-80FE-1CB63CCFCBB6}"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF006400"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -5889,13 +5918,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>655875</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>91838</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6671,7 +6700,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>1531</v>
+        <v>1519</v>
       </c>
       <c r="Q2">
         <f>Formato!N22</f>
@@ -16894,7 +16923,7 @@
         <v>941</v>
       </c>
       <c r="J192" t="s">
-        <v>1506</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.2">
@@ -42087,7 +42116,7 @@
         <v>1380</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>1508</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -45046,7 +45075,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:Z38"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="102.1640625" bestFit="1" customWidth="1"/>
@@ -45417,55 +45446,55 @@
     </row>
     <row r="16" spans="1:26" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="77" t="s">
-        <v>1510</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="78" t="s">
-        <v>1511</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="78" t="s">
-        <v>1512</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>1511</v>
+      </c>
+      <c r="G20" s="18" t="s">
+        <v>1512</v>
+      </c>
+      <c r="H20" s="18" t="s">
         <v>1513</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="I20" s="18" t="s">
         <v>1514</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="J20" s="18" t="s">
         <v>1515</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="K20" s="18" t="s">
         <v>1516</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="L20" s="18" t="s">
         <v>1517</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>1518</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>1519</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>1520</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>1521</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>1522</v>
-      </c>
-      <c r="K20" s="18" t="s">
-        <v>1523</v>
-      </c>
-      <c r="L20" s="18" t="s">
-        <v>1524</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
@@ -45547,174 +45576,6 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>1497</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1441</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1446</v>
-      </c>
-      <c r="D27" t="s">
-        <v>1442</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>1525</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1489</v>
-      </c>
-      <c r="C28" t="s">
-        <v>1495</v>
-      </c>
-      <c r="D28" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>1526</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1489</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1495</v>
-      </c>
-      <c r="D29" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>1527</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1489</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1495</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>1528</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1489</v>
-      </c>
-      <c r="C31" t="s">
-        <v>1495</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>1529</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1489</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1495</v>
-      </c>
-      <c r="D32" t="s">
-        <v>1495</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>1509</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1489</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1495</v>
-      </c>
-      <c r="D33" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>1499</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1495</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1489</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1495</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>1501</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1495</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1489</v>
-      </c>
-      <c r="D35" t="s">
-        <v>1495</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>1500</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1495</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1489</v>
-      </c>
-      <c r="D36" t="s">
-        <v>1495</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>1502</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1495</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1489</v>
-      </c>
-      <c r="D37" t="s">
-        <v>1495</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>1503</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1495</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1489</v>
-      </c>
-      <c r="D38" t="s">
-        <v>1495</v>
-      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -45734,7 +45595,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor theme="3" tint="0.249977111117893"/>
   </sheetPr>
-  <dimension ref="B4:L42"/>
+  <dimension ref="B4:L37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.1640625" customWidth="1"/>
@@ -45745,10 +45606,10 @@
   <sheetData>
     <row r="4" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F5" s="88" t="s">
+      <c r="F5" s="80" t="s">
         <v>1490</v>
       </c>
-      <c r="G5" s="89"/>
+      <c r="G5" s="81"/>
     </row>
     <row r="6" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="F6" s="53"/>
@@ -45759,10 +45620,10 @@
       <c r="G7" s="54"/>
     </row>
     <row r="8" spans="2:12" ht="23" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="90" t="s">
+      <c r="B8" s="82" t="s">
         <v>1491</v>
       </c>
-      <c r="C8" s="91"/>
+      <c r="C8" s="83"/>
       <c r="F8" s="25" t="s">
         <v>1492</v>
       </c>
@@ -45787,18 +45648,18 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="92" t="s">
-        <v>1505</v>
-      </c>
-      <c r="C11" s="92"/>
+      <c r="B11" s="84" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C11" s="84"/>
       <c r="F11" s="29"/>
       <c r="G11" s="30"/>
     </row>
     <row r="12" spans="2:12" ht="19" x14ac:dyDescent="0.2">
-      <c r="B12" s="92" t="s">
-        <v>1504</v>
-      </c>
-      <c r="C12" s="92"/>
+      <c r="B12" s="84" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C12" s="84"/>
       <c r="L12" s="31" t="s">
         <v>1489</v>
       </c>
@@ -45810,10 +45671,10 @@
     </row>
     <row r="14" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="49" t="s">
-        <v>1496</v>
+        <v>1520</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>1441</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -45821,17 +45682,16 @@
     </row>
     <row r="17" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="51" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C17" s="51" t="s">
         <v>1497</v>
       </c>
-      <c r="C17" s="51" t="s">
-        <v>1498</v>
-      </c>
       <c r="L17" s="33"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B18" t="str">
-        <f>IF(IFERROR(_xlfn.XLOOKUP('Check list'!$C$14,_Requeridos!$B$27:$D$27,_Requeridos!$B28:$D28,""),"")="SI",_Requeridos!$A28,"")</f>
-        <v>¿El activo es un recurso tangible controlado por la compañía?</v>
+      <c r="B18" t="s">
+        <v>1521</v>
       </c>
       <c r="C18" t="s">
         <v>1489</v>
@@ -45839,9 +45699,8 @@
       <c r="L18" s="33"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B19" t="str">
-        <f>IF(IFERROR(_xlfn.XLOOKUP('Check list'!$C$14,_Requeridos!$B$27:$D$27,_Requeridos!$B29:$D29,""),"")="SI",_Requeridos!$A29,"")</f>
-        <v>¿Se espera que el activo sea utilizado en el giro normal del negocio por más de un año?</v>
+      <c r="B19" t="s">
+        <v>1522</v>
       </c>
       <c r="C19" t="s">
         <v>1489</v>
@@ -45849,9 +45708,8 @@
       <c r="L19" s="33"/>
     </row>
     <row r="20" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" t="str">
-        <f>IF(IFERROR(_xlfn.XLOOKUP('Check list'!$C$14,_Requeridos!$B$27:$D$27,_Requeridos!$B30:$D30,""),"")="SI",_Requeridos!$A30,"")</f>
-        <v>¿Es probable que el activo genere beneficios económicos o apoye funciones administrativas?</v>
+      <c r="B20" t="s">
+        <v>1523</v>
       </c>
       <c r="C20" t="s">
         <v>1489</v>
@@ -45859,116 +45717,124 @@
       <c r="L20" s="32"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B21" t="str">
-        <f>IF(IFERROR(_xlfn.XLOOKUP('Check list'!$C$14,_Requeridos!$B$27:$D$27,_Requeridos!$B31:$D31,""),"")="SI",_Requeridos!$A31,"")</f>
-        <v>¿Su valor puede ser medido de forma confiable y razonable?</v>
+      <c r="B21" t="s">
+        <v>1524</v>
       </c>
       <c r="C21" t="s">
         <v>1489</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B22" t="str">
-        <f>IF(IFERROR(_xlfn.XLOOKUP('Check list'!$C$14,_Requeridos!$B$27:$D$27,_Requeridos!$B32:$D32,""),"")="SI",_Requeridos!$A32,"")</f>
-        <v>¿El valor del activo supera 2.5 Salarios Mínimos Mensuales Legales Vigentes (SMMLV)?</v>
+      <c r="B22" t="s">
+        <v>1525</v>
       </c>
       <c r="C22" t="s">
         <v>1489</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="B23" s="34" t="str">
-        <f>IF(IFERROR(_xlfn.XLOOKUP('Check list'!$C$14,_Requeridos!$B$27:$D$27,_Requeridos!$B33:$D33,""),"")="SI",_Requeridos!$A33,"")</f>
-        <v>¿Es de interés para la organización, de tal forma que esté dispuesta a realizarle seguimiento y control como propiedad, planta y equipo?</v>
+      <c r="B23" s="34" t="s">
+        <v>1526</v>
       </c>
       <c r="C23" t="s">
         <v>1489</v>
       </c>
     </row>
-    <row r="24" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="47" t="str">
-        <f>IF(IFERROR(_xlfn.XLOOKUP('Check list'!$C$14,_Requeridos!$B$27:$D$27,_Requeridos!$B34:$D34,""),"")="SI",_Requeridos!$A34,"")</f>
-        <v/>
-      </c>
-      <c r="C24" s="47" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="47" t="str">
-        <f>IF(IFERROR(_xlfn.XLOOKUP('Check list'!$C$14,_Requeridos!$B$27:$D$27,_Requeridos!$B35:$D35,""),"")="SI",_Requeridos!$A35,"")</f>
-        <v/>
-      </c>
-      <c r="C25" s="47" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="47" t="str">
-        <f>IF(IFERROR(_xlfn.XLOOKUP('Check list'!$C$14,_Requeridos!$B$27:$D$27,_Requeridos!$B36:$D36,""),"")="SI",_Requeridos!$A36,"")</f>
-        <v/>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="47" t="str">
-        <f>IF(IFERROR(_xlfn.XLOOKUP('Check list'!$C$14,_Requeridos!$B$27:$D$27,_Requeridos!$B37:$D37,""),"")="SI",_Requeridos!$A37,"")</f>
-        <v/>
-      </c>
-      <c r="C27" s="47" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="48" t="str">
-        <f>IF(IFERROR(_xlfn.XLOOKUP('Check list'!$C$14,_Requeridos!$B$27:$D$27,_Requeridos!$B38:$D38,""),"")="SI",_Requeridos!$A38,"")</f>
-        <v/>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B25" s="11" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C25" s="21" t="str">
+        <f ca="1">IF(C14="","Seleccione un país válido",IF(COUNTIFS(B18:B32,"&lt;&gt;""",C18:C32,"NO")&gt;0,"NO CUMPLE","CUMPLE"))</f>
+        <v>CUMPLE</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:12" ht="23" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="82" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C27" s="83"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B28" s="47" t="s">
+        <v>1527</v>
       </c>
       <c r="C28" s="47" t="s">
         <v>1489</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B29" s="34"/>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B35" s="11" t="s">
+      <c r="B29" s="47" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C29" s="47" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B30" s="47" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C30" s="47" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B31" s="47" t="s">
         <v>1530</v>
       </c>
-      <c r="C35" s="21" t="str">
-        <f>IF(C14="","Seleccione un país válido",IF(COUNTIFS(B18:B28,"&lt;&gt;""",C18:C28,"NO")&gt;0,"NO CUMPLE","CUMPLE"))</f>
+      <c r="C31" s="47" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="B32" s="48" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C32" s="47" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="C34" s="21" t="str">
+        <f>IF(C14="","Seleccione un país válido",IF(COUNTIFS(B28:B32,"&lt;&gt;""",C28:C32,"NO")&gt;0,"NO CUMPLE","CUMPLE"))</f>
         <v>CUMPLE</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B42" s="52" t="s">
-        <v>1507</v>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B37" s="52" t="s">
+        <v>1501</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B27:C27"/>
   </mergeCells>
-  <conditionalFormatting sqref="C18:C28">
-    <cfRule type="expression" dxfId="4" priority="51">
-      <formula>B18=""</formula>
+  <conditionalFormatting sqref="C25">
+    <cfRule type="containsText" dxfId="5" priority="27" operator="containsText" text="NO CUMPLE">
+      <formula>NOT(ISERROR(SEARCH("NO CUMPLE",C25)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="28" operator="containsText" text="CUMPLE">
+      <formula>NOT(ISERROR(SEARCH("CUMPLE",C25)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C35">
-    <cfRule type="containsText" dxfId="3" priority="27" operator="containsText" text="NO CUMPLE">
-      <formula>NOT(ISERROR(SEARCH("NO CUMPLE",C35)))</formula>
+  <conditionalFormatting sqref="C34">
+    <cfRule type="containsText" dxfId="1" priority="29" operator="containsText" text="NO CUMPLE">
+      <formula>NOT(ISERROR(SEARCH("NO CUMPLE",C34)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="28" operator="containsText" text="CUMPLE">
-      <formula>NOT(ISERROR(SEARCH("CUMPLE",C35)))</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C34">
+    <cfRule type="containsText" dxfId="0" priority="30" operator="containsText" text="CUMPLE">
+      <formula>NOT(ISERROR(SEARCH("CUMPLE",C34)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13 C15:C16 C18:C29" xr:uid="{59ED7ABD-2EF3-4F7C-8CCB-C3B41B691E96}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13 C15:C16 C28:C32 C18:C23" xr:uid="{59ED7ABD-2EF3-4F7C-8CCB-C3B41B691E96}">
       <formula1>$L$12:$L$13</formula1>
     </dataValidation>
   </dataValidations>
@@ -45979,202 +45845,11 @@
   </headerFooter>
   <drawing r:id="rId2"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="29" id="{C6F7AAB8-2ACB-5948-8914-7B3367303C3F}">
-            <xm:f>IFERROR(_xlfn.XLOOKUP($C$14,_Requeridos!$A$21:$A$30,_Requeridos!$B$21:$B$30,""),"") &lt;&gt; "SI"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="64"/>
-                  <bgColor rgb="FFFFFFFF"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B18</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="31" id="{CE08586A-BC88-2A4D-95C4-65DCEFCF42E6}">
-            <xm:f>IFERROR(_xlfn.XLOOKUP($C$14,_Requeridos!$A$21:$A$30,_Requeridos!$C$21:$C$30,""),"") &lt;&gt; "SI"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="64"/>
-                  <bgColor rgb="FFFFFFFF"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B19</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="33" id="{A6203441-A068-4A4B-9577-139E76C45968}">
-            <xm:f>IFERROR(_xlfn.XLOOKUP($C$14,_Requeridos!$A$21:$A$30,_Requeridos!$D$21:$D$30,""),"") &lt;&gt; "SI"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="64"/>
-                  <bgColor rgb="FFFFFFFF"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B20</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="35" id="{28C7941B-1876-1046-8874-5722020BE513}">
-            <xm:f>IFERROR(_xlfn.XLOOKUP($C$14,_Requeridos!$A$21:$A$30,_Requeridos!$E$21:$E$30,""),"") &lt;&gt; "SI"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="64"/>
-                  <bgColor rgb="FFFFFFFF"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B21</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="37" id="{72ACC58B-1D1B-DD46-8B5A-797507531A08}">
-            <xm:f>IFERROR(_xlfn.XLOOKUP($C$14,_Requeridos!$A$21:$A$30,_Requeridos!$F$21:$F$30,""),"") &lt;&gt; "SI"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="64"/>
-                  <bgColor rgb="FFFFFFFF"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B22</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="39" id="{CBFFBDF4-04E7-9640-9C89-905137E125AC}">
-            <xm:f>IFERROR(_xlfn.XLOOKUP($C$14,_Requeridos!$A$21:$A$30,_Requeridos!$G$21:$G$30,""),"") &lt;&gt; "SI"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="64"/>
-                  <bgColor rgb="FFFFFFFF"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B23</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="41" id="{6F1567CF-EAC7-D742-B3AA-576B12F76461}">
-            <xm:f>IFERROR(_xlfn.XLOOKUP($C$14,_Requeridos!$A$21:$A$30,_Requeridos!$H$21:$H$30,""),"") &lt;&gt; "SI"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="64"/>
-                  <bgColor rgb="FFFFFFFF"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B24</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="43" id="{8434A182-8D55-AD4E-9E6D-49DC14BAF881}">
-            <xm:f>IFERROR(_xlfn.XLOOKUP($C$14,_Requeridos!$A$21:$A$30,_Requeridos!$I$21:$I$30,""),"") &lt;&gt; "SI"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="64"/>
-                  <bgColor rgb="FFFFFFFF"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B25</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="45" id="{4EF82847-CE1B-4A47-A7C8-A33F1C37F09D}">
-            <xm:f>IFERROR(_xlfn.XLOOKUP($C$14,_Requeridos!$A$21:$A$30,_Requeridos!$J$21:$J$30,""),"") &lt;&gt; "SI"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="64"/>
-                  <bgColor rgb="FFFFFFFF"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B26</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="47" id="{EB3BEA08-97F5-3C4D-869B-42212D6D0A52}">
-            <xm:f>IFERROR(_xlfn.XLOOKUP($C$14,_Requeridos!$A$21:$A$30,_Requeridos!$K$21:$K$30,""),"") &lt;&gt; "SI"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="64"/>
-                  <bgColor rgb="FFFFFFFF"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B27</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="49" id="{B24B4B04-B24F-8941-8A0D-885423D539B8}">
-            <xm:f>IFERROR(_xlfn.XLOOKUP($C$14,_Requeridos!$A$21:$A$30,_Requeridos!$L$21:$L$30,""),"") &lt;&gt; "SI"</xm:f>
-            <x14:dxf>
-              <font>
-                <color rgb="FFFFFFFF"/>
-              </font>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor indexed="64"/>
-                  <bgColor rgb="FFFFFFFF"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>B28</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="País" prompt="Selecciona el país" xr:uid="{24B190AB-A1BD-9342-A014-8FAC3536C7F8}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B5DB2DB7-FD43-5546-BD62-0D7870E179BD}">
           <x14:formula1>
-            <xm:f>_ListasClase!$Q$2:$Q$10</xm:f>
+            <xm:f>Sociedades!$A$2:$A$10</xm:f>
           </x14:formula1>
           <xm:sqref>C14</xm:sqref>
         </x14:dataValidation>
@@ -46267,81 +45942,81 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A11" s="39"/>
-      <c r="B11" s="82" t="s">
+      <c r="B11" s="87" t="s">
         <v>1348</v>
       </c>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="83"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="83"/>
-      <c r="M11" s="83"/>
-      <c r="N11" s="83"/>
-      <c r="O11" s="83"/>
-      <c r="P11" s="83"/>
-      <c r="Q11" s="83"/>
-      <c r="R11" s="83"/>
-      <c r="S11" s="83"/>
-      <c r="T11" s="83"/>
-      <c r="U11" s="83"/>
-      <c r="V11" s="83"/>
-      <c r="W11" s="83"/>
-      <c r="X11" s="83"/>
-      <c r="Y11" s="83"/>
-      <c r="Z11" s="83"/>
-      <c r="AA11" s="83"/>
-      <c r="AB11" s="83"/>
-      <c r="AC11" s="83"/>
-      <c r="AD11" s="83"/>
-      <c r="AE11" s="83"/>
-      <c r="AF11" s="83"/>
-      <c r="AG11" s="83"/>
-      <c r="AH11" s="83"/>
-      <c r="AI11" s="83"/>
-      <c r="AJ11" s="84"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="88"/>
+      <c r="J11" s="88"/>
+      <c r="K11" s="88"/>
+      <c r="L11" s="88"/>
+      <c r="M11" s="88"/>
+      <c r="N11" s="88"/>
+      <c r="O11" s="88"/>
+      <c r="P11" s="88"/>
+      <c r="Q11" s="88"/>
+      <c r="R11" s="88"/>
+      <c r="S11" s="88"/>
+      <c r="T11" s="88"/>
+      <c r="U11" s="88"/>
+      <c r="V11" s="88"/>
+      <c r="W11" s="88"/>
+      <c r="X11" s="88"/>
+      <c r="Y11" s="88"/>
+      <c r="Z11" s="88"/>
+      <c r="AA11" s="88"/>
+      <c r="AB11" s="88"/>
+      <c r="AC11" s="88"/>
+      <c r="AD11" s="88"/>
+      <c r="AE11" s="88"/>
+      <c r="AF11" s="88"/>
+      <c r="AG11" s="88"/>
+      <c r="AH11" s="88"/>
+      <c r="AI11" s="88"/>
+      <c r="AJ11" s="89"/>
     </row>
     <row r="12" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="40"/>
-      <c r="B12" s="85"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="86"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="86"/>
-      <c r="J12" s="86"/>
-      <c r="K12" s="86"/>
-      <c r="L12" s="86"/>
-      <c r="M12" s="86"/>
-      <c r="N12" s="86"/>
-      <c r="O12" s="86"/>
-      <c r="P12" s="86"/>
-      <c r="Q12" s="86"/>
-      <c r="R12" s="86"/>
-      <c r="S12" s="86"/>
-      <c r="T12" s="86"/>
-      <c r="U12" s="86"/>
-      <c r="V12" s="86"/>
-      <c r="W12" s="86"/>
-      <c r="X12" s="86"/>
-      <c r="Y12" s="86"/>
-      <c r="Z12" s="86"/>
-      <c r="AA12" s="86"/>
-      <c r="AB12" s="86"/>
-      <c r="AC12" s="86"/>
-      <c r="AD12" s="86"/>
-      <c r="AE12" s="86"/>
-      <c r="AF12" s="86"/>
-      <c r="AG12" s="86"/>
-      <c r="AH12" s="86"/>
-      <c r="AI12" s="86"/>
-      <c r="AJ12" s="87"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="91"/>
+      <c r="J12" s="91"/>
+      <c r="K12" s="91"/>
+      <c r="L12" s="91"/>
+      <c r="M12" s="91"/>
+      <c r="N12" s="91"/>
+      <c r="O12" s="91"/>
+      <c r="P12" s="91"/>
+      <c r="Q12" s="91"/>
+      <c r="R12" s="91"/>
+      <c r="S12" s="91"/>
+      <c r="T12" s="91"/>
+      <c r="U12" s="91"/>
+      <c r="V12" s="91"/>
+      <c r="W12" s="91"/>
+      <c r="X12" s="91"/>
+      <c r="Y12" s="91"/>
+      <c r="Z12" s="91"/>
+      <c r="AA12" s="91"/>
+      <c r="AB12" s="91"/>
+      <c r="AC12" s="91"/>
+      <c r="AD12" s="91"/>
+      <c r="AE12" s="91"/>
+      <c r="AF12" s="91"/>
+      <c r="AG12" s="91"/>
+      <c r="AH12" s="91"/>
+      <c r="AI12" s="91"/>
+      <c r="AJ12" s="92"/>
     </row>
     <row r="13" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="75"/>
@@ -46389,9 +46064,9 @@
       <c r="C14" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="80"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="80"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="85"/>
       <c r="G14" s="56"/>
       <c r="H14" s="60"/>
       <c r="I14" s="60"/>
@@ -46429,9 +46104,9 @@
         <v>1350</v>
       </c>
       <c r="C15" s="56"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="85"/>
+      <c r="F15" s="85"/>
       <c r="G15" s="56"/>
       <c r="H15" s="60"/>
       <c r="I15" s="60"/>
@@ -46469,9 +46144,9 @@
         <v>1351</v>
       </c>
       <c r="C16" s="57"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="80"/>
+      <c r="D16" s="85"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="85"/>
       <c r="G16" s="61"/>
       <c r="H16" s="60"/>
       <c r="I16" s="60"/>
@@ -46509,9 +46184,9 @@
         <v>1352</v>
       </c>
       <c r="C17" s="59"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
       <c r="G17" s="61"/>
       <c r="H17" s="60"/>
       <c r="I17" s="60"/>
@@ -46549,9 +46224,9 @@
         <v>1353</v>
       </c>
       <c r="C18" s="59"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="80"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="85"/>
+      <c r="F18" s="85"/>
       <c r="G18" s="61"/>
       <c r="H18" s="60"/>
       <c r="I18" s="60"/>
@@ -46589,9 +46264,9 @@
         <v>1354</v>
       </c>
       <c r="C19" s="59"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
       <c r="G19" s="61"/>
       <c r="H19" s="60"/>
       <c r="I19" s="60"/>
@@ -46656,11 +46331,11 @@
       <c r="AD20" s="37"/>
       <c r="AE20" s="37"/>
       <c r="AF20" s="37"/>
-      <c r="AG20" s="81" t="s">
+      <c r="AG20" s="86" t="s">
         <v>1355</v>
       </c>
-      <c r="AH20" s="81"/>
-      <c r="AI20" s="81"/>
+      <c r="AH20" s="86"/>
+      <c r="AI20" s="86"/>
     </row>
     <row r="21" spans="1:37" s="45" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="43"/>
@@ -50322,10 +49997,10 @@
     <mergeCell ref="B11:AJ12"/>
   </mergeCells>
   <conditionalFormatting sqref="AJ22:AJ89">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Faltan">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Faltan">
       <formula>NOT(ISERROR(SEARCH("Faltan",AJ22)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Completo">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Completo">
       <formula>NOT(ISERROR(SEARCH("Completo",AJ22)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/resources/Formato_Dinamico_.xlsx
+++ b/resources/Formato_Dinamico_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santiago/Desktop/creacion activo SAP py/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C90E71-D4EA-874E-B665-80C62C1D563F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B403EE66-DB19-E84D-AE57-39CEF092B42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="7" xr2:uid="{CA7242B3-F58B-4D52-905C-F122405A1A29}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Criterio " sheetId="2" r:id="rId3"/>
     <sheet name="Ceco" sheetId="3" r:id="rId4"/>
     <sheet name="Emplazamiento" sheetId="4" r:id="rId5"/>
-    <sheet name="_ListasClase" sheetId="8" r:id="rId6"/>
+    <sheet name="_ListasClase" sheetId="8" state="hidden" r:id="rId6"/>
     <sheet name="_Requeridos" sheetId="9" r:id="rId7"/>
     <sheet name="Check list" sheetId="11" r:id="rId8"/>
     <sheet name="Formato" sheetId="5" r:id="rId9"/>
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7844" uniqueCount="1533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7838" uniqueCount="1530">
   <si>
     <t xml:space="preserve">Sociedad </t>
   </si>
@@ -4635,19 +4635,7 @@
     <t>SI</t>
   </si>
   <si>
-    <t>PAÍSES</t>
-  </si>
-  <si>
     <t>✅ Checklist de Validación</t>
-  </si>
-  <si>
-    <t>PE=</t>
-  </si>
-  <si>
-    <t>CO=</t>
-  </si>
-  <si>
-    <t>CHI=</t>
   </si>
   <si>
     <t>NO</t>
@@ -4832,6 +4820,9 @@
   </si>
   <si>
     <t>EXCLUSIVO PARA FILIALES DE PERÚ</t>
+  </si>
+  <si>
+    <t>Respuesta SI/NO</t>
   </si>
 </sst>
 </file>
@@ -5179,7 +5170,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -5220,96 +5211,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -5421,7 +5322,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5477,15 +5378,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -5536,20 +5428,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -5641,16 +5527,10 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5664,29 +5544,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="7" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="7" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="7" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="7" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5694,33 +5581,7 @@
     <cellStyle name="Normal 4" xfId="1" xr:uid="{3283983A-646C-44C7-A2FC-29FE31B28852}"/>
     <cellStyle name="Porcentaje 2" xfId="2" xr:uid="{57290B1F-A1BC-40FC-80FE-1CB63CCFCBB6}"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF006400"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <font>
         <b/>
@@ -5763,133 +5624,53 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF006400"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF006400"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5983,7 +5764,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>1962149</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>47348</xdr:rowOff>
+      <xdr:rowOff>85448</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6632,7 +6413,7 @@
       <c r="AN1" t="s">
         <v>1428</v>
       </c>
-      <c r="AO1" s="79" t="s">
+      <c r="AO1" s="68" t="s">
         <v>1429</v>
       </c>
       <c r="AP1" t="s">
@@ -6695,12 +6476,12 @@
         <f>Formato!N22</f>
         <v>0</v>
       </c>
-      <c r="I2" s="79">
+      <c r="I2" s="68">
         <f>Formato!AA22</f>
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="Q2">
         <f>Formato!N22</f>
@@ -6710,7 +6491,7 @@
         <f>Formato!D22</f>
         <v>0</v>
       </c>
-      <c r="S2" s="79"/>
+      <c r="S2" s="68"/>
       <c r="T2" t="str">
         <f>Formato!AB22</f>
         <v xml:space="preserve">POLP5K04CS </v>
@@ -16923,7 +16704,7 @@
         <v>941</v>
       </c>
       <c r="J192" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.2">
@@ -42077,7 +41858,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor theme="4" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:Q346"/>
+  <dimension ref="A1:S346"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="48.33203125" bestFit="1" customWidth="1"/>
@@ -42090,7 +41871,7 @@
     <col min="15" max="15" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>1449</v>
       </c>
@@ -42116,10 +41897,13 @@
         <v>1380</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>1502</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1498</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="str" cm="1">
         <f t="array" ref="A2:A31">IFERROR(_xlfn._xlws.FILTER(Clase!$C$2:$C$292, Clase!$A$2:$A$292=Formato!$C$14, ""), "")</f>
         <v>Terrenos Rurales</v>
@@ -42156,8 +41940,11 @@
         <f t="array" ref="Q2:Q4">IFERROR(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Sociedades!$B$2:$B$10,Sociedades!$B$2:$B$10&lt;&gt;"")),"")</f>
         <v>Colombia</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S2" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <v>Edificios</v>
       </c>
@@ -42185,8 +41972,11 @@
       <c r="Q3" t="str">
         <v>Chile</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S3" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <v>Leasing Financiero - Edificaciones</v>
       </c>
@@ -42215,7 +42005,7 @@
         <v>Perú</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <v>Leasing Financiero - Edificaciones Relacion</v>
       </c>
@@ -42241,7 +42031,7 @@
         <v>10003</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
         <v>Equipos de Subestación Nueva Estruc 40 Años</v>
       </c>
@@ -42267,7 +42057,7 @@
         <v>10004</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <v>Equipos de Subestación Nueva Estruc 38 Años</v>
       </c>
@@ -42293,7 +42083,7 @@
         <v>10005</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
         <v>Equipos de Subestación Nueva Estruc 32 Años</v>
       </c>
@@ -42319,7 +42109,7 @@
         <v>10006</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
         <v>Equipos de Subestación Nueva Estruc 30 Años</v>
       </c>
@@ -42345,7 +42135,7 @@
         <v>10007</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
         <v>Equipos de Subestación Nueva Estruc 27 Años</v>
       </c>
@@ -42371,7 +42161,7 @@
         <v>10008</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <v>Equipos de Subestación Nueva Estruc 25 Años</v>
       </c>
@@ -42397,7 +42187,7 @@
         <v>10009</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <v>Equipos de Subestación Nueva Estruc 20 Años</v>
       </c>
@@ -42423,7 +42213,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <v>Equipos de Subestación Nueva Estruc 15 Años</v>
       </c>
@@ -42449,7 +42239,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
         <v>Equipos de Subestación Nueva Estruc 39 Años</v>
       </c>
@@ -42475,7 +42265,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
         <v>Equipos de Subestación Nueva Estruc 18 Años</v>
       </c>
@@ -42501,7 +42291,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
         <v>Equipos de Subestación Nueva Estruc 10 Años</v>
       </c>
@@ -45445,56 +45235,56 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="77" t="s">
-        <v>1503</v>
+      <c r="A16" s="66" t="s">
+        <v>1499</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="78" t="s">
-        <v>1504</v>
+      <c r="A17" s="67" t="s">
+        <v>1500</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="78" t="s">
-        <v>1505</v>
+      <c r="A18" s="67" t="s">
+        <v>1501</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E20" s="18" t="s">
         <v>1506</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="F20" s="18" t="s">
         <v>1507</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="G20" s="18" t="s">
         <v>1508</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="H20" s="18" t="s">
         <v>1509</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="I20" s="18" t="s">
         <v>1510</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="J20" s="18" t="s">
         <v>1511</v>
       </c>
-      <c r="G20" s="18" t="s">
+      <c r="K20" s="18" t="s">
         <v>1512</v>
       </c>
-      <c r="H20" s="18" t="s">
+      <c r="L20" s="18" t="s">
         <v>1513</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>1514</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>1515</v>
-      </c>
-      <c r="K20" s="18" t="s">
-        <v>1516</v>
-      </c>
-      <c r="L20" s="18" t="s">
-        <v>1517</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
@@ -45595,7 +45385,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor theme="3" tint="0.249977111117893"/>
   </sheetPr>
-  <dimension ref="B4:L37"/>
+  <dimension ref="B5:L37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.1640625" customWidth="1"/>
@@ -45604,121 +45394,106 @@
     <col min="6" max="12" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F5" s="80" t="s">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+    </row>
+    <row r="7" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+    </row>
+    <row r="8" spans="2:12" ht="23" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="69" t="s">
         <v>1490</v>
       </c>
-      <c r="G5" s="81"/>
-    </row>
-    <row r="6" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F6" s="53"/>
-      <c r="G6" s="54"/>
-    </row>
-    <row r="7" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="F7" s="53"/>
-      <c r="G7" s="54"/>
-    </row>
-    <row r="8" spans="2:12" ht="23" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="82" t="s">
-        <v>1491</v>
-      </c>
-      <c r="C8" s="83"/>
-      <c r="F8" s="25" t="s">
+      <c r="C8" s="70"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="F10" s="80"/>
+      <c r="G10" s="80"/>
+    </row>
+    <row r="11" spans="2:12" ht="19" x14ac:dyDescent="0.2">
+      <c r="B11" s="71" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+    </row>
+    <row r="12" spans="2:12" ht="19" x14ac:dyDescent="0.2">
+      <c r="B12" s="71" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C12" s="71"/>
+      <c r="L12" s="80"/>
+    </row>
+    <row r="13" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L13" s="80"/>
+    </row>
+    <row r="14" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="40" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="L14" s="80"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="80"/>
+    </row>
+    <row r="16" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L16" s="80"/>
+    </row>
+    <row r="17" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="42" t="s">
         <v>1492</v>
       </c>
-      <c r="G8" s="26" t="s">
-        <v>1446</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="F9" s="27" t="s">
+      <c r="C17" s="42" t="s">
         <v>1493</v>
       </c>
-      <c r="G9" s="28" t="s">
-        <v>1441</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="F10" s="27" t="s">
-        <v>1494</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>1442</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="20" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="84" t="s">
-        <v>1499</v>
-      </c>
-      <c r="C11" s="84"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="30"/>
-    </row>
-    <row r="12" spans="2:12" ht="19" x14ac:dyDescent="0.2">
-      <c r="B12" s="84" t="s">
-        <v>1498</v>
-      </c>
-      <c r="C12" s="84"/>
-      <c r="L12" s="31" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="L13" s="32" t="s">
-        <v>1495</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="49" t="s">
-        <v>1520</v>
-      </c>
-      <c r="C14" s="50" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="L16" s="33"/>
-    </row>
-    <row r="17" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="51" t="s">
-        <v>1496</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>1497</v>
-      </c>
-      <c r="L17" s="33"/>
+      <c r="L17" s="80"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
       <c r="C18" t="s">
         <v>1489</v>
       </c>
-      <c r="L18" s="33"/>
+      <c r="L18" s="80"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
       <c r="C19" t="s">
         <v>1489</v>
       </c>
-      <c r="L19" s="33"/>
-    </row>
-    <row r="20" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L19" s="80"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
       <c r="C20" t="s">
         <v>1489</v>
       </c>
-      <c r="L20" s="32"/>
+      <c r="L20" s="80"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
       <c r="C21" t="s">
         <v>1489</v>
@@ -45726,15 +45501,15 @@
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="C22" t="s">
         <v>1489</v>
       </c>
     </row>
     <row r="23" spans="2:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="B23" s="34" t="s">
-        <v>1526</v>
+      <c r="B23" s="25" t="s">
+        <v>1522</v>
       </c>
       <c r="C23" t="s">
         <v>1489</v>
@@ -45742,57 +45517,57 @@
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="11" t="s">
-        <v>1518</v>
+        <v>1514</v>
       </c>
       <c r="C25" s="21" t="str">
-        <f ca="1">IF(C14="","Seleccione un país válido",IF(COUNTIFS(B18:B32,"&lt;&gt;""",C18:C32,"NO")&gt;0,"NO CUMPLE","CUMPLE"))</f>
+        <f>IF(C14="","Seleccione un país válido",IF(COUNTIFS(B18:B23,"&lt;&gt;""",C18:C23,"NO")&gt;0,"NO CUMPLE","CUMPLE"))</f>
         <v>CUMPLE</v>
       </c>
     </row>
     <row r="26" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="2:12" ht="23" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="82" t="s">
-        <v>1532</v>
-      </c>
-      <c r="C27" s="83"/>
+      <c r="B27" s="69" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C27" s="70"/>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="38" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B29" s="38" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B30" s="38" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B31" s="38" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="B32" s="39" t="s">
         <v>1527</v>
       </c>
-      <c r="C28" s="47" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B29" s="47" t="s">
-        <v>1528</v>
-      </c>
-      <c r="C29" s="47" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B30" s="47" t="s">
-        <v>1529</v>
-      </c>
-      <c r="C30" s="47" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B31" s="47" t="s">
-        <v>1530</v>
-      </c>
-      <c r="C31" s="47" t="s">
-        <v>1489</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="B32" s="48" t="s">
-        <v>1531</v>
-      </c>
-      <c r="C32" s="47" t="s">
+      <c r="C32" s="38" t="s">
         <v>1489</v>
       </c>
     </row>
@@ -45803,8 +45578,8 @@
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B37" s="52" t="s">
-        <v>1501</v>
+      <c r="B37" s="43" t="s">
+        <v>1497</v>
       </c>
     </row>
   </sheetData>
@@ -45815,26 +45590,26 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B27:C27"/>
   </mergeCells>
+  <conditionalFormatting sqref="C34">
+    <cfRule type="containsText" dxfId="5" priority="29" operator="containsText" text="NO CUMPLE">
+      <formula>NOT(ISERROR(SEARCH("NO CUMPLE",C34)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="30" operator="containsText" text="CUMPLE">
+      <formula>NOT(ISERROR(SEARCH("CUMPLE",C34)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C25">
-    <cfRule type="containsText" dxfId="5" priority="27" operator="containsText" text="NO CUMPLE">
+    <cfRule type="containsText" dxfId="3" priority="31" operator="containsText" text="NO CUMPLE">
       <formula>NOT(ISERROR(SEARCH("NO CUMPLE",C25)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="28" operator="containsText" text="CUMPLE">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C25">
+    <cfRule type="containsText" dxfId="2" priority="32" operator="containsText" text="CUMPLE">
       <formula>NOT(ISERROR(SEARCH("CUMPLE",C25)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C34">
-    <cfRule type="containsText" dxfId="1" priority="29" operator="containsText" text="NO CUMPLE">
-      <formula>NOT(ISERROR(SEARCH("NO CUMPLE",C34)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C34">
-    <cfRule type="containsText" dxfId="0" priority="30" operator="containsText" text="CUMPLE">
-      <formula>NOT(ISERROR(SEARCH("CUMPLE",C34)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13 C15:C16 C28:C32 C18:C23" xr:uid="{59ED7ABD-2EF3-4F7C-8CCB-C3B41B691E96}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C13 C15:C16" xr:uid="{59ED7ABD-2EF3-4F7C-8CCB-C3B41B691E96}">
       <formula1>$L$12:$L$13</formula1>
     </dataValidation>
   </dataValidations>
@@ -45846,12 +45621,18 @@
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B5DB2DB7-FD43-5546-BD62-0D7870E179BD}">
           <x14:formula1>
             <xm:f>Sociedades!$A$2:$A$10</xm:f>
           </x14:formula1>
           <xm:sqref>C14</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{61407E6C-8F5F-904E-8613-F639EB9C5A3C}">
+          <x14:formula1>
+            <xm:f>_ListasClase!$S$2:$S$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>C18:C23 C28:C32</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -45867,4128 +45648,4128 @@
   <dimension ref="A10:AK107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.5" style="38" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30" style="38" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.1640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.1640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.6640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.6640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8" style="38" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.83203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="19.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.1640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.6640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.6640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.1640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.1640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="18.1640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.6640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.1640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.83203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="11.1640625" style="38" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.83203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="213.33203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="10.83203125" style="38"/>
+    <col min="1" max="1" width="3.5" style="29" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30" style="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.1640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.5" style="29" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5" style="29" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8" style="29" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.5" style="29" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="19.5" style="29" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.1640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.1640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.1640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.5" style="29" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18.1640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20.5" style="29" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.1640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.83203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="11.1640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.83203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="213.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="10.83203125" style="29"/>
   </cols>
   <sheetData>
     <row r="10" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="35"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="35"/>
-      <c r="V10" s="35"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="35"/>
-      <c r="Y10" s="35"/>
-      <c r="Z10" s="35"/>
-      <c r="AA10" s="35"/>
-      <c r="AB10" s="35"/>
-      <c r="AC10" s="35"/>
-      <c r="AD10" s="35"/>
-      <c r="AE10" s="35"/>
-      <c r="AF10" s="35"/>
-      <c r="AG10" s="35"/>
-      <c r="AH10" s="35"/>
-      <c r="AI10" s="37"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="26"/>
+      <c r="U10" s="26"/>
+      <c r="V10" s="26"/>
+      <c r="W10" s="26"/>
+      <c r="X10" s="26"/>
+      <c r="Y10" s="26"/>
+      <c r="Z10" s="26"/>
+      <c r="AA10" s="26"/>
+      <c r="AB10" s="26"/>
+      <c r="AC10" s="26"/>
+      <c r="AD10" s="26"/>
+      <c r="AE10" s="26"/>
+      <c r="AF10" s="26"/>
+      <c r="AG10" s="26"/>
+      <c r="AH10" s="26"/>
+      <c r="AI10" s="28"/>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A11" s="39"/>
-      <c r="B11" s="87" t="s">
+      <c r="A11" s="30"/>
+      <c r="B11" s="74" t="s">
         <v>1348</v>
       </c>
-      <c r="C11" s="88"/>
-      <c r="D11" s="88"/>
-      <c r="E11" s="88"/>
-      <c r="F11" s="88"/>
-      <c r="G11" s="88"/>
-      <c r="H11" s="88"/>
-      <c r="I11" s="88"/>
-      <c r="J11" s="88"/>
-      <c r="K11" s="88"/>
-      <c r="L11" s="88"/>
-      <c r="M11" s="88"/>
-      <c r="N11" s="88"/>
-      <c r="O11" s="88"/>
-      <c r="P11" s="88"/>
-      <c r="Q11" s="88"/>
-      <c r="R11" s="88"/>
-      <c r="S11" s="88"/>
-      <c r="T11" s="88"/>
-      <c r="U11" s="88"/>
-      <c r="V11" s="88"/>
-      <c r="W11" s="88"/>
-      <c r="X11" s="88"/>
-      <c r="Y11" s="88"/>
-      <c r="Z11" s="88"/>
-      <c r="AA11" s="88"/>
-      <c r="AB11" s="88"/>
-      <c r="AC11" s="88"/>
-      <c r="AD11" s="88"/>
-      <c r="AE11" s="88"/>
-      <c r="AF11" s="88"/>
-      <c r="AG11" s="88"/>
-      <c r="AH11" s="88"/>
-      <c r="AI11" s="88"/>
-      <c r="AJ11" s="89"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="75"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="75"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="75"/>
+      <c r="Q11" s="75"/>
+      <c r="R11" s="75"/>
+      <c r="S11" s="75"/>
+      <c r="T11" s="75"/>
+      <c r="U11" s="75"/>
+      <c r="V11" s="75"/>
+      <c r="W11" s="75"/>
+      <c r="X11" s="75"/>
+      <c r="Y11" s="75"/>
+      <c r="Z11" s="75"/>
+      <c r="AA11" s="75"/>
+      <c r="AB11" s="75"/>
+      <c r="AC11" s="75"/>
+      <c r="AD11" s="75"/>
+      <c r="AE11" s="75"/>
+      <c r="AF11" s="75"/>
+      <c r="AG11" s="75"/>
+      <c r="AH11" s="75"/>
+      <c r="AI11" s="75"/>
+      <c r="AJ11" s="76"/>
     </row>
     <row r="12" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="40"/>
-      <c r="B12" s="90"/>
-      <c r="C12" s="91"/>
-      <c r="D12" s="91"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="91"/>
-      <c r="K12" s="91"/>
-      <c r="L12" s="91"/>
-      <c r="M12" s="91"/>
-      <c r="N12" s="91"/>
-      <c r="O12" s="91"/>
-      <c r="P12" s="91"/>
-      <c r="Q12" s="91"/>
-      <c r="R12" s="91"/>
-      <c r="S12" s="91"/>
-      <c r="T12" s="91"/>
-      <c r="U12" s="91"/>
-      <c r="V12" s="91"/>
-      <c r="W12" s="91"/>
-      <c r="X12" s="91"/>
-      <c r="Y12" s="91"/>
-      <c r="Z12" s="91"/>
-      <c r="AA12" s="91"/>
-      <c r="AB12" s="91"/>
-      <c r="AC12" s="91"/>
-      <c r="AD12" s="91"/>
-      <c r="AE12" s="91"/>
-      <c r="AF12" s="91"/>
-      <c r="AG12" s="91"/>
-      <c r="AH12" s="91"/>
-      <c r="AI12" s="91"/>
-      <c r="AJ12" s="92"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="78"/>
+      <c r="N12" s="78"/>
+      <c r="O12" s="78"/>
+      <c r="P12" s="78"/>
+      <c r="Q12" s="78"/>
+      <c r="R12" s="78"/>
+      <c r="S12" s="78"/>
+      <c r="T12" s="78"/>
+      <c r="U12" s="78"/>
+      <c r="V12" s="78"/>
+      <c r="W12" s="78"/>
+      <c r="X12" s="78"/>
+      <c r="Y12" s="78"/>
+      <c r="Z12" s="78"/>
+      <c r="AA12" s="78"/>
+      <c r="AB12" s="78"/>
+      <c r="AC12" s="78"/>
+      <c r="AD12" s="78"/>
+      <c r="AE12" s="78"/>
+      <c r="AF12" s="78"/>
+      <c r="AG12" s="78"/>
+      <c r="AH12" s="78"/>
+      <c r="AI12" s="78"/>
+      <c r="AJ12" s="79"/>
     </row>
     <row r="13" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="75"/>
-      <c r="B13" s="76"/>
-      <c r="C13" s="76"/>
-      <c r="D13" s="76"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="76"/>
-      <c r="G13" s="76"/>
-      <c r="H13" s="76"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="76"/>
-      <c r="K13" s="76"/>
-      <c r="L13" s="76"/>
-      <c r="M13" s="76"/>
-      <c r="N13" s="76"/>
-      <c r="O13" s="76"/>
-      <c r="P13" s="76"/>
-      <c r="Q13" s="76"/>
-      <c r="R13" s="76"/>
-      <c r="S13" s="76"/>
-      <c r="T13" s="76"/>
-      <c r="U13" s="76"/>
-      <c r="V13" s="76"/>
-      <c r="W13" s="76"/>
-      <c r="X13" s="76"/>
-      <c r="Y13" s="76"/>
-      <c r="Z13" s="76"/>
-      <c r="AA13" s="76"/>
-      <c r="AB13" s="76"/>
-      <c r="AC13" s="76"/>
-      <c r="AD13" s="76"/>
-      <c r="AE13" s="76"/>
-      <c r="AF13" s="76"/>
-      <c r="AG13" s="76"/>
-      <c r="AH13" s="76"/>
-      <c r="AI13" s="76"/>
-      <c r="AJ13" s="76"/>
+      <c r="A13" s="64"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="65"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="65"/>
+      <c r="U13" s="65"/>
+      <c r="V13" s="65"/>
+      <c r="W13" s="65"/>
+      <c r="X13" s="65"/>
+      <c r="Y13" s="65"/>
+      <c r="Z13" s="65"/>
+      <c r="AA13" s="65"/>
+      <c r="AB13" s="65"/>
+      <c r="AC13" s="65"/>
+      <c r="AD13" s="65"/>
+      <c r="AE13" s="65"/>
+      <c r="AF13" s="65"/>
+      <c r="AG13" s="65"/>
+      <c r="AH13" s="65"/>
+      <c r="AI13" s="65"/>
+      <c r="AJ13" s="65"/>
     </row>
     <row r="14" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="42"/>
-      <c r="B14" s="55" t="s">
+      <c r="A14" s="33"/>
+      <c r="B14" s="44" t="s">
         <v>1349</v>
       </c>
-      <c r="C14" s="74" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="85"/>
-      <c r="E14" s="85"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="56"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="60"/>
-      <c r="K14" s="60"/>
-      <c r="L14" s="60"/>
-      <c r="M14" s="60"/>
-      <c r="N14" s="60"/>
-      <c r="O14" s="60"/>
-      <c r="P14" s="60"/>
-      <c r="Q14" s="60"/>
-      <c r="R14" s="60"/>
-      <c r="S14" s="60"/>
-      <c r="T14" s="60"/>
-      <c r="U14" s="60"/>
-      <c r="V14" s="60"/>
-      <c r="W14" s="60"/>
-      <c r="X14" s="60"/>
-      <c r="Y14" s="60"/>
-      <c r="Z14" s="60"/>
-      <c r="AA14" s="60"/>
-      <c r="AB14" s="60"/>
-      <c r="AC14" s="60"/>
-      <c r="AD14" s="60"/>
-      <c r="AE14" s="60"/>
-      <c r="AF14" s="56"/>
-      <c r="AG14" s="60"/>
-      <c r="AH14" s="60"/>
-      <c r="AI14" s="62"/>
-      <c r="AJ14" s="41"/>
+      <c r="C14" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
+      <c r="N14" s="49"/>
+      <c r="O14" s="49"/>
+      <c r="P14" s="49"/>
+      <c r="Q14" s="49"/>
+      <c r="R14" s="49"/>
+      <c r="S14" s="49"/>
+      <c r="T14" s="49"/>
+      <c r="U14" s="49"/>
+      <c r="V14" s="49"/>
+      <c r="W14" s="49"/>
+      <c r="X14" s="49"/>
+      <c r="Y14" s="49"/>
+      <c r="Z14" s="49"/>
+      <c r="AA14" s="49"/>
+      <c r="AB14" s="49"/>
+      <c r="AC14" s="49"/>
+      <c r="AD14" s="49"/>
+      <c r="AE14" s="49"/>
+      <c r="AF14" s="45"/>
+      <c r="AG14" s="49"/>
+      <c r="AH14" s="49"/>
+      <c r="AI14" s="51"/>
+      <c r="AJ14" s="32"/>
     </row>
     <row r="15" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="42"/>
-      <c r="B15" s="55" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="44" t="s">
         <v>1350</v>
       </c>
-      <c r="C15" s="56"/>
-      <c r="D15" s="85"/>
-      <c r="E15" s="85"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="60"/>
-      <c r="N15" s="60"/>
-      <c r="O15" s="60"/>
-      <c r="P15" s="60"/>
-      <c r="Q15" s="60"/>
-      <c r="R15" s="60"/>
-      <c r="S15" s="60"/>
-      <c r="T15" s="60"/>
-      <c r="U15" s="60"/>
-      <c r="V15" s="60"/>
-      <c r="W15" s="60"/>
-      <c r="X15" s="60"/>
-      <c r="Y15" s="60"/>
-      <c r="Z15" s="60"/>
-      <c r="AA15" s="60"/>
-      <c r="AB15" s="60"/>
-      <c r="AC15" s="60"/>
-      <c r="AD15" s="60"/>
-      <c r="AE15" s="60"/>
-      <c r="AF15" s="56"/>
-      <c r="AG15" s="60"/>
-      <c r="AH15" s="60"/>
-      <c r="AI15" s="62"/>
-      <c r="AJ15" s="41"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="49"/>
+      <c r="O15" s="49"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="49"/>
+      <c r="U15" s="49"/>
+      <c r="V15" s="49"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="49"/>
+      <c r="Y15" s="49"/>
+      <c r="Z15" s="49"/>
+      <c r="AA15" s="49"/>
+      <c r="AB15" s="49"/>
+      <c r="AC15" s="49"/>
+      <c r="AD15" s="49"/>
+      <c r="AE15" s="49"/>
+      <c r="AF15" s="45"/>
+      <c r="AG15" s="49"/>
+      <c r="AH15" s="49"/>
+      <c r="AI15" s="51"/>
+      <c r="AJ15" s="32"/>
     </row>
     <row r="16" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="42"/>
-      <c r="B16" s="55" t="s">
+      <c r="A16" s="33"/>
+      <c r="B16" s="44" t="s">
         <v>1351</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="85"/>
-      <c r="F16" s="85"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60"/>
-      <c r="M16" s="60"/>
-      <c r="N16" s="60"/>
-      <c r="O16" s="60"/>
-      <c r="P16" s="60"/>
-      <c r="Q16" s="60"/>
-      <c r="R16" s="60"/>
-      <c r="S16" s="60"/>
-      <c r="T16" s="60"/>
-      <c r="U16" s="60"/>
-      <c r="V16" s="60"/>
-      <c r="W16" s="60"/>
-      <c r="X16" s="60"/>
-      <c r="Y16" s="60"/>
-      <c r="Z16" s="60"/>
-      <c r="AA16" s="60"/>
-      <c r="AB16" s="60"/>
-      <c r="AC16" s="60"/>
-      <c r="AD16" s="60"/>
-      <c r="AE16" s="60"/>
-      <c r="AF16" s="61"/>
-      <c r="AG16" s="60"/>
-      <c r="AH16" s="60"/>
-      <c r="AI16" s="62"/>
-      <c r="AJ16" s="41"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="49"/>
+      <c r="L16" s="49"/>
+      <c r="M16" s="49"/>
+      <c r="N16" s="49"/>
+      <c r="O16" s="49"/>
+      <c r="P16" s="49"/>
+      <c r="Q16" s="49"/>
+      <c r="R16" s="49"/>
+      <c r="S16" s="49"/>
+      <c r="T16" s="49"/>
+      <c r="U16" s="49"/>
+      <c r="V16" s="49"/>
+      <c r="W16" s="49"/>
+      <c r="X16" s="49"/>
+      <c r="Y16" s="49"/>
+      <c r="Z16" s="49"/>
+      <c r="AA16" s="49"/>
+      <c r="AB16" s="49"/>
+      <c r="AC16" s="49"/>
+      <c r="AD16" s="49"/>
+      <c r="AE16" s="49"/>
+      <c r="AF16" s="50"/>
+      <c r="AG16" s="49"/>
+      <c r="AH16" s="49"/>
+      <c r="AI16" s="51"/>
+      <c r="AJ16" s="32"/>
     </row>
     <row r="17" spans="1:37" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="42"/>
-      <c r="B17" s="58" t="s">
+      <c r="A17" s="33"/>
+      <c r="B17" s="47" t="s">
         <v>1352</v>
       </c>
-      <c r="C17" s="59"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="60"/>
-      <c r="L17" s="60"/>
-      <c r="M17" s="60"/>
-      <c r="N17" s="60"/>
-      <c r="O17" s="60"/>
-      <c r="P17" s="60"/>
-      <c r="Q17" s="60"/>
-      <c r="R17" s="60"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="60"/>
-      <c r="U17" s="60"/>
-      <c r="V17" s="60"/>
-      <c r="W17" s="60"/>
-      <c r="X17" s="60"/>
-      <c r="Y17" s="60"/>
-      <c r="Z17" s="60"/>
-      <c r="AA17" s="60"/>
-      <c r="AB17" s="60"/>
-      <c r="AC17" s="60"/>
-      <c r="AD17" s="60"/>
-      <c r="AE17" s="60"/>
-      <c r="AF17" s="61"/>
-      <c r="AG17" s="60"/>
-      <c r="AH17" s="60"/>
-      <c r="AI17" s="62"/>
-      <c r="AJ17" s="41"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="49"/>
+      <c r="L17" s="49"/>
+      <c r="M17" s="49"/>
+      <c r="N17" s="49"/>
+      <c r="O17" s="49"/>
+      <c r="P17" s="49"/>
+      <c r="Q17" s="49"/>
+      <c r="R17" s="49"/>
+      <c r="S17" s="49"/>
+      <c r="T17" s="49"/>
+      <c r="U17" s="49"/>
+      <c r="V17" s="49"/>
+      <c r="W17" s="49"/>
+      <c r="X17" s="49"/>
+      <c r="Y17" s="49"/>
+      <c r="Z17" s="49"/>
+      <c r="AA17" s="49"/>
+      <c r="AB17" s="49"/>
+      <c r="AC17" s="49"/>
+      <c r="AD17" s="49"/>
+      <c r="AE17" s="49"/>
+      <c r="AF17" s="50"/>
+      <c r="AG17" s="49"/>
+      <c r="AH17" s="49"/>
+      <c r="AI17" s="51"/>
+      <c r="AJ17" s="32"/>
     </row>
     <row r="18" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="42"/>
-      <c r="B18" s="55" t="s">
+      <c r="A18" s="33"/>
+      <c r="B18" s="44" t="s">
         <v>1353</v>
       </c>
-      <c r="C18" s="59"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="60"/>
-      <c r="K18" s="60"/>
-      <c r="L18" s="60"/>
-      <c r="M18" s="60"/>
-      <c r="N18" s="60"/>
-      <c r="O18" s="60"/>
-      <c r="P18" s="60"/>
-      <c r="Q18" s="60"/>
-      <c r="R18" s="60"/>
-      <c r="S18" s="60"/>
-      <c r="T18" s="60"/>
-      <c r="U18" s="60"/>
-      <c r="V18" s="60"/>
-      <c r="W18" s="60"/>
-      <c r="X18" s="60"/>
-      <c r="Y18" s="60"/>
-      <c r="Z18" s="60"/>
-      <c r="AA18" s="60"/>
-      <c r="AB18" s="60"/>
-      <c r="AC18" s="60"/>
-      <c r="AD18" s="60"/>
-      <c r="AE18" s="60"/>
-      <c r="AF18" s="61"/>
-      <c r="AG18" s="60"/>
-      <c r="AH18" s="60"/>
-      <c r="AI18" s="62"/>
-      <c r="AJ18" s="41"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="49"/>
+      <c r="M18" s="49"/>
+      <c r="N18" s="49"/>
+      <c r="O18" s="49"/>
+      <c r="P18" s="49"/>
+      <c r="Q18" s="49"/>
+      <c r="R18" s="49"/>
+      <c r="S18" s="49"/>
+      <c r="T18" s="49"/>
+      <c r="U18" s="49"/>
+      <c r="V18" s="49"/>
+      <c r="W18" s="49"/>
+      <c r="X18" s="49"/>
+      <c r="Y18" s="49"/>
+      <c r="Z18" s="49"/>
+      <c r="AA18" s="49"/>
+      <c r="AB18" s="49"/>
+      <c r="AC18" s="49"/>
+      <c r="AD18" s="49"/>
+      <c r="AE18" s="49"/>
+      <c r="AF18" s="50"/>
+      <c r="AG18" s="49"/>
+      <c r="AH18" s="49"/>
+      <c r="AI18" s="51"/>
+      <c r="AJ18" s="32"/>
     </row>
     <row r="19" spans="1:37" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="42"/>
-      <c r="B19" s="55" t="s">
+      <c r="A19" s="33"/>
+      <c r="B19" s="44" t="s">
         <v>1354</v>
       </c>
-      <c r="C19" s="59"/>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="60"/>
-      <c r="L19" s="60"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="60"/>
-      <c r="O19" s="60"/>
-      <c r="P19" s="60"/>
-      <c r="Q19" s="60"/>
-      <c r="R19" s="60"/>
-      <c r="S19" s="60"/>
-      <c r="T19" s="60"/>
-      <c r="U19" s="60"/>
-      <c r="V19" s="60"/>
-      <c r="W19" s="60"/>
-      <c r="X19" s="60"/>
-      <c r="Y19" s="60"/>
-      <c r="Z19" s="60"/>
-      <c r="AA19" s="60"/>
-      <c r="AB19" s="60"/>
-      <c r="AC19" s="60"/>
-      <c r="AD19" s="60"/>
-      <c r="AE19" s="60"/>
-      <c r="AF19" s="61"/>
-      <c r="AG19" s="60"/>
-      <c r="AH19" s="60"/>
-      <c r="AI19" s="62"/>
-      <c r="AJ19" s="41"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="F19" s="72"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="49"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="49"/>
+      <c r="N19" s="49"/>
+      <c r="O19" s="49"/>
+      <c r="P19" s="49"/>
+      <c r="Q19" s="49"/>
+      <c r="R19" s="49"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="49"/>
+      <c r="U19" s="49"/>
+      <c r="V19" s="49"/>
+      <c r="W19" s="49"/>
+      <c r="X19" s="49"/>
+      <c r="Y19" s="49"/>
+      <c r="Z19" s="49"/>
+      <c r="AA19" s="49"/>
+      <c r="AB19" s="49"/>
+      <c r="AC19" s="49"/>
+      <c r="AD19" s="49"/>
+      <c r="AE19" s="49"/>
+      <c r="AF19" s="50"/>
+      <c r="AG19" s="49"/>
+      <c r="AH19" s="49"/>
+      <c r="AI19" s="51"/>
+      <c r="AJ19" s="32"/>
     </row>
     <row r="20" spans="1:37" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="37"/>
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="37"/>
-      <c r="L20" s="37"/>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="37"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="37"/>
-      <c r="S20" s="37"/>
-      <c r="T20" s="37"/>
-      <c r="U20" s="37"/>
-      <c r="V20" s="37"/>
-      <c r="W20" s="37"/>
-      <c r="X20" s="37"/>
-      <c r="Y20" s="37"/>
-      <c r="Z20" s="37"/>
-      <c r="AA20" s="37"/>
-      <c r="AB20" s="37"/>
-      <c r="AC20" s="37"/>
-      <c r="AD20" s="37"/>
-      <c r="AE20" s="37"/>
-      <c r="AF20" s="37"/>
-      <c r="AG20" s="86" t="s">
+      <c r="A20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="28"/>
+      <c r="W20" s="28"/>
+      <c r="X20" s="28"/>
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="28"/>
+      <c r="AA20" s="28"/>
+      <c r="AB20" s="28"/>
+      <c r="AC20" s="28"/>
+      <c r="AD20" s="28"/>
+      <c r="AE20" s="28"/>
+      <c r="AF20" s="28"/>
+      <c r="AG20" s="73" t="s">
         <v>1355</v>
       </c>
-      <c r="AH20" s="86"/>
-      <c r="AI20" s="86"/>
-    </row>
-    <row r="21" spans="1:37" s="45" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="43"/>
-      <c r="B21" s="64" t="s">
+      <c r="AH20" s="73"/>
+      <c r="AI20" s="73"/>
+    </row>
+    <row r="21" spans="1:37" s="36" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="34"/>
+      <c r="B21" s="53" t="s">
         <v>1356</v>
       </c>
-      <c r="C21" s="64" t="s">
+      <c r="C21" s="53" t="s">
         <v>1357</v>
       </c>
-      <c r="D21" s="64" t="s">
+      <c r="D21" s="53" t="s">
         <v>1358</v>
       </c>
-      <c r="E21" s="64" t="s">
+      <c r="E21" s="53" t="s">
         <v>1359</v>
       </c>
-      <c r="F21" s="64" t="s">
+      <c r="F21" s="53" t="s">
         <v>1360</v>
       </c>
-      <c r="G21" s="64" t="s">
+      <c r="G21" s="53" t="s">
         <v>1361</v>
       </c>
-      <c r="H21" s="64" t="s">
+      <c r="H21" s="53" t="s">
         <v>1362</v>
       </c>
-      <c r="I21" s="64" t="s">
+      <c r="I21" s="53" t="s">
         <v>1363</v>
       </c>
-      <c r="J21" s="64" t="s">
+      <c r="J21" s="53" t="s">
         <v>1364</v>
       </c>
-      <c r="K21" s="64" t="s">
+      <c r="K21" s="53" t="s">
         <v>1364</v>
       </c>
-      <c r="L21" s="64" t="s">
+      <c r="L21" s="53" t="s">
         <v>1365</v>
       </c>
-      <c r="M21" s="64" t="s">
+      <c r="M21" s="53" t="s">
         <v>1366</v>
       </c>
-      <c r="N21" s="64" t="s">
+      <c r="N21" s="53" t="s">
         <v>1367</v>
       </c>
-      <c r="O21" s="64" t="s">
+      <c r="O21" s="53" t="s">
         <v>1368</v>
       </c>
-      <c r="P21" s="64" t="s">
+      <c r="P21" s="53" t="s">
         <v>1369</v>
       </c>
-      <c r="Q21" s="64" t="s">
+      <c r="Q21" s="53" t="s">
         <v>1370</v>
       </c>
-      <c r="R21" s="64" t="s">
+      <c r="R21" s="53" t="s">
         <v>1371</v>
       </c>
-      <c r="S21" s="64" t="s">
+      <c r="S21" s="53" t="s">
         <v>1372</v>
       </c>
-      <c r="T21" s="64" t="s">
+      <c r="T21" s="53" t="s">
         <v>1373</v>
       </c>
-      <c r="U21" s="64" t="s">
+      <c r="U21" s="53" t="s">
         <v>1374</v>
       </c>
-      <c r="V21" s="64" t="s">
+      <c r="V21" s="53" t="s">
         <v>1375</v>
       </c>
-      <c r="W21" s="64" t="s">
+      <c r="W21" s="53" t="s">
         <v>1376</v>
       </c>
-      <c r="X21" s="64" t="s">
+      <c r="X21" s="53" t="s">
         <v>1377</v>
       </c>
-      <c r="Y21" s="64" t="s">
+      <c r="Y21" s="53" t="s">
         <v>1378</v>
       </c>
-      <c r="Z21" s="64" t="s">
+      <c r="Z21" s="53" t="s">
         <v>1001</v>
       </c>
-      <c r="AA21" s="64" t="s">
+      <c r="AA21" s="53" t="s">
         <v>1379</v>
       </c>
-      <c r="AB21" s="64" t="s">
+      <c r="AB21" s="53" t="s">
         <v>1380</v>
       </c>
-      <c r="AC21" s="64" t="s">
+      <c r="AC21" s="53" t="s">
         <v>1381</v>
       </c>
-      <c r="AD21" s="64" t="s">
+      <c r="AD21" s="53" t="s">
         <v>1382</v>
       </c>
-      <c r="AE21" s="64" t="s">
+      <c r="AE21" s="53" t="s">
         <v>1383</v>
       </c>
-      <c r="AF21" s="64" t="s">
+      <c r="AF21" s="53" t="s">
         <v>1384</v>
       </c>
-      <c r="AG21" s="66" t="s">
+      <c r="AG21" s="55" t="s">
         <v>1385</v>
       </c>
-      <c r="AH21" s="66" t="s">
+      <c r="AH21" s="55" t="s">
         <v>1386</v>
       </c>
-      <c r="AI21" s="66" t="s">
+      <c r="AI21" s="55" t="s">
         <v>1387</v>
       </c>
-      <c r="AJ21" s="65" t="s">
+      <c r="AJ21" s="54" t="s">
         <v>1388</v>
       </c>
-      <c r="AK21" s="44"/>
-    </row>
-    <row r="22" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="40"/>
-      <c r="B22" s="67">
+      <c r="AK21" s="35"/>
+    </row>
+    <row r="22" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="31"/>
+      <c r="B22" s="56">
         <v>1</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="69" t="str">
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F22,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H22" s="68"/>
-      <c r="I22" s="70"/>
-      <c r="J22" s="68"/>
-      <c r="K22" s="70"/>
-      <c r="L22" s="70"/>
-      <c r="M22" s="70"/>
-      <c r="N22" s="70"/>
-      <c r="O22" s="70"/>
-      <c r="P22" s="70"/>
-      <c r="Q22" s="70"/>
-      <c r="R22" s="70"/>
-      <c r="S22" s="70"/>
-      <c r="T22" s="70"/>
-      <c r="U22" s="70"/>
-      <c r="V22" s="70"/>
-      <c r="W22" s="70"/>
-      <c r="X22" s="70"/>
-      <c r="Y22" s="70"/>
-      <c r="Z22" s="70"/>
-      <c r="AA22" s="70"/>
-      <c r="AB22" s="68" t="s">
+      <c r="H22" s="57"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="59"/>
+      <c r="M22" s="59"/>
+      <c r="N22" s="59"/>
+      <c r="O22" s="59"/>
+      <c r="P22" s="59"/>
+      <c r="Q22" s="59"/>
+      <c r="R22" s="59"/>
+      <c r="S22" s="59"/>
+      <c r="T22" s="59"/>
+      <c r="U22" s="59"/>
+      <c r="V22" s="59"/>
+      <c r="W22" s="59"/>
+      <c r="X22" s="59"/>
+      <c r="Y22" s="59"/>
+      <c r="Z22" s="59"/>
+      <c r="AA22" s="59"/>
+      <c r="AB22" s="57" t="s">
         <v>991</v>
       </c>
-      <c r="AC22" s="68"/>
-      <c r="AD22" s="69" t="str">
+      <c r="AC22" s="57"/>
+      <c r="AD22" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB22,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v xml:space="preserve"> Eduardo Saez </v>
       </c>
-      <c r="AE22" s="68"/>
-      <c r="AF22" s="68"/>
-      <c r="AG22" s="71"/>
-      <c r="AH22" s="68"/>
-      <c r="AI22" s="72"/>
-      <c r="AJ22" s="73" t="str">
+      <c r="AE22" s="57"/>
+      <c r="AF22" s="57"/>
+      <c r="AG22" s="60"/>
+      <c r="AH22" s="57"/>
+      <c r="AI22" s="61"/>
+      <c r="AJ22" s="62" t="str">
         <f>IF(COUNTA(C22,D22,E22,F22,H22,I22,L22,M22,N22,P22,Q22,R22,S22,T22,U22,X22,Y22,Z22,AB22,AC22,AH22)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C22=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D22=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E22=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F22=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G22=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H22=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I22=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L22=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M22=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N22=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P22=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q22=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R22=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S22=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T22=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U22=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X22=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y22=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z22=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB22=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC22=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH22=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C22=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D22=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E22=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F22=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G22=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H22=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I22=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L22=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M22=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N22=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P22=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q22=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R22=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S22=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T22=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U22=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X22=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y22=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z22=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB22=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC22=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH22=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v>⚠️ Faltan: Orden de Inversión, Elemento PEP, Descripción Activo SAP, Clase, Cantidad, Nombre principal AF, Criterio Clas. 3, Criterio Clas. 5, Centro, Emplazamiento, Valor Unitario</v>
       </c>
-      <c r="AK22" s="63"/>
-    </row>
-    <row r="23" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="40"/>
-      <c r="B23" s="67">
+      <c r="AK22" s="52"/>
+    </row>
+    <row r="23" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="31"/>
+      <c r="B23" s="56">
         <v>2</v>
       </c>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="69" t="str">
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F23,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H23" s="68"/>
-      <c r="I23" s="70"/>
-      <c r="J23" s="68"/>
-      <c r="K23" s="70"/>
-      <c r="L23" s="70"/>
-      <c r="M23" s="70"/>
-      <c r="N23" s="70"/>
-      <c r="O23" s="70"/>
-      <c r="P23" s="70"/>
-      <c r="Q23" s="70"/>
-      <c r="R23" s="70"/>
-      <c r="S23" s="70"/>
-      <c r="T23" s="70"/>
-      <c r="U23" s="70"/>
-      <c r="V23" s="70"/>
-      <c r="W23" s="70"/>
-      <c r="X23" s="70"/>
-      <c r="Y23" s="70"/>
-      <c r="Z23" s="70"/>
-      <c r="AA23" s="70"/>
-      <c r="AB23" s="68"/>
-      <c r="AC23" s="68"/>
-      <c r="AD23" s="69" t="str">
+      <c r="H23" s="57"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="59"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="59"/>
+      <c r="O23" s="59"/>
+      <c r="P23" s="59"/>
+      <c r="Q23" s="59"/>
+      <c r="R23" s="59"/>
+      <c r="S23" s="59"/>
+      <c r="T23" s="59"/>
+      <c r="U23" s="59"/>
+      <c r="V23" s="59"/>
+      <c r="W23" s="59"/>
+      <c r="X23" s="59"/>
+      <c r="Y23" s="59"/>
+      <c r="Z23" s="59"/>
+      <c r="AA23" s="59"/>
+      <c r="AB23" s="57"/>
+      <c r="AC23" s="57"/>
+      <c r="AD23" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB23,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE23" s="68"/>
-      <c r="AF23" s="68"/>
-      <c r="AG23" s="71"/>
-      <c r="AH23" s="68"/>
-      <c r="AI23" s="72"/>
-      <c r="AJ23" s="73" t="str">
+      <c r="AE23" s="57"/>
+      <c r="AF23" s="57"/>
+      <c r="AG23" s="60"/>
+      <c r="AH23" s="57"/>
+      <c r="AI23" s="61"/>
+      <c r="AJ23" s="62" t="str">
         <f>IF(COUNTA(C23,D23,E23,F23,H23,I23,L23,M23,N23,P23,Q23,R23,S23,T23,U23,X23,Y23,Z23,AB23,AC23,AH23)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C23=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D23=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E23=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F23=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G23=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H23=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I23=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L23=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M23=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N23=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P23=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q23=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R23=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S23=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T23=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U23=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X23=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y23=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z23=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB23=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC23=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH23=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C23=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D23=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E23=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F23=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G23=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H23=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I23=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L23=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M23=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N23=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P23=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q23=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R23=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S23=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T23=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U23=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X23=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y23=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z23=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB23=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC23=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH23=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK23" s="63"/>
-    </row>
-    <row r="24" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="40"/>
-      <c r="B24" s="67">
-        <v>3</v>
-      </c>
-      <c r="C24" s="68"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="69" t="str">
+      <c r="AK23" s="52"/>
+    </row>
+    <row r="24" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="31"/>
+      <c r="B24" s="56">
+        <v>3</v>
+      </c>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F24,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H24" s="68"/>
-      <c r="I24" s="70"/>
-      <c r="J24" s="68"/>
-      <c r="K24" s="70"/>
-      <c r="L24" s="70"/>
-      <c r="M24" s="70"/>
-      <c r="N24" s="70"/>
-      <c r="O24" s="70"/>
-      <c r="P24" s="70"/>
-      <c r="Q24" s="70"/>
-      <c r="R24" s="70"/>
-      <c r="S24" s="70"/>
-      <c r="T24" s="70"/>
-      <c r="U24" s="70"/>
-      <c r="V24" s="70"/>
-      <c r="W24" s="70"/>
-      <c r="X24" s="70"/>
-      <c r="Y24" s="70"/>
-      <c r="Z24" s="70"/>
-      <c r="AA24" s="70"/>
-      <c r="AB24" s="68"/>
-      <c r="AC24" s="68"/>
-      <c r="AD24" s="69" t="str">
+      <c r="H24" s="57"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="57"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="59"/>
+      <c r="M24" s="59"/>
+      <c r="N24" s="59"/>
+      <c r="O24" s="59"/>
+      <c r="P24" s="59"/>
+      <c r="Q24" s="59"/>
+      <c r="R24" s="59"/>
+      <c r="S24" s="59"/>
+      <c r="T24" s="59"/>
+      <c r="U24" s="59"/>
+      <c r="V24" s="59"/>
+      <c r="W24" s="59"/>
+      <c r="X24" s="59"/>
+      <c r="Y24" s="59"/>
+      <c r="Z24" s="59"/>
+      <c r="AA24" s="59"/>
+      <c r="AB24" s="57"/>
+      <c r="AC24" s="57"/>
+      <c r="AD24" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB24,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE24" s="68"/>
-      <c r="AF24" s="68"/>
-      <c r="AG24" s="71"/>
-      <c r="AH24" s="68"/>
-      <c r="AI24" s="72"/>
-      <c r="AJ24" s="73" t="str">
+      <c r="AE24" s="57"/>
+      <c r="AF24" s="57"/>
+      <c r="AG24" s="60"/>
+      <c r="AH24" s="57"/>
+      <c r="AI24" s="61"/>
+      <c r="AJ24" s="62" t="str">
         <f>IF(COUNTA(C24,D24,E24,F24,H24,I24,L24,M24,N24,P24,Q24,R24,S24,T24,U24,X24,Y24,Z24,AB24,AC24,AH24)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C24=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D24=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E24=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F24=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G24=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H24=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I24=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L24=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M24=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N24=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P24=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q24=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R24=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S24=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T24=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U24=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X24=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y24=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z24=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB24=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC24=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH24=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C24=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D24=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E24=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F24=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G24=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H24=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I24=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L24=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M24=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N24=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P24=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q24=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R24=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S24=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T24=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U24=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X24=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y24=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z24=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB24=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC24=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH24=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK24" s="63"/>
-    </row>
-    <row r="25" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="40"/>
-      <c r="B25" s="67">
+      <c r="AK24" s="52"/>
+    </row>
+    <row r="25" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="31"/>
+      <c r="B25" s="56">
         <v>4</v>
       </c>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="69" t="str">
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F25,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H25" s="68"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="68"/>
-      <c r="K25" s="70"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="70"/>
-      <c r="N25" s="70"/>
-      <c r="O25" s="70"/>
-      <c r="P25" s="70"/>
-      <c r="Q25" s="70"/>
-      <c r="R25" s="70"/>
-      <c r="S25" s="70"/>
-      <c r="T25" s="70"/>
-      <c r="U25" s="70"/>
-      <c r="V25" s="70"/>
-      <c r="W25" s="70"/>
-      <c r="X25" s="70"/>
-      <c r="Y25" s="70"/>
-      <c r="Z25" s="70"/>
-      <c r="AA25" s="70"/>
-      <c r="AB25" s="68"/>
-      <c r="AC25" s="68"/>
-      <c r="AD25" s="69" t="str">
+      <c r="H25" s="57"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="59"/>
+      <c r="O25" s="59"/>
+      <c r="P25" s="59"/>
+      <c r="Q25" s="59"/>
+      <c r="R25" s="59"/>
+      <c r="S25" s="59"/>
+      <c r="T25" s="59"/>
+      <c r="U25" s="59"/>
+      <c r="V25" s="59"/>
+      <c r="W25" s="59"/>
+      <c r="X25" s="59"/>
+      <c r="Y25" s="59"/>
+      <c r="Z25" s="59"/>
+      <c r="AA25" s="59"/>
+      <c r="AB25" s="57"/>
+      <c r="AC25" s="57"/>
+      <c r="AD25" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB25,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE25" s="68"/>
-      <c r="AF25" s="68"/>
-      <c r="AG25" s="71"/>
-      <c r="AH25" s="68"/>
-      <c r="AI25" s="72"/>
-      <c r="AJ25" s="73" t="str">
+      <c r="AE25" s="57"/>
+      <c r="AF25" s="57"/>
+      <c r="AG25" s="60"/>
+      <c r="AH25" s="57"/>
+      <c r="AI25" s="61"/>
+      <c r="AJ25" s="62" t="str">
         <f>IF(COUNTA(C25,D25,E25,F25,H25,I25,L25,M25,N25,P25,Q25,R25,S25,T25,U25,X25,Y25,Z25,AB25,AC25,AH25)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C25=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D25=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E25=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F25=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G25=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H25=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I25=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L25=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M25=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N25=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P25=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q25=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R25=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S25=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T25=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U25=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X25=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y25=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z25=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB25=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC25=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH25=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C25=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D25=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E25=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F25=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G25=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H25=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I25=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L25=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M25=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N25=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P25=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q25=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R25=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S25=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T25=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U25=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X25=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y25=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z25=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB25=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC25=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH25=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK25" s="63"/>
-    </row>
-    <row r="26" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="40"/>
-      <c r="B26" s="67">
+      <c r="AK25" s="52"/>
+    </row>
+    <row r="26" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="31"/>
+      <c r="B26" s="56">
         <v>5</v>
       </c>
-      <c r="C26" s="68"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="69" t="str">
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F26,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H26" s="68"/>
-      <c r="I26" s="70"/>
-      <c r="J26" s="68"/>
-      <c r="K26" s="70"/>
-      <c r="L26" s="70"/>
-      <c r="M26" s="70"/>
-      <c r="N26" s="70"/>
-      <c r="O26" s="70"/>
-      <c r="P26" s="70"/>
-      <c r="Q26" s="70"/>
-      <c r="R26" s="70"/>
-      <c r="S26" s="70"/>
-      <c r="T26" s="70"/>
-      <c r="U26" s="70"/>
-      <c r="V26" s="70"/>
-      <c r="W26" s="70"/>
-      <c r="X26" s="70"/>
-      <c r="Y26" s="70"/>
-      <c r="Z26" s="70"/>
-      <c r="AA26" s="70"/>
-      <c r="AB26" s="68"/>
-      <c r="AC26" s="68"/>
-      <c r="AD26" s="69" t="str">
+      <c r="H26" s="57"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="59"/>
+      <c r="N26" s="59"/>
+      <c r="O26" s="59"/>
+      <c r="P26" s="59"/>
+      <c r="Q26" s="59"/>
+      <c r="R26" s="59"/>
+      <c r="S26" s="59"/>
+      <c r="T26" s="59"/>
+      <c r="U26" s="59"/>
+      <c r="V26" s="59"/>
+      <c r="W26" s="59"/>
+      <c r="X26" s="59"/>
+      <c r="Y26" s="59"/>
+      <c r="Z26" s="59"/>
+      <c r="AA26" s="59"/>
+      <c r="AB26" s="57"/>
+      <c r="AC26" s="57"/>
+      <c r="AD26" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB26,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE26" s="68"/>
-      <c r="AF26" s="68"/>
-      <c r="AG26" s="71"/>
-      <c r="AH26" s="68"/>
-      <c r="AI26" s="72"/>
-      <c r="AJ26" s="73" t="str">
+      <c r="AE26" s="57"/>
+      <c r="AF26" s="57"/>
+      <c r="AG26" s="60"/>
+      <c r="AH26" s="57"/>
+      <c r="AI26" s="61"/>
+      <c r="AJ26" s="62" t="str">
         <f>IF(COUNTA(C26,D26,E26,F26,H26,I26,L26,M26,N26,P26,Q26,R26,S26,T26,U26,X26,Y26,Z26,AB26,AC26,AH26)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C26=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D26=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E26=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F26=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G26=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H26=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I26=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L26=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M26=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N26=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P26=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q26=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R26=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S26=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T26=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U26=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X26=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y26=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z26=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB26=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC26=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH26=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C26=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D26=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E26=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F26=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G26=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H26=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I26=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L26=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M26=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N26=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P26=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q26=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R26=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S26=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T26=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U26=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X26=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y26=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z26=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB26=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC26=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH26=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK26" s="63"/>
-    </row>
-    <row r="27" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="40"/>
-      <c r="B27" s="67">
+      <c r="AK26" s="52"/>
+    </row>
+    <row r="27" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="31"/>
+      <c r="B27" s="56">
         <v>6</v>
       </c>
-      <c r="C27" s="68"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="69" t="str">
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F27,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H27" s="68"/>
-      <c r="I27" s="70"/>
-      <c r="J27" s="68"/>
-      <c r="K27" s="70"/>
-      <c r="L27" s="70"/>
-      <c r="M27" s="70"/>
-      <c r="N27" s="70"/>
-      <c r="O27" s="70"/>
-      <c r="P27" s="70"/>
-      <c r="Q27" s="70"/>
-      <c r="R27" s="70"/>
-      <c r="S27" s="70"/>
-      <c r="T27" s="70"/>
-      <c r="U27" s="70"/>
-      <c r="V27" s="70"/>
-      <c r="W27" s="70"/>
-      <c r="X27" s="70"/>
-      <c r="Y27" s="70"/>
-      <c r="Z27" s="70"/>
-      <c r="AA27" s="70"/>
-      <c r="AB27" s="68"/>
-      <c r="AC27" s="68"/>
-      <c r="AD27" s="69" t="str">
+      <c r="H27" s="57"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="57"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="59"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="59"/>
+      <c r="O27" s="59"/>
+      <c r="P27" s="59"/>
+      <c r="Q27" s="59"/>
+      <c r="R27" s="59"/>
+      <c r="S27" s="59"/>
+      <c r="T27" s="59"/>
+      <c r="U27" s="59"/>
+      <c r="V27" s="59"/>
+      <c r="W27" s="59"/>
+      <c r="X27" s="59"/>
+      <c r="Y27" s="59"/>
+      <c r="Z27" s="59"/>
+      <c r="AA27" s="59"/>
+      <c r="AB27" s="57"/>
+      <c r="AC27" s="57"/>
+      <c r="AD27" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB27,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE27" s="68"/>
-      <c r="AF27" s="68"/>
-      <c r="AG27" s="71"/>
-      <c r="AH27" s="68"/>
-      <c r="AI27" s="72"/>
-      <c r="AJ27" s="73" t="str">
+      <c r="AE27" s="57"/>
+      <c r="AF27" s="57"/>
+      <c r="AG27" s="60"/>
+      <c r="AH27" s="57"/>
+      <c r="AI27" s="61"/>
+      <c r="AJ27" s="62" t="str">
         <f>IF(COUNTA(C27,D27,E27,F27,H27,I27,L27,M27,N27,P27,Q27,R27,S27,T27,U27,X27,Y27,Z27,AB27,AC27,AH27)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C27=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D27=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E27=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F27=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G27=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H27=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I27=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L27=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M27=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N27=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P27=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q27=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R27=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S27=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T27=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U27=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X27=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y27=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z27=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB27=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC27=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH27=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C27=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D27=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E27=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F27=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G27=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H27=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I27=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L27=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M27=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N27=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P27=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q27=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R27=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S27=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T27=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U27=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X27=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y27=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z27=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB27=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC27=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH27=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK27" s="63"/>
-    </row>
-    <row r="28" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="40"/>
-      <c r="B28" s="67">
+      <c r="AK27" s="52"/>
+    </row>
+    <row r="28" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="31"/>
+      <c r="B28" s="56">
         <v>7</v>
       </c>
-      <c r="C28" s="68"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="69" t="str">
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F28,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H28" s="68"/>
-      <c r="I28" s="70"/>
-      <c r="J28" s="68"/>
-      <c r="K28" s="70"/>
-      <c r="L28" s="70"/>
-      <c r="M28" s="70"/>
-      <c r="N28" s="70"/>
-      <c r="O28" s="70"/>
-      <c r="P28" s="70"/>
-      <c r="Q28" s="70"/>
-      <c r="R28" s="70"/>
-      <c r="S28" s="70"/>
-      <c r="T28" s="70"/>
-      <c r="U28" s="70"/>
-      <c r="V28" s="70"/>
-      <c r="W28" s="70"/>
-      <c r="X28" s="70"/>
-      <c r="Y28" s="70"/>
-      <c r="Z28" s="70"/>
-      <c r="AA28" s="70"/>
-      <c r="AB28" s="68"/>
-      <c r="AC28" s="68"/>
-      <c r="AD28" s="69" t="str">
+      <c r="H28" s="57"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="57"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="59"/>
+      <c r="M28" s="59"/>
+      <c r="N28" s="59"/>
+      <c r="O28" s="59"/>
+      <c r="P28" s="59"/>
+      <c r="Q28" s="59"/>
+      <c r="R28" s="59"/>
+      <c r="S28" s="59"/>
+      <c r="T28" s="59"/>
+      <c r="U28" s="59"/>
+      <c r="V28" s="59"/>
+      <c r="W28" s="59"/>
+      <c r="X28" s="59"/>
+      <c r="Y28" s="59"/>
+      <c r="Z28" s="59"/>
+      <c r="AA28" s="59"/>
+      <c r="AB28" s="57"/>
+      <c r="AC28" s="57"/>
+      <c r="AD28" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB28,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE28" s="68"/>
-      <c r="AF28" s="68"/>
-      <c r="AG28" s="71"/>
-      <c r="AH28" s="68"/>
-      <c r="AI28" s="72"/>
-      <c r="AJ28" s="73" t="str">
+      <c r="AE28" s="57"/>
+      <c r="AF28" s="57"/>
+      <c r="AG28" s="60"/>
+      <c r="AH28" s="57"/>
+      <c r="AI28" s="61"/>
+      <c r="AJ28" s="62" t="str">
         <f>IF(COUNTA(C28,D28,E28,F28,H28,I28,L28,M28,N28,P28,Q28,R28,S28,T28,U28,X28,Y28,Z28,AB28,AC28,AH28)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C28=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D28=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E28=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F28=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G28=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H28=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I28=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L28=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M28=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N28=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P28=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q28=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R28=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S28=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T28=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U28=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X28=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y28=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z28=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB28=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC28=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH28=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C28=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D28=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E28=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F28=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G28=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H28=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I28=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L28=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M28=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N28=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P28=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q28=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R28=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S28=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T28=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U28=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X28=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y28=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z28=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB28=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC28=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH28=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK28" s="63"/>
-    </row>
-    <row r="29" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="40"/>
-      <c r="B29" s="67">
+      <c r="AK28" s="52"/>
+    </row>
+    <row r="29" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="31"/>
+      <c r="B29" s="56">
         <v>8</v>
       </c>
-      <c r="C29" s="68"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="69" t="str">
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F29,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H29" s="68"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="68"/>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="70"/>
-      <c r="O29" s="70"/>
-      <c r="P29" s="70"/>
-      <c r="Q29" s="70"/>
-      <c r="R29" s="70"/>
-      <c r="S29" s="70"/>
-      <c r="T29" s="70"/>
-      <c r="U29" s="70"/>
-      <c r="V29" s="70"/>
-      <c r="W29" s="70"/>
-      <c r="X29" s="70"/>
-      <c r="Y29" s="70"/>
-      <c r="Z29" s="70"/>
-      <c r="AA29" s="70"/>
-      <c r="AB29" s="68"/>
-      <c r="AC29" s="68"/>
-      <c r="AD29" s="69" t="str">
+      <c r="H29" s="57"/>
+      <c r="I29" s="59"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="59"/>
+      <c r="M29" s="59"/>
+      <c r="N29" s="59"/>
+      <c r="O29" s="59"/>
+      <c r="P29" s="59"/>
+      <c r="Q29" s="59"/>
+      <c r="R29" s="59"/>
+      <c r="S29" s="59"/>
+      <c r="T29" s="59"/>
+      <c r="U29" s="59"/>
+      <c r="V29" s="59"/>
+      <c r="W29" s="59"/>
+      <c r="X29" s="59"/>
+      <c r="Y29" s="59"/>
+      <c r="Z29" s="59"/>
+      <c r="AA29" s="59"/>
+      <c r="AB29" s="57"/>
+      <c r="AC29" s="57"/>
+      <c r="AD29" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB29,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE29" s="68"/>
-      <c r="AF29" s="68"/>
-      <c r="AG29" s="71"/>
-      <c r="AH29" s="68"/>
-      <c r="AI29" s="72"/>
-      <c r="AJ29" s="73" t="str">
+      <c r="AE29" s="57"/>
+      <c r="AF29" s="57"/>
+      <c r="AG29" s="60"/>
+      <c r="AH29" s="57"/>
+      <c r="AI29" s="61"/>
+      <c r="AJ29" s="62" t="str">
         <f>IF(COUNTA(C29,D29,E29,F29,H29,I29,L29,M29,N29,P29,Q29,R29,S29,T29,U29,X29,Y29,Z29,AB29,AC29,AH29)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C29=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D29=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E29=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F29=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G29=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H29=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I29=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L29=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M29=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N29=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P29=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q29=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R29=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S29=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T29=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U29=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X29=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y29=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z29=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB29=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC29=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH29=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C29=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D29=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E29=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F29=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G29=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H29=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I29=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L29=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M29=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N29=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P29=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q29=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R29=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S29=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T29=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U29=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X29=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y29=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z29=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB29=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC29=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH29=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK29" s="63"/>
-    </row>
-    <row r="30" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="40"/>
-      <c r="B30" s="67">
+      <c r="AK29" s="52"/>
+    </row>
+    <row r="30" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="31"/>
+      <c r="B30" s="56">
         <v>9</v>
       </c>
-      <c r="C30" s="68"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="69" t="str">
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F30,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H30" s="68"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="68"/>
-      <c r="K30" s="70"/>
-      <c r="L30" s="70"/>
-      <c r="M30" s="70"/>
-      <c r="N30" s="70"/>
-      <c r="O30" s="70"/>
-      <c r="P30" s="70"/>
-      <c r="Q30" s="70"/>
-      <c r="R30" s="70"/>
-      <c r="S30" s="70"/>
-      <c r="T30" s="70"/>
-      <c r="U30" s="70"/>
-      <c r="V30" s="70"/>
-      <c r="W30" s="70"/>
-      <c r="X30" s="70"/>
-      <c r="Y30" s="70"/>
-      <c r="Z30" s="70"/>
-      <c r="AA30" s="70"/>
-      <c r="AB30" s="68"/>
-      <c r="AC30" s="68"/>
-      <c r="AD30" s="69" t="str">
+      <c r="H30" s="57"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="59"/>
+      <c r="M30" s="59"/>
+      <c r="N30" s="59"/>
+      <c r="O30" s="59"/>
+      <c r="P30" s="59"/>
+      <c r="Q30" s="59"/>
+      <c r="R30" s="59"/>
+      <c r="S30" s="59"/>
+      <c r="T30" s="59"/>
+      <c r="U30" s="59"/>
+      <c r="V30" s="59"/>
+      <c r="W30" s="59"/>
+      <c r="X30" s="59"/>
+      <c r="Y30" s="59"/>
+      <c r="Z30" s="59"/>
+      <c r="AA30" s="59"/>
+      <c r="AB30" s="57"/>
+      <c r="AC30" s="57"/>
+      <c r="AD30" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB30,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE30" s="68"/>
-      <c r="AF30" s="68"/>
-      <c r="AG30" s="71"/>
-      <c r="AH30" s="68"/>
-      <c r="AI30" s="72"/>
-      <c r="AJ30" s="73" t="str">
+      <c r="AE30" s="57"/>
+      <c r="AF30" s="57"/>
+      <c r="AG30" s="60"/>
+      <c r="AH30" s="57"/>
+      <c r="AI30" s="61"/>
+      <c r="AJ30" s="62" t="str">
         <f>IF(COUNTA(C30,D30,E30,F30,H30,I30,L30,M30,N30,P30,Q30,R30,S30,T30,U30,X30,Y30,Z30,AB30,AC30,AH30)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C30=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D30=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E30=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F30=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G30=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H30=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I30=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L30=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M30=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N30=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P30=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q30=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R30=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S30=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T30=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U30=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X30=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y30=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z30=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB30=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC30=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH30=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C30=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D30=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E30=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F30=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G30=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H30=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I30=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L30=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M30=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N30=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P30=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q30=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R30=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S30=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T30=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U30=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X30=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y30=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z30=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB30=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC30=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH30=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK30" s="63"/>
-    </row>
-    <row r="31" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="40"/>
-      <c r="B31" s="67">
+      <c r="AK30" s="52"/>
+    </row>
+    <row r="31" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="31"/>
+      <c r="B31" s="56">
         <v>10</v>
       </c>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="69" t="str">
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F31,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H31" s="68"/>
-      <c r="I31" s="70"/>
-      <c r="J31" s="68"/>
-      <c r="K31" s="70"/>
-      <c r="L31" s="70"/>
-      <c r="M31" s="70"/>
-      <c r="N31" s="70"/>
-      <c r="O31" s="70"/>
-      <c r="P31" s="70"/>
-      <c r="Q31" s="70"/>
-      <c r="R31" s="70"/>
-      <c r="S31" s="70"/>
-      <c r="T31" s="70"/>
-      <c r="U31" s="70"/>
-      <c r="V31" s="70"/>
-      <c r="W31" s="70"/>
-      <c r="X31" s="70"/>
-      <c r="Y31" s="70"/>
-      <c r="Z31" s="70"/>
-      <c r="AA31" s="70"/>
-      <c r="AB31" s="68"/>
-      <c r="AC31" s="68"/>
-      <c r="AD31" s="69" t="str">
+      <c r="H31" s="57"/>
+      <c r="I31" s="59"/>
+      <c r="J31" s="57"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="59"/>
+      <c r="M31" s="59"/>
+      <c r="N31" s="59"/>
+      <c r="O31" s="59"/>
+      <c r="P31" s="59"/>
+      <c r="Q31" s="59"/>
+      <c r="R31" s="59"/>
+      <c r="S31" s="59"/>
+      <c r="T31" s="59"/>
+      <c r="U31" s="59"/>
+      <c r="V31" s="59"/>
+      <c r="W31" s="59"/>
+      <c r="X31" s="59"/>
+      <c r="Y31" s="59"/>
+      <c r="Z31" s="59"/>
+      <c r="AA31" s="59"/>
+      <c r="AB31" s="57"/>
+      <c r="AC31" s="57"/>
+      <c r="AD31" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB31,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE31" s="68"/>
-      <c r="AF31" s="68"/>
-      <c r="AG31" s="71"/>
-      <c r="AH31" s="68"/>
-      <c r="AI31" s="72"/>
-      <c r="AJ31" s="73" t="str">
+      <c r="AE31" s="57"/>
+      <c r="AF31" s="57"/>
+      <c r="AG31" s="60"/>
+      <c r="AH31" s="57"/>
+      <c r="AI31" s="61"/>
+      <c r="AJ31" s="62" t="str">
         <f>IF(COUNTA(C31,D31,E31,F31,H31,I31,L31,M31,N31,P31,Q31,R31,S31,T31,U31,X31,Y31,Z31,AB31,AC31,AH31)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C31=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D31=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E31=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F31=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G31=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H31=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I31=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L31=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M31=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N31=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P31=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q31=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R31=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S31=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T31=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U31=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X31=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y31=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z31=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB31=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC31=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH31=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C31=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D31=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E31=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F31=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G31=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H31=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I31=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L31=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M31=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N31=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P31=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q31=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R31=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S31=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T31=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U31=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X31=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y31=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z31=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB31=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC31=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH31=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK31" s="63"/>
-    </row>
-    <row r="32" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="40"/>
-      <c r="B32" s="67">
+      <c r="AK31" s="52"/>
+    </row>
+    <row r="32" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="31"/>
+      <c r="B32" s="56">
         <v>11</v>
       </c>
-      <c r="C32" s="68"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="68"/>
-      <c r="F32" s="68"/>
-      <c r="G32" s="69" t="str">
+      <c r="C32" s="57"/>
+      <c r="D32" s="57"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F32,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H32" s="68"/>
-      <c r="I32" s="70"/>
-      <c r="J32" s="68"/>
-      <c r="K32" s="70"/>
-      <c r="L32" s="70"/>
-      <c r="M32" s="70"/>
-      <c r="N32" s="70"/>
-      <c r="O32" s="70"/>
-      <c r="P32" s="70"/>
-      <c r="Q32" s="70"/>
-      <c r="R32" s="70"/>
-      <c r="S32" s="70"/>
-      <c r="T32" s="70"/>
-      <c r="U32" s="70"/>
-      <c r="V32" s="70"/>
-      <c r="W32" s="70"/>
-      <c r="X32" s="70"/>
-      <c r="Y32" s="70"/>
-      <c r="Z32" s="70"/>
-      <c r="AA32" s="70"/>
-      <c r="AB32" s="68"/>
-      <c r="AC32" s="68"/>
-      <c r="AD32" s="69" t="str">
+      <c r="H32" s="57"/>
+      <c r="I32" s="59"/>
+      <c r="J32" s="57"/>
+      <c r="K32" s="59"/>
+      <c r="L32" s="59"/>
+      <c r="M32" s="59"/>
+      <c r="N32" s="59"/>
+      <c r="O32" s="59"/>
+      <c r="P32" s="59"/>
+      <c r="Q32" s="59"/>
+      <c r="R32" s="59"/>
+      <c r="S32" s="59"/>
+      <c r="T32" s="59"/>
+      <c r="U32" s="59"/>
+      <c r="V32" s="59"/>
+      <c r="W32" s="59"/>
+      <c r="X32" s="59"/>
+      <c r="Y32" s="59"/>
+      <c r="Z32" s="59"/>
+      <c r="AA32" s="59"/>
+      <c r="AB32" s="57"/>
+      <c r="AC32" s="57"/>
+      <c r="AD32" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB32,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE32" s="68"/>
-      <c r="AF32" s="68"/>
-      <c r="AG32" s="71"/>
-      <c r="AH32" s="68"/>
-      <c r="AI32" s="72"/>
-      <c r="AJ32" s="73" t="str">
+      <c r="AE32" s="57"/>
+      <c r="AF32" s="57"/>
+      <c r="AG32" s="60"/>
+      <c r="AH32" s="57"/>
+      <c r="AI32" s="61"/>
+      <c r="AJ32" s="62" t="str">
         <f>IF(COUNTA(C32,D32,E32,F32,H32,I32,L32,M32,N32,P32,Q32,R32,S32,T32,U32,X32,Y32,Z32,AB32,AC32,AH32)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C32=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D32=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E32=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F32=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G32=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H32=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I32=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L32=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M32=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N32=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P32=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q32=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R32=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S32=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T32=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U32=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X32=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y32=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z32=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB32=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC32=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH32=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C32=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D32=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E32=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F32=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G32=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H32=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I32=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L32=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M32=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N32=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P32=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q32=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R32=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S32=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T32=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U32=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X32=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y32=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z32=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB32=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC32=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH32=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK32" s="63"/>
-    </row>
-    <row r="33" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="40"/>
-      <c r="B33" s="67">
+      <c r="AK32" s="52"/>
+    </row>
+    <row r="33" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="31"/>
+      <c r="B33" s="56">
         <v>12</v>
       </c>
-      <c r="C33" s="68"/>
-      <c r="D33" s="68"/>
-      <c r="E33" s="68"/>
-      <c r="F33" s="68"/>
-      <c r="G33" s="69" t="str">
+      <c r="C33" s="57"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F33,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H33" s="68"/>
-      <c r="I33" s="70"/>
-      <c r="J33" s="68"/>
-      <c r="K33" s="70"/>
-      <c r="L33" s="70"/>
-      <c r="M33" s="70"/>
-      <c r="N33" s="70"/>
-      <c r="O33" s="70"/>
-      <c r="P33" s="70"/>
-      <c r="Q33" s="70"/>
-      <c r="R33" s="70"/>
-      <c r="S33" s="70"/>
-      <c r="T33" s="70"/>
-      <c r="U33" s="70"/>
-      <c r="V33" s="70"/>
-      <c r="W33" s="70"/>
-      <c r="X33" s="70"/>
-      <c r="Y33" s="70"/>
-      <c r="Z33" s="70"/>
-      <c r="AA33" s="70"/>
-      <c r="AB33" s="68"/>
-      <c r="AC33" s="68"/>
-      <c r="AD33" s="69" t="str">
+      <c r="H33" s="57"/>
+      <c r="I33" s="59"/>
+      <c r="J33" s="57"/>
+      <c r="K33" s="59"/>
+      <c r="L33" s="59"/>
+      <c r="M33" s="59"/>
+      <c r="N33" s="59"/>
+      <c r="O33" s="59"/>
+      <c r="P33" s="59"/>
+      <c r="Q33" s="59"/>
+      <c r="R33" s="59"/>
+      <c r="S33" s="59"/>
+      <c r="T33" s="59"/>
+      <c r="U33" s="59"/>
+      <c r="V33" s="59"/>
+      <c r="W33" s="59"/>
+      <c r="X33" s="59"/>
+      <c r="Y33" s="59"/>
+      <c r="Z33" s="59"/>
+      <c r="AA33" s="59"/>
+      <c r="AB33" s="57"/>
+      <c r="AC33" s="57"/>
+      <c r="AD33" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB33,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE33" s="68"/>
-      <c r="AF33" s="68"/>
-      <c r="AG33" s="71"/>
-      <c r="AH33" s="68"/>
-      <c r="AI33" s="72"/>
-      <c r="AJ33" s="73" t="str">
+      <c r="AE33" s="57"/>
+      <c r="AF33" s="57"/>
+      <c r="AG33" s="60"/>
+      <c r="AH33" s="57"/>
+      <c r="AI33" s="61"/>
+      <c r="AJ33" s="62" t="str">
         <f>IF(COUNTA(C33,D33,E33,F33,H33,I33,L33,M33,N33,P33,Q33,R33,S33,T33,U33,X33,Y33,Z33,AB33,AC33,AH33)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C33=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D33=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E33=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F33=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G33=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H33=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I33=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L33=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M33=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N33=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P33=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q33=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R33=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S33=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T33=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U33=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X33=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y33=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z33=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB33=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC33=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH33=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C33=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D33=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E33=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F33=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G33=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H33=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I33=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L33=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M33=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N33=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P33=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q33=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R33=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S33=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T33=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U33=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X33=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y33=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z33=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB33=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC33=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH33=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK33" s="63"/>
-    </row>
-    <row r="34" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A34" s="40"/>
-      <c r="B34" s="67">
+      <c r="AK33" s="52"/>
+    </row>
+    <row r="34" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="31"/>
+      <c r="B34" s="56">
         <v>13</v>
       </c>
-      <c r="C34" s="68"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="68"/>
-      <c r="G34" s="69" t="str">
+      <c r="C34" s="57"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F34,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H34" s="68"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="68"/>
-      <c r="K34" s="70"/>
-      <c r="L34" s="70"/>
-      <c r="M34" s="70"/>
-      <c r="N34" s="70"/>
-      <c r="O34" s="70"/>
-      <c r="P34" s="70"/>
-      <c r="Q34" s="70"/>
-      <c r="R34" s="70"/>
-      <c r="S34" s="70"/>
-      <c r="T34" s="70"/>
-      <c r="U34" s="70"/>
-      <c r="V34" s="70"/>
-      <c r="W34" s="70"/>
-      <c r="X34" s="70"/>
-      <c r="Y34" s="70"/>
-      <c r="Z34" s="70"/>
-      <c r="AA34" s="70"/>
-      <c r="AB34" s="68"/>
-      <c r="AC34" s="68"/>
-      <c r="AD34" s="69" t="str">
+      <c r="H34" s="57"/>
+      <c r="I34" s="59"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="59"/>
+      <c r="L34" s="59"/>
+      <c r="M34" s="59"/>
+      <c r="N34" s="59"/>
+      <c r="O34" s="59"/>
+      <c r="P34" s="59"/>
+      <c r="Q34" s="59"/>
+      <c r="R34" s="59"/>
+      <c r="S34" s="59"/>
+      <c r="T34" s="59"/>
+      <c r="U34" s="59"/>
+      <c r="V34" s="59"/>
+      <c r="W34" s="59"/>
+      <c r="X34" s="59"/>
+      <c r="Y34" s="59"/>
+      <c r="Z34" s="59"/>
+      <c r="AA34" s="59"/>
+      <c r="AB34" s="57"/>
+      <c r="AC34" s="57"/>
+      <c r="AD34" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB34,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE34" s="68"/>
-      <c r="AF34" s="68"/>
-      <c r="AG34" s="71"/>
-      <c r="AH34" s="68"/>
-      <c r="AI34" s="72"/>
-      <c r="AJ34" s="73" t="str">
+      <c r="AE34" s="57"/>
+      <c r="AF34" s="57"/>
+      <c r="AG34" s="60"/>
+      <c r="AH34" s="57"/>
+      <c r="AI34" s="61"/>
+      <c r="AJ34" s="62" t="str">
         <f>IF(COUNTA(C34,D34,E34,F34,H34,I34,L34,M34,N34,P34,Q34,R34,S34,T34,U34,X34,Y34,Z34,AB34,AC34,AH34)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C34=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D34=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E34=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F34=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G34=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H34=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I34=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L34=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M34=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N34=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P34=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q34=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R34=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S34=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T34=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U34=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X34=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y34=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z34=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB34=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC34=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH34=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C34=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D34=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E34=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F34=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G34=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H34=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I34=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L34=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M34=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N34=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P34=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q34=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R34=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S34=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T34=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U34=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X34=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y34=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z34=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB34=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC34=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH34=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK34" s="63"/>
-    </row>
-    <row r="35" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="40"/>
-      <c r="B35" s="67">
+      <c r="AK34" s="52"/>
+    </row>
+    <row r="35" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="31"/>
+      <c r="B35" s="56">
         <v>14</v>
       </c>
-      <c r="C35" s="68"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="69" t="str">
+      <c r="C35" s="57"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F35,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H35" s="68"/>
-      <c r="I35" s="70"/>
-      <c r="J35" s="68"/>
-      <c r="K35" s="70"/>
-      <c r="L35" s="70"/>
-      <c r="M35" s="70"/>
-      <c r="N35" s="70"/>
-      <c r="O35" s="70"/>
-      <c r="P35" s="70"/>
-      <c r="Q35" s="70"/>
-      <c r="R35" s="70"/>
-      <c r="S35" s="70"/>
-      <c r="T35" s="70"/>
-      <c r="U35" s="70"/>
-      <c r="V35" s="70"/>
-      <c r="W35" s="70"/>
-      <c r="X35" s="70"/>
-      <c r="Y35" s="70"/>
-      <c r="Z35" s="70"/>
-      <c r="AA35" s="70"/>
-      <c r="AB35" s="68"/>
-      <c r="AC35" s="68"/>
-      <c r="AD35" s="69" t="str">
+      <c r="H35" s="57"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="57"/>
+      <c r="K35" s="59"/>
+      <c r="L35" s="59"/>
+      <c r="M35" s="59"/>
+      <c r="N35" s="59"/>
+      <c r="O35" s="59"/>
+      <c r="P35" s="59"/>
+      <c r="Q35" s="59"/>
+      <c r="R35" s="59"/>
+      <c r="S35" s="59"/>
+      <c r="T35" s="59"/>
+      <c r="U35" s="59"/>
+      <c r="V35" s="59"/>
+      <c r="W35" s="59"/>
+      <c r="X35" s="59"/>
+      <c r="Y35" s="59"/>
+      <c r="Z35" s="59"/>
+      <c r="AA35" s="59"/>
+      <c r="AB35" s="57"/>
+      <c r="AC35" s="57"/>
+      <c r="AD35" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB35,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE35" s="68"/>
-      <c r="AF35" s="68"/>
-      <c r="AG35" s="71"/>
-      <c r="AH35" s="68"/>
-      <c r="AI35" s="72"/>
-      <c r="AJ35" s="73" t="str">
+      <c r="AE35" s="57"/>
+      <c r="AF35" s="57"/>
+      <c r="AG35" s="60"/>
+      <c r="AH35" s="57"/>
+      <c r="AI35" s="61"/>
+      <c r="AJ35" s="62" t="str">
         <f>IF(COUNTA(C35,D35,E35,F35,H35,I35,L35,M35,N35,P35,Q35,R35,S35,T35,U35,X35,Y35,Z35,AB35,AC35,AH35)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C35=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D35=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E35=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F35=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G35=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H35=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I35=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L35=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M35=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N35=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P35=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q35=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R35=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S35=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T35=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U35=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X35=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y35=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z35=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB35=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC35=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH35=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C35=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D35=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E35=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F35=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G35=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H35=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I35=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L35=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M35=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N35=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P35=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q35=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R35=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S35=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T35=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U35=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X35=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y35=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z35=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB35=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC35=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH35=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK35" s="63"/>
-    </row>
-    <row r="36" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="40"/>
-      <c r="B36" s="67">
+      <c r="AK35" s="52"/>
+    </row>
+    <row r="36" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="31"/>
+      <c r="B36" s="56">
         <v>15</v>
       </c>
-      <c r="C36" s="68"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="69" t="str">
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F36,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H36" s="68"/>
-      <c r="I36" s="70"/>
-      <c r="J36" s="68"/>
-      <c r="K36" s="70"/>
-      <c r="L36" s="70"/>
-      <c r="M36" s="70"/>
-      <c r="N36" s="70"/>
-      <c r="O36" s="70"/>
-      <c r="P36" s="70"/>
-      <c r="Q36" s="70"/>
-      <c r="R36" s="70"/>
-      <c r="S36" s="70"/>
-      <c r="T36" s="70"/>
-      <c r="U36" s="70"/>
-      <c r="V36" s="70"/>
-      <c r="W36" s="70"/>
-      <c r="X36" s="70"/>
-      <c r="Y36" s="70"/>
-      <c r="Z36" s="70"/>
-      <c r="AA36" s="70"/>
-      <c r="AB36" s="68"/>
-      <c r="AC36" s="68"/>
-      <c r="AD36" s="69" t="str">
+      <c r="H36" s="57"/>
+      <c r="I36" s="59"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="59"/>
+      <c r="L36" s="59"/>
+      <c r="M36" s="59"/>
+      <c r="N36" s="59"/>
+      <c r="O36" s="59"/>
+      <c r="P36" s="59"/>
+      <c r="Q36" s="59"/>
+      <c r="R36" s="59"/>
+      <c r="S36" s="59"/>
+      <c r="T36" s="59"/>
+      <c r="U36" s="59"/>
+      <c r="V36" s="59"/>
+      <c r="W36" s="59"/>
+      <c r="X36" s="59"/>
+      <c r="Y36" s="59"/>
+      <c r="Z36" s="59"/>
+      <c r="AA36" s="59"/>
+      <c r="AB36" s="57"/>
+      <c r="AC36" s="57"/>
+      <c r="AD36" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB36,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE36" s="68"/>
-      <c r="AF36" s="68"/>
-      <c r="AG36" s="71"/>
-      <c r="AH36" s="68"/>
-      <c r="AI36" s="72"/>
-      <c r="AJ36" s="73" t="str">
+      <c r="AE36" s="57"/>
+      <c r="AF36" s="57"/>
+      <c r="AG36" s="60"/>
+      <c r="AH36" s="57"/>
+      <c r="AI36" s="61"/>
+      <c r="AJ36" s="62" t="str">
         <f>IF(COUNTA(C36,D36,E36,F36,H36,I36,L36,M36,N36,P36,Q36,R36,S36,T36,U36,X36,Y36,Z36,AB36,AC36,AH36)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C36=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D36=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E36=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F36=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G36=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H36=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I36=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L36=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M36=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N36=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P36=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q36=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R36=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S36=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T36=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U36=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X36=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y36=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z36=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB36=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC36=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH36=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C36=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D36=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E36=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F36=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G36=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H36=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I36=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L36=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M36=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N36=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P36=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q36=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R36=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S36=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T36=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U36=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X36=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y36=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z36=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB36=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC36=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH36=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK36" s="63"/>
-    </row>
-    <row r="37" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A37" s="40"/>
-      <c r="B37" s="67">
+      <c r="AK36" s="52"/>
+    </row>
+    <row r="37" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="31"/>
+      <c r="B37" s="56">
         <v>16</v>
       </c>
-      <c r="C37" s="68"/>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="69" t="str">
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F37,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H37" s="68"/>
-      <c r="I37" s="70"/>
-      <c r="J37" s="68"/>
-      <c r="K37" s="70"/>
-      <c r="L37" s="70"/>
-      <c r="M37" s="70"/>
-      <c r="N37" s="70"/>
-      <c r="O37" s="70"/>
-      <c r="P37" s="70"/>
-      <c r="Q37" s="70"/>
-      <c r="R37" s="70"/>
-      <c r="S37" s="70"/>
-      <c r="T37" s="70"/>
-      <c r="U37" s="70"/>
-      <c r="V37" s="70"/>
-      <c r="W37" s="70"/>
-      <c r="X37" s="70"/>
-      <c r="Y37" s="70"/>
-      <c r="Z37" s="70"/>
-      <c r="AA37" s="70"/>
-      <c r="AB37" s="68"/>
-      <c r="AC37" s="68"/>
-      <c r="AD37" s="69" t="str">
+      <c r="H37" s="57"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="59"/>
+      <c r="L37" s="59"/>
+      <c r="M37" s="59"/>
+      <c r="N37" s="59"/>
+      <c r="O37" s="59"/>
+      <c r="P37" s="59"/>
+      <c r="Q37" s="59"/>
+      <c r="R37" s="59"/>
+      <c r="S37" s="59"/>
+      <c r="T37" s="59"/>
+      <c r="U37" s="59"/>
+      <c r="V37" s="59"/>
+      <c r="W37" s="59"/>
+      <c r="X37" s="59"/>
+      <c r="Y37" s="59"/>
+      <c r="Z37" s="59"/>
+      <c r="AA37" s="59"/>
+      <c r="AB37" s="57"/>
+      <c r="AC37" s="57"/>
+      <c r="AD37" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB37,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE37" s="68"/>
-      <c r="AF37" s="68"/>
-      <c r="AG37" s="71"/>
-      <c r="AH37" s="68"/>
-      <c r="AI37" s="72"/>
-      <c r="AJ37" s="73" t="str">
+      <c r="AE37" s="57"/>
+      <c r="AF37" s="57"/>
+      <c r="AG37" s="60"/>
+      <c r="AH37" s="57"/>
+      <c r="AI37" s="61"/>
+      <c r="AJ37" s="62" t="str">
         <f>IF(COUNTA(C37,D37,E37,F37,H37,I37,L37,M37,N37,P37,Q37,R37,S37,T37,U37,X37,Y37,Z37,AB37,AC37,AH37)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C37=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D37=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E37=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F37=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G37=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H37=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I37=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L37=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M37=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N37=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P37=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q37=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R37=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S37=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T37=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U37=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X37=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y37=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z37=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB37=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC37=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH37=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C37=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D37=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E37=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F37=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G37=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H37=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I37=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L37=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M37=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N37=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P37=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q37=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R37=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S37=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T37=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U37=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X37=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y37=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z37=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB37=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC37=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH37=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK37" s="63"/>
-    </row>
-    <row r="38" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="40"/>
-      <c r="B38" s="67">
+      <c r="AK37" s="52"/>
+    </row>
+    <row r="38" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="31"/>
+      <c r="B38" s="56">
         <v>17</v>
       </c>
-      <c r="C38" s="68"/>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="69" t="str">
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F38,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H38" s="68"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="70"/>
-      <c r="L38" s="70"/>
-      <c r="M38" s="70"/>
-      <c r="N38" s="70"/>
-      <c r="O38" s="70"/>
-      <c r="P38" s="70"/>
-      <c r="Q38" s="70"/>
-      <c r="R38" s="70"/>
-      <c r="S38" s="70"/>
-      <c r="T38" s="70"/>
-      <c r="U38" s="70"/>
-      <c r="V38" s="70"/>
-      <c r="W38" s="70"/>
-      <c r="X38" s="70"/>
-      <c r="Y38" s="70"/>
-      <c r="Z38" s="70"/>
-      <c r="AA38" s="70"/>
-      <c r="AB38" s="68"/>
-      <c r="AC38" s="68"/>
-      <c r="AD38" s="69" t="str">
+      <c r="H38" s="57"/>
+      <c r="I38" s="59"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="59"/>
+      <c r="L38" s="59"/>
+      <c r="M38" s="59"/>
+      <c r="N38" s="59"/>
+      <c r="O38" s="59"/>
+      <c r="P38" s="59"/>
+      <c r="Q38" s="59"/>
+      <c r="R38" s="59"/>
+      <c r="S38" s="59"/>
+      <c r="T38" s="59"/>
+      <c r="U38" s="59"/>
+      <c r="V38" s="59"/>
+      <c r="W38" s="59"/>
+      <c r="X38" s="59"/>
+      <c r="Y38" s="59"/>
+      <c r="Z38" s="59"/>
+      <c r="AA38" s="59"/>
+      <c r="AB38" s="57"/>
+      <c r="AC38" s="57"/>
+      <c r="AD38" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB38,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE38" s="68"/>
-      <c r="AF38" s="68"/>
-      <c r="AG38" s="71"/>
-      <c r="AH38" s="68"/>
-      <c r="AI38" s="72"/>
-      <c r="AJ38" s="73" t="str">
+      <c r="AE38" s="57"/>
+      <c r="AF38" s="57"/>
+      <c r="AG38" s="60"/>
+      <c r="AH38" s="57"/>
+      <c r="AI38" s="61"/>
+      <c r="AJ38" s="62" t="str">
         <f>IF(COUNTA(C38,D38,E38,F38,H38,I38,L38,M38,N38,P38,Q38,R38,S38,T38,U38,X38,Y38,Z38,AB38,AC38,AH38)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C38=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D38=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E38=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F38=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G38=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H38=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I38=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L38=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M38=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N38=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P38=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q38=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R38=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S38=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T38=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U38=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X38=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y38=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z38=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB38=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC38=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH38=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C38=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D38=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E38=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F38=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G38=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H38=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I38=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L38=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M38=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N38=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P38=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q38=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R38=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S38=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T38=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U38=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X38=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y38=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z38=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB38=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC38=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH38=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK38" s="63"/>
-    </row>
-    <row r="39" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="40"/>
-      <c r="B39" s="67">
+      <c r="AK38" s="52"/>
+    </row>
+    <row r="39" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="31"/>
+      <c r="B39" s="56">
         <v>18</v>
       </c>
-      <c r="C39" s="68"/>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="69" t="str">
+      <c r="C39" s="57"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F39,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H39" s="68"/>
-      <c r="I39" s="70"/>
-      <c r="J39" s="68"/>
-      <c r="K39" s="70"/>
-      <c r="L39" s="70"/>
-      <c r="M39" s="70"/>
-      <c r="N39" s="70"/>
-      <c r="O39" s="70"/>
-      <c r="P39" s="70"/>
-      <c r="Q39" s="70"/>
-      <c r="R39" s="70"/>
-      <c r="S39" s="70"/>
-      <c r="T39" s="70"/>
-      <c r="U39" s="70"/>
-      <c r="V39" s="70"/>
-      <c r="W39" s="70"/>
-      <c r="X39" s="70"/>
-      <c r="Y39" s="70"/>
-      <c r="Z39" s="70"/>
-      <c r="AA39" s="70"/>
-      <c r="AB39" s="68"/>
-      <c r="AC39" s="68"/>
-      <c r="AD39" s="69" t="str">
+      <c r="H39" s="57"/>
+      <c r="I39" s="59"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="59"/>
+      <c r="L39" s="59"/>
+      <c r="M39" s="59"/>
+      <c r="N39" s="59"/>
+      <c r="O39" s="59"/>
+      <c r="P39" s="59"/>
+      <c r="Q39" s="59"/>
+      <c r="R39" s="59"/>
+      <c r="S39" s="59"/>
+      <c r="T39" s="59"/>
+      <c r="U39" s="59"/>
+      <c r="V39" s="59"/>
+      <c r="W39" s="59"/>
+      <c r="X39" s="59"/>
+      <c r="Y39" s="59"/>
+      <c r="Z39" s="59"/>
+      <c r="AA39" s="59"/>
+      <c r="AB39" s="57"/>
+      <c r="AC39" s="57"/>
+      <c r="AD39" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB39,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE39" s="68"/>
-      <c r="AF39" s="68"/>
-      <c r="AG39" s="71"/>
-      <c r="AH39" s="68"/>
-      <c r="AI39" s="72"/>
-      <c r="AJ39" s="73" t="str">
+      <c r="AE39" s="57"/>
+      <c r="AF39" s="57"/>
+      <c r="AG39" s="60"/>
+      <c r="AH39" s="57"/>
+      <c r="AI39" s="61"/>
+      <c r="AJ39" s="62" t="str">
         <f>IF(COUNTA(C39,D39,E39,F39,H39,I39,L39,M39,N39,P39,Q39,R39,S39,T39,U39,X39,Y39,Z39,AB39,AC39,AH39)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C39=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D39=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E39=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F39=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G39=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H39=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I39=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L39=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M39=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N39=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P39=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q39=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R39=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S39=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T39=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U39=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X39=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y39=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z39=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB39=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC39=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH39=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C39=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D39=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E39=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F39=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G39=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H39=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I39=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L39=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M39=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N39=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P39=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q39=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R39=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S39=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T39=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U39=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X39=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y39=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z39=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB39=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC39=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH39=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK39" s="63"/>
-    </row>
-    <row r="40" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="40"/>
-      <c r="B40" s="67">
+      <c r="AK39" s="52"/>
+    </row>
+    <row r="40" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="31"/>
+      <c r="B40" s="56">
         <v>19</v>
       </c>
-      <c r="C40" s="68"/>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="69" t="str">
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F40,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H40" s="68"/>
-      <c r="I40" s="70"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="70"/>
-      <c r="L40" s="70"/>
-      <c r="M40" s="70"/>
-      <c r="N40" s="70"/>
-      <c r="O40" s="70"/>
-      <c r="P40" s="70"/>
-      <c r="Q40" s="70"/>
-      <c r="R40" s="70"/>
-      <c r="S40" s="70"/>
-      <c r="T40" s="70"/>
-      <c r="U40" s="70"/>
-      <c r="V40" s="70"/>
-      <c r="W40" s="70"/>
-      <c r="X40" s="70"/>
-      <c r="Y40" s="70"/>
-      <c r="Z40" s="70"/>
-      <c r="AA40" s="70"/>
-      <c r="AB40" s="68"/>
-      <c r="AC40" s="68"/>
-      <c r="AD40" s="69" t="str">
+      <c r="H40" s="57"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="59"/>
+      <c r="L40" s="59"/>
+      <c r="M40" s="59"/>
+      <c r="N40" s="59"/>
+      <c r="O40" s="59"/>
+      <c r="P40" s="59"/>
+      <c r="Q40" s="59"/>
+      <c r="R40" s="59"/>
+      <c r="S40" s="59"/>
+      <c r="T40" s="59"/>
+      <c r="U40" s="59"/>
+      <c r="V40" s="59"/>
+      <c r="W40" s="59"/>
+      <c r="X40" s="59"/>
+      <c r="Y40" s="59"/>
+      <c r="Z40" s="59"/>
+      <c r="AA40" s="59"/>
+      <c r="AB40" s="57"/>
+      <c r="AC40" s="57"/>
+      <c r="AD40" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB40,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE40" s="68"/>
-      <c r="AF40" s="68"/>
-      <c r="AG40" s="71"/>
-      <c r="AH40" s="68"/>
-      <c r="AI40" s="72"/>
-      <c r="AJ40" s="73" t="str">
+      <c r="AE40" s="57"/>
+      <c r="AF40" s="57"/>
+      <c r="AG40" s="60"/>
+      <c r="AH40" s="57"/>
+      <c r="AI40" s="61"/>
+      <c r="AJ40" s="62" t="str">
         <f>IF(COUNTA(C40,D40,E40,F40,H40,I40,L40,M40,N40,P40,Q40,R40,S40,T40,U40,X40,Y40,Z40,AB40,AC40,AH40)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C40=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D40=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E40=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F40=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G40=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H40=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I40=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L40=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M40=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N40=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P40=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q40=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R40=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S40=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T40=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U40=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X40=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y40=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z40=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB40=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC40=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH40=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C40=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D40=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E40=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F40=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G40=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H40=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I40=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L40=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M40=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N40=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P40=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q40=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R40=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S40=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T40=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U40=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X40=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y40=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z40=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB40=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC40=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH40=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK40" s="63"/>
-    </row>
-    <row r="41" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="40"/>
-      <c r="B41" s="67">
+      <c r="AK40" s="52"/>
+    </row>
+    <row r="41" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="31"/>
+      <c r="B41" s="56">
         <v>20</v>
       </c>
-      <c r="C41" s="68"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="69" t="str">
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+      <c r="G41" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F41,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H41" s="68"/>
-      <c r="I41" s="70"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
-      <c r="M41" s="70"/>
-      <c r="N41" s="70"/>
-      <c r="O41" s="70"/>
-      <c r="P41" s="70"/>
-      <c r="Q41" s="70"/>
-      <c r="R41" s="70"/>
-      <c r="S41" s="70"/>
-      <c r="T41" s="70"/>
-      <c r="U41" s="70"/>
-      <c r="V41" s="70"/>
-      <c r="W41" s="70"/>
-      <c r="X41" s="70"/>
-      <c r="Y41" s="70"/>
-      <c r="Z41" s="70"/>
-      <c r="AA41" s="70"/>
-      <c r="AB41" s="68"/>
-      <c r="AC41" s="68"/>
-      <c r="AD41" s="69" t="str">
+      <c r="H41" s="57"/>
+      <c r="I41" s="59"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="59"/>
+      <c r="L41" s="59"/>
+      <c r="M41" s="59"/>
+      <c r="N41" s="59"/>
+      <c r="O41" s="59"/>
+      <c r="P41" s="59"/>
+      <c r="Q41" s="59"/>
+      <c r="R41" s="59"/>
+      <c r="S41" s="59"/>
+      <c r="T41" s="59"/>
+      <c r="U41" s="59"/>
+      <c r="V41" s="59"/>
+      <c r="W41" s="59"/>
+      <c r="X41" s="59"/>
+      <c r="Y41" s="59"/>
+      <c r="Z41" s="59"/>
+      <c r="AA41" s="59"/>
+      <c r="AB41" s="57"/>
+      <c r="AC41" s="57"/>
+      <c r="AD41" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB41,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE41" s="68"/>
-      <c r="AF41" s="68"/>
-      <c r="AG41" s="71"/>
-      <c r="AH41" s="68"/>
-      <c r="AI41" s="72"/>
-      <c r="AJ41" s="73" t="str">
+      <c r="AE41" s="57"/>
+      <c r="AF41" s="57"/>
+      <c r="AG41" s="60"/>
+      <c r="AH41" s="57"/>
+      <c r="AI41" s="61"/>
+      <c r="AJ41" s="62" t="str">
         <f>IF(COUNTA(C41,D41,E41,F41,H41,I41,L41,M41,N41,P41,Q41,R41,S41,T41,U41,X41,Y41,Z41,AB41,AC41,AH41)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C41=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D41=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E41=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F41=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G41=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H41=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I41=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L41=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M41=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N41=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P41=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q41=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R41=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S41=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T41=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U41=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X41=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y41=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z41=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB41=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC41=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH41=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C41=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D41=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E41=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F41=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G41=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H41=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I41=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L41=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M41=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N41=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P41=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q41=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R41=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S41=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T41=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U41=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X41=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y41=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z41=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB41=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC41=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH41=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK41" s="63"/>
-    </row>
-    <row r="42" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="40"/>
-      <c r="B42" s="67">
+      <c r="AK41" s="52"/>
+    </row>
+    <row r="42" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="31"/>
+      <c r="B42" s="56">
         <v>21</v>
       </c>
-      <c r="C42" s="68"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="69" t="str">
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F42,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H42" s="68"/>
-      <c r="I42" s="70"/>
-      <c r="J42" s="68"/>
-      <c r="K42" s="70"/>
-      <c r="L42" s="70"/>
-      <c r="M42" s="70"/>
-      <c r="N42" s="70"/>
-      <c r="O42" s="70"/>
-      <c r="P42" s="70"/>
-      <c r="Q42" s="70"/>
-      <c r="R42" s="70"/>
-      <c r="S42" s="70"/>
-      <c r="T42" s="70"/>
-      <c r="U42" s="70"/>
-      <c r="V42" s="70"/>
-      <c r="W42" s="70"/>
-      <c r="X42" s="70"/>
-      <c r="Y42" s="70"/>
-      <c r="Z42" s="70"/>
-      <c r="AA42" s="70"/>
-      <c r="AB42" s="68"/>
-      <c r="AC42" s="68"/>
-      <c r="AD42" s="69" t="str">
+      <c r="H42" s="57"/>
+      <c r="I42" s="59"/>
+      <c r="J42" s="57"/>
+      <c r="K42" s="59"/>
+      <c r="L42" s="59"/>
+      <c r="M42" s="59"/>
+      <c r="N42" s="59"/>
+      <c r="O42" s="59"/>
+      <c r="P42" s="59"/>
+      <c r="Q42" s="59"/>
+      <c r="R42" s="59"/>
+      <c r="S42" s="59"/>
+      <c r="T42" s="59"/>
+      <c r="U42" s="59"/>
+      <c r="V42" s="59"/>
+      <c r="W42" s="59"/>
+      <c r="X42" s="59"/>
+      <c r="Y42" s="59"/>
+      <c r="Z42" s="59"/>
+      <c r="AA42" s="59"/>
+      <c r="AB42" s="57"/>
+      <c r="AC42" s="57"/>
+      <c r="AD42" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB42,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE42" s="68"/>
-      <c r="AF42" s="68"/>
-      <c r="AG42" s="71"/>
-      <c r="AH42" s="68"/>
-      <c r="AI42" s="72"/>
-      <c r="AJ42" s="73" t="str">
+      <c r="AE42" s="57"/>
+      <c r="AF42" s="57"/>
+      <c r="AG42" s="60"/>
+      <c r="AH42" s="57"/>
+      <c r="AI42" s="61"/>
+      <c r="AJ42" s="62" t="str">
         <f>IF(COUNTA(C42,D42,E42,F42,H42,I42,L42,M42,N42,P42,Q42,R42,S42,T42,U42,X42,Y42,Z42,AB42,AC42,AH42)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C42=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D42=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E42=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F42=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G42=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H42=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I42=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L42=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M42=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N42=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P42=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q42=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R42=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S42=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T42=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U42=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X42=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y42=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z42=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB42=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC42=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH42=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C42=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D42=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E42=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F42=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G42=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H42=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I42=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L42=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M42=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N42=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P42=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q42=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R42=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S42=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T42=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U42=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X42=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y42=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z42=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB42=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC42=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH42=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK42" s="63"/>
-    </row>
-    <row r="43" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="40"/>
-      <c r="B43" s="67">
+      <c r="AK42" s="52"/>
+    </row>
+    <row r="43" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="31"/>
+      <c r="B43" s="56">
         <v>22</v>
       </c>
-      <c r="C43" s="68"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="69" t="str">
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F43,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H43" s="68"/>
-      <c r="I43" s="70"/>
-      <c r="J43" s="68"/>
-      <c r="K43" s="70"/>
-      <c r="L43" s="70"/>
-      <c r="M43" s="70"/>
-      <c r="N43" s="70"/>
-      <c r="O43" s="70"/>
-      <c r="P43" s="70"/>
-      <c r="Q43" s="70"/>
-      <c r="R43" s="70"/>
-      <c r="S43" s="70"/>
-      <c r="T43" s="70"/>
-      <c r="U43" s="70"/>
-      <c r="V43" s="70"/>
-      <c r="W43" s="70"/>
-      <c r="X43" s="70"/>
-      <c r="Y43" s="70"/>
-      <c r="Z43" s="70"/>
-      <c r="AA43" s="70"/>
-      <c r="AB43" s="68"/>
-      <c r="AC43" s="68"/>
-      <c r="AD43" s="69" t="str">
+      <c r="H43" s="57"/>
+      <c r="I43" s="59"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="59"/>
+      <c r="L43" s="59"/>
+      <c r="M43" s="59"/>
+      <c r="N43" s="59"/>
+      <c r="O43" s="59"/>
+      <c r="P43" s="59"/>
+      <c r="Q43" s="59"/>
+      <c r="R43" s="59"/>
+      <c r="S43" s="59"/>
+      <c r="T43" s="59"/>
+      <c r="U43" s="59"/>
+      <c r="V43" s="59"/>
+      <c r="W43" s="59"/>
+      <c r="X43" s="59"/>
+      <c r="Y43" s="59"/>
+      <c r="Z43" s="59"/>
+      <c r="AA43" s="59"/>
+      <c r="AB43" s="57"/>
+      <c r="AC43" s="57"/>
+      <c r="AD43" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB43,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE43" s="68"/>
-      <c r="AF43" s="68"/>
-      <c r="AG43" s="71"/>
-      <c r="AH43" s="68"/>
-      <c r="AI43" s="72"/>
-      <c r="AJ43" s="73" t="str">
+      <c r="AE43" s="57"/>
+      <c r="AF43" s="57"/>
+      <c r="AG43" s="60"/>
+      <c r="AH43" s="57"/>
+      <c r="AI43" s="61"/>
+      <c r="AJ43" s="62" t="str">
         <f>IF(COUNTA(C43,D43,E43,F43,H43,I43,L43,M43,N43,P43,Q43,R43,S43,T43,U43,X43,Y43,Z43,AB43,AC43,AH43)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C43=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D43=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E43=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F43=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G43=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H43=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I43=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L43=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M43=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N43=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P43=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q43=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R43=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S43=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T43=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U43=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X43=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y43=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z43=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB43=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC43=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH43=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C43=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D43=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E43=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F43=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G43=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H43=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I43=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L43=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M43=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N43=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P43=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q43=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R43=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S43=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T43=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U43=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X43=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y43=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z43=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB43=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC43=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH43=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK43" s="63"/>
-    </row>
-    <row r="44" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="40"/>
-      <c r="B44" s="67">
+      <c r="AK43" s="52"/>
+    </row>
+    <row r="44" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" s="31"/>
+      <c r="B44" s="56">
         <v>23</v>
       </c>
-      <c r="C44" s="68"/>
-      <c r="D44" s="68"/>
-      <c r="E44" s="68"/>
-      <c r="F44" s="68"/>
-      <c r="G44" s="69" t="str">
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F44,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H44" s="68"/>
-      <c r="I44" s="70"/>
-      <c r="J44" s="68"/>
-      <c r="K44" s="70"/>
-      <c r="L44" s="70"/>
-      <c r="M44" s="70"/>
-      <c r="N44" s="70"/>
-      <c r="O44" s="70"/>
-      <c r="P44" s="70"/>
-      <c r="Q44" s="70"/>
-      <c r="R44" s="70"/>
-      <c r="S44" s="70"/>
-      <c r="T44" s="70"/>
-      <c r="U44" s="70"/>
-      <c r="V44" s="70"/>
-      <c r="W44" s="70"/>
-      <c r="X44" s="70"/>
-      <c r="Y44" s="70"/>
-      <c r="Z44" s="70"/>
-      <c r="AA44" s="70"/>
-      <c r="AB44" s="68"/>
-      <c r="AC44" s="68"/>
-      <c r="AD44" s="69" t="str">
+      <c r="H44" s="57"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="59"/>
+      <c r="L44" s="59"/>
+      <c r="M44" s="59"/>
+      <c r="N44" s="59"/>
+      <c r="O44" s="59"/>
+      <c r="P44" s="59"/>
+      <c r="Q44" s="59"/>
+      <c r="R44" s="59"/>
+      <c r="S44" s="59"/>
+      <c r="T44" s="59"/>
+      <c r="U44" s="59"/>
+      <c r="V44" s="59"/>
+      <c r="W44" s="59"/>
+      <c r="X44" s="59"/>
+      <c r="Y44" s="59"/>
+      <c r="Z44" s="59"/>
+      <c r="AA44" s="59"/>
+      <c r="AB44" s="57"/>
+      <c r="AC44" s="57"/>
+      <c r="AD44" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB44,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE44" s="68"/>
-      <c r="AF44" s="68"/>
-      <c r="AG44" s="71"/>
-      <c r="AH44" s="68"/>
-      <c r="AI44" s="72"/>
-      <c r="AJ44" s="73" t="str">
+      <c r="AE44" s="57"/>
+      <c r="AF44" s="57"/>
+      <c r="AG44" s="60"/>
+      <c r="AH44" s="57"/>
+      <c r="AI44" s="61"/>
+      <c r="AJ44" s="62" t="str">
         <f>IF(COUNTA(C44,D44,E44,F44,H44,I44,L44,M44,N44,P44,Q44,R44,S44,T44,U44,X44,Y44,Z44,AB44,AC44,AH44)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C44=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D44=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E44=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F44=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G44=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H44=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I44=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L44=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M44=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N44=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P44=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q44=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R44=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S44=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T44=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U44=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X44=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y44=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z44=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB44=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC44=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH44=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C44=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D44=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E44=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F44=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G44=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H44=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I44=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L44=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M44=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N44=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P44=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q44=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R44=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S44=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T44=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U44=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X44=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y44=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z44=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB44=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC44=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH44=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK44" s="63"/>
-    </row>
-    <row r="45" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="40"/>
-      <c r="B45" s="67">
+      <c r="AK44" s="52"/>
+    </row>
+    <row r="45" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" s="31"/>
+      <c r="B45" s="56">
         <v>24</v>
       </c>
-      <c r="C45" s="68"/>
-      <c r="D45" s="68"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="69" t="str">
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F45,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H45" s="68"/>
-      <c r="I45" s="70"/>
-      <c r="J45" s="68"/>
-      <c r="K45" s="70"/>
-      <c r="L45" s="70"/>
-      <c r="M45" s="70"/>
-      <c r="N45" s="70"/>
-      <c r="O45" s="70"/>
-      <c r="P45" s="70"/>
-      <c r="Q45" s="70"/>
-      <c r="R45" s="70"/>
-      <c r="S45" s="70"/>
-      <c r="T45" s="70"/>
-      <c r="U45" s="70"/>
-      <c r="V45" s="70"/>
-      <c r="W45" s="70"/>
-      <c r="X45" s="70"/>
-      <c r="Y45" s="70"/>
-      <c r="Z45" s="70"/>
-      <c r="AA45" s="70"/>
-      <c r="AB45" s="68"/>
-      <c r="AC45" s="68"/>
-      <c r="AD45" s="69" t="str">
+      <c r="H45" s="57"/>
+      <c r="I45" s="59"/>
+      <c r="J45" s="57"/>
+      <c r="K45" s="59"/>
+      <c r="L45" s="59"/>
+      <c r="M45" s="59"/>
+      <c r="N45" s="59"/>
+      <c r="O45" s="59"/>
+      <c r="P45" s="59"/>
+      <c r="Q45" s="59"/>
+      <c r="R45" s="59"/>
+      <c r="S45" s="59"/>
+      <c r="T45" s="59"/>
+      <c r="U45" s="59"/>
+      <c r="V45" s="59"/>
+      <c r="W45" s="59"/>
+      <c r="X45" s="59"/>
+      <c r="Y45" s="59"/>
+      <c r="Z45" s="59"/>
+      <c r="AA45" s="59"/>
+      <c r="AB45" s="57"/>
+      <c r="AC45" s="57"/>
+      <c r="AD45" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB45,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE45" s="68"/>
-      <c r="AF45" s="68"/>
-      <c r="AG45" s="71"/>
-      <c r="AH45" s="68"/>
-      <c r="AI45" s="72"/>
-      <c r="AJ45" s="73" t="str">
+      <c r="AE45" s="57"/>
+      <c r="AF45" s="57"/>
+      <c r="AG45" s="60"/>
+      <c r="AH45" s="57"/>
+      <c r="AI45" s="61"/>
+      <c r="AJ45" s="62" t="str">
         <f>IF(COUNTA(C45,D45,E45,F45,H45,I45,L45,M45,N45,P45,Q45,R45,S45,T45,U45,X45,Y45,Z45,AB45,AC45,AH45)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C45=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D45=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E45=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F45=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G45=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H45=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I45=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L45=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M45=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N45=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P45=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q45=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R45=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S45=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T45=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U45=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X45=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y45=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z45=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB45=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC45=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH45=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C45=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D45=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E45=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F45=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G45=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H45=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I45=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L45=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M45=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N45=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P45=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q45=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R45=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S45=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T45=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U45=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X45=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y45=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z45=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB45=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC45=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH45=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK45" s="63"/>
-    </row>
-    <row r="46" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" s="40"/>
-      <c r="B46" s="67">
+      <c r="AK45" s="52"/>
+    </row>
+    <row r="46" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A46" s="31"/>
+      <c r="B46" s="56">
         <v>25</v>
       </c>
-      <c r="C46" s="68"/>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="68"/>
-      <c r="G46" s="69" t="str">
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F46,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H46" s="68"/>
-      <c r="I46" s="70"/>
-      <c r="J46" s="68"/>
-      <c r="K46" s="70"/>
-      <c r="L46" s="70"/>
-      <c r="M46" s="70"/>
-      <c r="N46" s="70"/>
-      <c r="O46" s="70"/>
-      <c r="P46" s="70"/>
-      <c r="Q46" s="70"/>
-      <c r="R46" s="70"/>
-      <c r="S46" s="70"/>
-      <c r="T46" s="70"/>
-      <c r="U46" s="70"/>
-      <c r="V46" s="70"/>
-      <c r="W46" s="70"/>
-      <c r="X46" s="70"/>
-      <c r="Y46" s="70"/>
-      <c r="Z46" s="70"/>
-      <c r="AA46" s="70"/>
-      <c r="AB46" s="68"/>
-      <c r="AC46" s="68"/>
-      <c r="AD46" s="69" t="str">
+      <c r="H46" s="57"/>
+      <c r="I46" s="59"/>
+      <c r="J46" s="57"/>
+      <c r="K46" s="59"/>
+      <c r="L46" s="59"/>
+      <c r="M46" s="59"/>
+      <c r="N46" s="59"/>
+      <c r="O46" s="59"/>
+      <c r="P46" s="59"/>
+      <c r="Q46" s="59"/>
+      <c r="R46" s="59"/>
+      <c r="S46" s="59"/>
+      <c r="T46" s="59"/>
+      <c r="U46" s="59"/>
+      <c r="V46" s="59"/>
+      <c r="W46" s="59"/>
+      <c r="X46" s="59"/>
+      <c r="Y46" s="59"/>
+      <c r="Z46" s="59"/>
+      <c r="AA46" s="59"/>
+      <c r="AB46" s="57"/>
+      <c r="AC46" s="57"/>
+      <c r="AD46" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB46,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE46" s="68"/>
-      <c r="AF46" s="68"/>
-      <c r="AG46" s="71"/>
-      <c r="AH46" s="68"/>
-      <c r="AI46" s="72"/>
-      <c r="AJ46" s="73" t="str">
+      <c r="AE46" s="57"/>
+      <c r="AF46" s="57"/>
+      <c r="AG46" s="60"/>
+      <c r="AH46" s="57"/>
+      <c r="AI46" s="61"/>
+      <c r="AJ46" s="62" t="str">
         <f>IF(COUNTA(C46,D46,E46,F46,H46,I46,L46,M46,N46,P46,Q46,R46,S46,T46,U46,X46,Y46,Z46,AB46,AC46,AH46)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C46=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D46=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E46=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F46=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G46=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H46=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I46=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L46=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M46=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N46=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P46=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q46=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R46=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S46=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T46=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U46=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X46=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y46=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z46=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB46=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC46=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH46=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C46=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D46=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E46=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F46=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G46=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H46=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I46=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L46=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M46=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N46=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P46=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q46=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R46=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S46=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T46=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U46=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X46=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y46=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z46=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB46=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC46=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH46=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK46" s="63"/>
-    </row>
-    <row r="47" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="40"/>
-      <c r="B47" s="67">
+      <c r="AK46" s="52"/>
+    </row>
+    <row r="47" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="31"/>
+      <c r="B47" s="56">
         <v>26</v>
       </c>
-      <c r="C47" s="68"/>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="68"/>
-      <c r="G47" s="69" t="str">
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F47,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H47" s="68"/>
-      <c r="I47" s="70"/>
-      <c r="J47" s="68"/>
-      <c r="K47" s="70"/>
-      <c r="L47" s="70"/>
-      <c r="M47" s="70"/>
-      <c r="N47" s="70"/>
-      <c r="O47" s="70"/>
-      <c r="P47" s="70"/>
-      <c r="Q47" s="70"/>
-      <c r="R47" s="70"/>
-      <c r="S47" s="70"/>
-      <c r="T47" s="70"/>
-      <c r="U47" s="70"/>
-      <c r="V47" s="70"/>
-      <c r="W47" s="70"/>
-      <c r="X47" s="70"/>
-      <c r="Y47" s="70"/>
-      <c r="Z47" s="70"/>
-      <c r="AA47" s="70"/>
-      <c r="AB47" s="68"/>
-      <c r="AC47" s="68"/>
-      <c r="AD47" s="69" t="str">
+      <c r="H47" s="57"/>
+      <c r="I47" s="59"/>
+      <c r="J47" s="57"/>
+      <c r="K47" s="59"/>
+      <c r="L47" s="59"/>
+      <c r="M47" s="59"/>
+      <c r="N47" s="59"/>
+      <c r="O47" s="59"/>
+      <c r="P47" s="59"/>
+      <c r="Q47" s="59"/>
+      <c r="R47" s="59"/>
+      <c r="S47" s="59"/>
+      <c r="T47" s="59"/>
+      <c r="U47" s="59"/>
+      <c r="V47" s="59"/>
+      <c r="W47" s="59"/>
+      <c r="X47" s="59"/>
+      <c r="Y47" s="59"/>
+      <c r="Z47" s="59"/>
+      <c r="AA47" s="59"/>
+      <c r="AB47" s="57"/>
+      <c r="AC47" s="57"/>
+      <c r="AD47" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB47,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE47" s="68"/>
-      <c r="AF47" s="68"/>
-      <c r="AG47" s="71"/>
-      <c r="AH47" s="68"/>
-      <c r="AI47" s="72"/>
-      <c r="AJ47" s="73" t="str">
+      <c r="AE47" s="57"/>
+      <c r="AF47" s="57"/>
+      <c r="AG47" s="60"/>
+      <c r="AH47" s="57"/>
+      <c r="AI47" s="61"/>
+      <c r="AJ47" s="62" t="str">
         <f>IF(COUNTA(C47,D47,E47,F47,H47,I47,L47,M47,N47,P47,Q47,R47,S47,T47,U47,X47,Y47,Z47,AB47,AC47,AH47)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C47=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D47=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E47=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F47=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G47=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H47=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I47=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L47=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M47=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N47=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P47=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q47=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R47=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S47=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T47=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U47=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X47=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y47=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z47=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB47=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC47=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH47=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C47=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D47=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E47=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F47=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G47=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H47=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I47=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L47=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M47=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N47=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P47=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q47=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R47=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S47=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T47=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U47=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X47=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y47=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z47=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB47=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC47=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH47=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK47" s="63"/>
-    </row>
-    <row r="48" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="40"/>
-      <c r="B48" s="67">
+      <c r="AK47" s="52"/>
+    </row>
+    <row r="48" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="31"/>
+      <c r="B48" s="56">
         <v>27</v>
       </c>
-      <c r="C48" s="68"/>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
-      <c r="F48" s="68"/>
-      <c r="G48" s="69" t="str">
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F48,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H48" s="68"/>
-      <c r="I48" s="70"/>
-      <c r="J48" s="68"/>
-      <c r="K48" s="70"/>
-      <c r="L48" s="70"/>
-      <c r="M48" s="70"/>
-      <c r="N48" s="70"/>
-      <c r="O48" s="70"/>
-      <c r="P48" s="70"/>
-      <c r="Q48" s="70"/>
-      <c r="R48" s="70"/>
-      <c r="S48" s="70"/>
-      <c r="T48" s="70"/>
-      <c r="U48" s="70"/>
-      <c r="V48" s="70"/>
-      <c r="W48" s="70"/>
-      <c r="X48" s="70"/>
-      <c r="Y48" s="70"/>
-      <c r="Z48" s="70"/>
-      <c r="AA48" s="70"/>
-      <c r="AB48" s="68"/>
-      <c r="AC48" s="68"/>
-      <c r="AD48" s="69" t="str">
+      <c r="H48" s="57"/>
+      <c r="I48" s="59"/>
+      <c r="J48" s="57"/>
+      <c r="K48" s="59"/>
+      <c r="L48" s="59"/>
+      <c r="M48" s="59"/>
+      <c r="N48" s="59"/>
+      <c r="O48" s="59"/>
+      <c r="P48" s="59"/>
+      <c r="Q48" s="59"/>
+      <c r="R48" s="59"/>
+      <c r="S48" s="59"/>
+      <c r="T48" s="59"/>
+      <c r="U48" s="59"/>
+      <c r="V48" s="59"/>
+      <c r="W48" s="59"/>
+      <c r="X48" s="59"/>
+      <c r="Y48" s="59"/>
+      <c r="Z48" s="59"/>
+      <c r="AA48" s="59"/>
+      <c r="AB48" s="57"/>
+      <c r="AC48" s="57"/>
+      <c r="AD48" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB48,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE48" s="68"/>
-      <c r="AF48" s="68"/>
-      <c r="AG48" s="71"/>
-      <c r="AH48" s="68"/>
-      <c r="AI48" s="72"/>
-      <c r="AJ48" s="73" t="str">
+      <c r="AE48" s="57"/>
+      <c r="AF48" s="57"/>
+      <c r="AG48" s="60"/>
+      <c r="AH48" s="57"/>
+      <c r="AI48" s="61"/>
+      <c r="AJ48" s="62" t="str">
         <f>IF(COUNTA(C48,D48,E48,F48,H48,I48,L48,M48,N48,P48,Q48,R48,S48,T48,U48,X48,Y48,Z48,AB48,AC48,AH48)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C48=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D48=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E48=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F48=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G48=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H48=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I48=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L48=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M48=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N48=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P48=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q48=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R48=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S48=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T48=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U48=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X48=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y48=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z48=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB48=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC48=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH48=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C48=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D48=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E48=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F48=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G48=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H48=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I48=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L48=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M48=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N48=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P48=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q48=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R48=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S48=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T48=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U48=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X48=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y48=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z48=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB48=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC48=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH48=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK48" s="63"/>
-    </row>
-    <row r="49" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A49" s="40"/>
-      <c r="B49" s="67">
+      <c r="AK48" s="52"/>
+    </row>
+    <row r="49" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" s="31"/>
+      <c r="B49" s="56">
         <v>28</v>
       </c>
-      <c r="C49" s="68"/>
-      <c r="D49" s="68"/>
-      <c r="E49" s="68"/>
-      <c r="F49" s="68"/>
-      <c r="G49" s="69" t="str">
+      <c r="C49" s="57"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="57"/>
+      <c r="G49" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F49,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H49" s="68"/>
-      <c r="I49" s="70"/>
-      <c r="J49" s="68"/>
-      <c r="K49" s="70"/>
-      <c r="L49" s="70"/>
-      <c r="M49" s="70"/>
-      <c r="N49" s="70"/>
-      <c r="O49" s="70"/>
-      <c r="P49" s="70"/>
-      <c r="Q49" s="70"/>
-      <c r="R49" s="70"/>
-      <c r="S49" s="70"/>
-      <c r="T49" s="70"/>
-      <c r="U49" s="70"/>
-      <c r="V49" s="70"/>
-      <c r="W49" s="70"/>
-      <c r="X49" s="70"/>
-      <c r="Y49" s="70"/>
-      <c r="Z49" s="70"/>
-      <c r="AA49" s="70"/>
-      <c r="AB49" s="68"/>
-      <c r="AC49" s="68"/>
-      <c r="AD49" s="69" t="str">
+      <c r="H49" s="57"/>
+      <c r="I49" s="59"/>
+      <c r="J49" s="57"/>
+      <c r="K49" s="59"/>
+      <c r="L49" s="59"/>
+      <c r="M49" s="59"/>
+      <c r="N49" s="59"/>
+      <c r="O49" s="59"/>
+      <c r="P49" s="59"/>
+      <c r="Q49" s="59"/>
+      <c r="R49" s="59"/>
+      <c r="S49" s="59"/>
+      <c r="T49" s="59"/>
+      <c r="U49" s="59"/>
+      <c r="V49" s="59"/>
+      <c r="W49" s="59"/>
+      <c r="X49" s="59"/>
+      <c r="Y49" s="59"/>
+      <c r="Z49" s="59"/>
+      <c r="AA49" s="59"/>
+      <c r="AB49" s="57"/>
+      <c r="AC49" s="57"/>
+      <c r="AD49" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB49,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE49" s="68"/>
-      <c r="AF49" s="68"/>
-      <c r="AG49" s="71"/>
-      <c r="AH49" s="68"/>
-      <c r="AI49" s="72"/>
-      <c r="AJ49" s="73" t="str">
+      <c r="AE49" s="57"/>
+      <c r="AF49" s="57"/>
+      <c r="AG49" s="60"/>
+      <c r="AH49" s="57"/>
+      <c r="AI49" s="61"/>
+      <c r="AJ49" s="62" t="str">
         <f>IF(COUNTA(C49,D49,E49,F49,H49,I49,L49,M49,N49,P49,Q49,R49,S49,T49,U49,X49,Y49,Z49,AB49,AC49,AH49)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C49=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D49=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E49=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F49=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G49=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H49=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I49=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L49=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M49=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N49=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P49=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q49=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R49=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S49=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T49=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U49=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X49=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y49=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z49=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB49=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC49=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH49=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C49=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D49=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E49=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F49=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G49=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H49=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I49=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L49=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M49=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N49=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P49=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q49=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R49=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S49=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T49=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U49=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X49=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y49=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z49=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB49=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC49=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH49=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK49" s="63"/>
-    </row>
-    <row r="50" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="40"/>
-      <c r="B50" s="67">
+      <c r="AK49" s="52"/>
+    </row>
+    <row r="50" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="31"/>
+      <c r="B50" s="56">
         <v>29</v>
       </c>
-      <c r="C50" s="68"/>
-      <c r="D50" s="68"/>
-      <c r="E50" s="68"/>
-      <c r="F50" s="68"/>
-      <c r="G50" s="69" t="str">
+      <c r="C50" s="57"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="57"/>
+      <c r="G50" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F50,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H50" s="68"/>
-      <c r="I50" s="70"/>
-      <c r="J50" s="68"/>
-      <c r="K50" s="70"/>
-      <c r="L50" s="70"/>
-      <c r="M50" s="70"/>
-      <c r="N50" s="70"/>
-      <c r="O50" s="70"/>
-      <c r="P50" s="70"/>
-      <c r="Q50" s="70"/>
-      <c r="R50" s="70"/>
-      <c r="S50" s="70"/>
-      <c r="T50" s="70"/>
-      <c r="U50" s="70"/>
-      <c r="V50" s="70"/>
-      <c r="W50" s="70"/>
-      <c r="X50" s="70"/>
-      <c r="Y50" s="70"/>
-      <c r="Z50" s="70"/>
-      <c r="AA50" s="70"/>
-      <c r="AB50" s="68"/>
-      <c r="AC50" s="68"/>
-      <c r="AD50" s="69" t="str">
+      <c r="H50" s="57"/>
+      <c r="I50" s="59"/>
+      <c r="J50" s="57"/>
+      <c r="K50" s="59"/>
+      <c r="L50" s="59"/>
+      <c r="M50" s="59"/>
+      <c r="N50" s="59"/>
+      <c r="O50" s="59"/>
+      <c r="P50" s="59"/>
+      <c r="Q50" s="59"/>
+      <c r="R50" s="59"/>
+      <c r="S50" s="59"/>
+      <c r="T50" s="59"/>
+      <c r="U50" s="59"/>
+      <c r="V50" s="59"/>
+      <c r="W50" s="59"/>
+      <c r="X50" s="59"/>
+      <c r="Y50" s="59"/>
+      <c r="Z50" s="59"/>
+      <c r="AA50" s="59"/>
+      <c r="AB50" s="57"/>
+      <c r="AC50" s="57"/>
+      <c r="AD50" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB50,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE50" s="68"/>
-      <c r="AF50" s="68"/>
-      <c r="AG50" s="71"/>
-      <c r="AH50" s="68"/>
-      <c r="AI50" s="72"/>
-      <c r="AJ50" s="73" t="str">
+      <c r="AE50" s="57"/>
+      <c r="AF50" s="57"/>
+      <c r="AG50" s="60"/>
+      <c r="AH50" s="57"/>
+      <c r="AI50" s="61"/>
+      <c r="AJ50" s="62" t="str">
         <f>IF(COUNTA(C50,D50,E50,F50,H50,I50,L50,M50,N50,P50,Q50,R50,S50,T50,U50,X50,Y50,Z50,AB50,AC50,AH50)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C50=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D50=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E50=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F50=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G50=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H50=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I50=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L50=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M50=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N50=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P50=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q50=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R50=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S50=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T50=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U50=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X50=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y50=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z50=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB50=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC50=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH50=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C50=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D50=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E50=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F50=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G50=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H50=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I50=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L50=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M50=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N50=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P50=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q50=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R50=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S50=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T50=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U50=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X50=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y50=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z50=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB50=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC50=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH50=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK50" s="63"/>
-    </row>
-    <row r="51" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="40"/>
-      <c r="B51" s="67">
+      <c r="AK50" s="52"/>
+    </row>
+    <row r="51" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" s="31"/>
+      <c r="B51" s="56">
         <v>30</v>
       </c>
-      <c r="C51" s="68"/>
-      <c r="D51" s="68"/>
-      <c r="E51" s="68"/>
-      <c r="F51" s="68"/>
-      <c r="G51" s="69" t="str">
+      <c r="C51" s="57"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F51,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H51" s="68"/>
-      <c r="I51" s="70"/>
-      <c r="J51" s="68"/>
-      <c r="K51" s="70"/>
-      <c r="L51" s="70"/>
-      <c r="M51" s="70"/>
-      <c r="N51" s="70"/>
-      <c r="O51" s="70"/>
-      <c r="P51" s="70"/>
-      <c r="Q51" s="70"/>
-      <c r="R51" s="70"/>
-      <c r="S51" s="70"/>
-      <c r="T51" s="70"/>
-      <c r="U51" s="70"/>
-      <c r="V51" s="70"/>
-      <c r="W51" s="70"/>
-      <c r="X51" s="70"/>
-      <c r="Y51" s="70"/>
-      <c r="Z51" s="70"/>
-      <c r="AA51" s="70"/>
-      <c r="AB51" s="68"/>
-      <c r="AC51" s="68"/>
-      <c r="AD51" s="69" t="str">
+      <c r="H51" s="57"/>
+      <c r="I51" s="59"/>
+      <c r="J51" s="57"/>
+      <c r="K51" s="59"/>
+      <c r="L51" s="59"/>
+      <c r="M51" s="59"/>
+      <c r="N51" s="59"/>
+      <c r="O51" s="59"/>
+      <c r="P51" s="59"/>
+      <c r="Q51" s="59"/>
+      <c r="R51" s="59"/>
+      <c r="S51" s="59"/>
+      <c r="T51" s="59"/>
+      <c r="U51" s="59"/>
+      <c r="V51" s="59"/>
+      <c r="W51" s="59"/>
+      <c r="X51" s="59"/>
+      <c r="Y51" s="59"/>
+      <c r="Z51" s="59"/>
+      <c r="AA51" s="59"/>
+      <c r="AB51" s="57"/>
+      <c r="AC51" s="57"/>
+      <c r="AD51" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB51,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE51" s="68"/>
-      <c r="AF51" s="68"/>
-      <c r="AG51" s="71"/>
-      <c r="AH51" s="68"/>
-      <c r="AI51" s="72"/>
-      <c r="AJ51" s="73" t="str">
+      <c r="AE51" s="57"/>
+      <c r="AF51" s="57"/>
+      <c r="AG51" s="60"/>
+      <c r="AH51" s="57"/>
+      <c r="AI51" s="61"/>
+      <c r="AJ51" s="62" t="str">
         <f>IF(COUNTA(C51,D51,E51,F51,H51,I51,L51,M51,N51,P51,Q51,R51,S51,T51,U51,X51,Y51,Z51,AB51,AC51,AH51)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C51=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D51=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E51=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F51=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G51=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H51=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I51=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L51=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M51=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N51=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P51=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q51=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R51=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S51=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T51=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U51=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X51=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y51=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z51=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB51=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC51=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH51=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C51=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D51=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E51=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F51=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G51=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H51=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I51=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L51=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M51=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N51=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P51=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q51=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R51=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S51=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T51=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U51=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X51=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y51=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z51=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB51=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC51=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH51=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK51" s="63"/>
-    </row>
-    <row r="52" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="40"/>
-      <c r="B52" s="67">
+      <c r="AK51" s="52"/>
+    </row>
+    <row r="52" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A52" s="31"/>
+      <c r="B52" s="56">
         <v>31</v>
       </c>
-      <c r="C52" s="68"/>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="68"/>
-      <c r="G52" s="69" t="str">
+      <c r="C52" s="57"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F52,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H52" s="68"/>
-      <c r="I52" s="70"/>
-      <c r="J52" s="68"/>
-      <c r="K52" s="70"/>
-      <c r="L52" s="70"/>
-      <c r="M52" s="70"/>
-      <c r="N52" s="70"/>
-      <c r="O52" s="70"/>
-      <c r="P52" s="70"/>
-      <c r="Q52" s="70"/>
-      <c r="R52" s="70"/>
-      <c r="S52" s="70"/>
-      <c r="T52" s="70"/>
-      <c r="U52" s="70"/>
-      <c r="V52" s="70"/>
-      <c r="W52" s="70"/>
-      <c r="X52" s="70"/>
-      <c r="Y52" s="70"/>
-      <c r="Z52" s="70"/>
-      <c r="AA52" s="70"/>
-      <c r="AB52" s="68"/>
-      <c r="AC52" s="68"/>
-      <c r="AD52" s="69" t="str">
+      <c r="H52" s="57"/>
+      <c r="I52" s="59"/>
+      <c r="J52" s="57"/>
+      <c r="K52" s="59"/>
+      <c r="L52" s="59"/>
+      <c r="M52" s="59"/>
+      <c r="N52" s="59"/>
+      <c r="O52" s="59"/>
+      <c r="P52" s="59"/>
+      <c r="Q52" s="59"/>
+      <c r="R52" s="59"/>
+      <c r="S52" s="59"/>
+      <c r="T52" s="59"/>
+      <c r="U52" s="59"/>
+      <c r="V52" s="59"/>
+      <c r="W52" s="59"/>
+      <c r="X52" s="59"/>
+      <c r="Y52" s="59"/>
+      <c r="Z52" s="59"/>
+      <c r="AA52" s="59"/>
+      <c r="AB52" s="57"/>
+      <c r="AC52" s="57"/>
+      <c r="AD52" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB52,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE52" s="68"/>
-      <c r="AF52" s="68"/>
-      <c r="AG52" s="71"/>
-      <c r="AH52" s="68"/>
-      <c r="AI52" s="72"/>
-      <c r="AJ52" s="73" t="str">
+      <c r="AE52" s="57"/>
+      <c r="AF52" s="57"/>
+      <c r="AG52" s="60"/>
+      <c r="AH52" s="57"/>
+      <c r="AI52" s="61"/>
+      <c r="AJ52" s="62" t="str">
         <f>IF(COUNTA(C52,D52,E52,F52,H52,I52,L52,M52,N52,P52,Q52,R52,S52,T52,U52,X52,Y52,Z52,AB52,AC52,AH52)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C52=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D52=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E52=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F52=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G52=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H52=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I52=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L52=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M52=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N52=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P52=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q52=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R52=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S52=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T52=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U52=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X52=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y52=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z52=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB52=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC52=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH52=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C52=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D52=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E52=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F52=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G52=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H52=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I52=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L52=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M52=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N52=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P52=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q52=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R52=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S52=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T52=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U52=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X52=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y52=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z52=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB52=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC52=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH52=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK52" s="63"/>
-    </row>
-    <row r="53" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A53" s="40"/>
-      <c r="B53" s="67">
+      <c r="AK52" s="52"/>
+    </row>
+    <row r="53" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A53" s="31"/>
+      <c r="B53" s="56">
         <v>32</v>
       </c>
-      <c r="C53" s="68"/>
-      <c r="D53" s="68"/>
-      <c r="E53" s="68"/>
-      <c r="F53" s="68"/>
-      <c r="G53" s="69" t="str">
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F53,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H53" s="68"/>
-      <c r="I53" s="70"/>
-      <c r="J53" s="68"/>
-      <c r="K53" s="70"/>
-      <c r="L53" s="70"/>
-      <c r="M53" s="70"/>
-      <c r="N53" s="70"/>
-      <c r="O53" s="70"/>
-      <c r="P53" s="70"/>
-      <c r="Q53" s="70"/>
-      <c r="R53" s="70"/>
-      <c r="S53" s="70"/>
-      <c r="T53" s="70"/>
-      <c r="U53" s="70"/>
-      <c r="V53" s="70"/>
-      <c r="W53" s="70"/>
-      <c r="X53" s="70"/>
-      <c r="Y53" s="70"/>
-      <c r="Z53" s="70"/>
-      <c r="AA53" s="70"/>
-      <c r="AB53" s="68"/>
-      <c r="AC53" s="68"/>
-      <c r="AD53" s="69" t="str">
+      <c r="H53" s="57"/>
+      <c r="I53" s="59"/>
+      <c r="J53" s="57"/>
+      <c r="K53" s="59"/>
+      <c r="L53" s="59"/>
+      <c r="M53" s="59"/>
+      <c r="N53" s="59"/>
+      <c r="O53" s="59"/>
+      <c r="P53" s="59"/>
+      <c r="Q53" s="59"/>
+      <c r="R53" s="59"/>
+      <c r="S53" s="59"/>
+      <c r="T53" s="59"/>
+      <c r="U53" s="59"/>
+      <c r="V53" s="59"/>
+      <c r="W53" s="59"/>
+      <c r="X53" s="59"/>
+      <c r="Y53" s="59"/>
+      <c r="Z53" s="59"/>
+      <c r="AA53" s="59"/>
+      <c r="AB53" s="57"/>
+      <c r="AC53" s="57"/>
+      <c r="AD53" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB53,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE53" s="68"/>
-      <c r="AF53" s="68"/>
-      <c r="AG53" s="71"/>
-      <c r="AH53" s="68"/>
-      <c r="AI53" s="72"/>
-      <c r="AJ53" s="73" t="str">
+      <c r="AE53" s="57"/>
+      <c r="AF53" s="57"/>
+      <c r="AG53" s="60"/>
+      <c r="AH53" s="57"/>
+      <c r="AI53" s="61"/>
+      <c r="AJ53" s="62" t="str">
         <f>IF(COUNTA(C53,D53,E53,F53,H53,I53,L53,M53,N53,P53,Q53,R53,S53,T53,U53,X53,Y53,Z53,AB53,AC53,AH53)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C53=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D53=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E53=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F53=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G53=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H53=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I53=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L53=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M53=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N53=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P53=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q53=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R53=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S53=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T53=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U53=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X53=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y53=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z53=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB53=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC53=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH53=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C53=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D53=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E53=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F53=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G53=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H53=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I53=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L53=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M53=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N53=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P53=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q53=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R53=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S53=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T53=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U53=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X53=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y53=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z53=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB53=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC53=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH53=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK53" s="63"/>
-    </row>
-    <row r="54" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A54" s="40"/>
-      <c r="B54" s="67">
+      <c r="AK53" s="52"/>
+    </row>
+    <row r="54" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" s="31"/>
+      <c r="B54" s="56">
         <v>33</v>
       </c>
-      <c r="C54" s="68"/>
-      <c r="D54" s="68"/>
-      <c r="E54" s="68"/>
-      <c r="F54" s="68"/>
-      <c r="G54" s="69" t="str">
+      <c r="C54" s="57"/>
+      <c r="D54" s="57"/>
+      <c r="E54" s="57"/>
+      <c r="F54" s="57"/>
+      <c r="G54" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F54,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H54" s="68"/>
-      <c r="I54" s="70"/>
-      <c r="J54" s="68"/>
-      <c r="K54" s="70"/>
-      <c r="L54" s="70"/>
-      <c r="M54" s="70"/>
-      <c r="N54" s="70"/>
-      <c r="O54" s="70"/>
-      <c r="P54" s="70"/>
-      <c r="Q54" s="70"/>
-      <c r="R54" s="70"/>
-      <c r="S54" s="70"/>
-      <c r="T54" s="70"/>
-      <c r="U54" s="70"/>
-      <c r="V54" s="70"/>
-      <c r="W54" s="70"/>
-      <c r="X54" s="70"/>
-      <c r="Y54" s="70"/>
-      <c r="Z54" s="70"/>
-      <c r="AA54" s="70"/>
-      <c r="AB54" s="68"/>
-      <c r="AC54" s="68"/>
-      <c r="AD54" s="69" t="str">
+      <c r="H54" s="57"/>
+      <c r="I54" s="59"/>
+      <c r="J54" s="57"/>
+      <c r="K54" s="59"/>
+      <c r="L54" s="59"/>
+      <c r="M54" s="59"/>
+      <c r="N54" s="59"/>
+      <c r="O54" s="59"/>
+      <c r="P54" s="59"/>
+      <c r="Q54" s="59"/>
+      <c r="R54" s="59"/>
+      <c r="S54" s="59"/>
+      <c r="T54" s="59"/>
+      <c r="U54" s="59"/>
+      <c r="V54" s="59"/>
+      <c r="W54" s="59"/>
+      <c r="X54" s="59"/>
+      <c r="Y54" s="59"/>
+      <c r="Z54" s="59"/>
+      <c r="AA54" s="59"/>
+      <c r="AB54" s="57"/>
+      <c r="AC54" s="57"/>
+      <c r="AD54" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB54,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE54" s="68"/>
-      <c r="AF54" s="68"/>
-      <c r="AG54" s="71"/>
-      <c r="AH54" s="68"/>
-      <c r="AI54" s="72"/>
-      <c r="AJ54" s="73" t="str">
+      <c r="AE54" s="57"/>
+      <c r="AF54" s="57"/>
+      <c r="AG54" s="60"/>
+      <c r="AH54" s="57"/>
+      <c r="AI54" s="61"/>
+      <c r="AJ54" s="62" t="str">
         <f>IF(COUNTA(C54,D54,E54,F54,H54,I54,L54,M54,N54,P54,Q54,R54,S54,T54,U54,X54,Y54,Z54,AB54,AC54,AH54)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C54=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D54=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E54=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F54=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G54=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H54=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I54=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L54=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M54=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N54=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P54=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q54=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R54=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S54=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T54=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U54=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X54=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y54=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z54=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB54=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC54=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH54=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C54=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D54=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E54=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F54=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G54=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H54=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I54=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L54=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M54=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N54=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P54=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q54=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R54=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S54=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T54=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U54=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X54=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y54=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z54=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB54=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC54=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH54=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK54" s="63"/>
-    </row>
-    <row r="55" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A55" s="40"/>
-      <c r="B55" s="67">
+      <c r="AK54" s="52"/>
+    </row>
+    <row r="55" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A55" s="31"/>
+      <c r="B55" s="56">
         <v>34</v>
       </c>
-      <c r="C55" s="68"/>
-      <c r="D55" s="68"/>
-      <c r="E55" s="68"/>
-      <c r="F55" s="68"/>
-      <c r="G55" s="69" t="str">
+      <c r="C55" s="57"/>
+      <c r="D55" s="57"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F55,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H55" s="68"/>
-      <c r="I55" s="70"/>
-      <c r="J55" s="68"/>
-      <c r="K55" s="70"/>
-      <c r="L55" s="70"/>
-      <c r="M55" s="70"/>
-      <c r="N55" s="70"/>
-      <c r="O55" s="70"/>
-      <c r="P55" s="70"/>
-      <c r="Q55" s="70"/>
-      <c r="R55" s="70"/>
-      <c r="S55" s="70"/>
-      <c r="T55" s="70"/>
-      <c r="U55" s="70"/>
-      <c r="V55" s="70"/>
-      <c r="W55" s="70"/>
-      <c r="X55" s="70"/>
-      <c r="Y55" s="70"/>
-      <c r="Z55" s="70"/>
-      <c r="AA55" s="70"/>
-      <c r="AB55" s="68"/>
-      <c r="AC55" s="68"/>
-      <c r="AD55" s="69" t="str">
+      <c r="H55" s="57"/>
+      <c r="I55" s="59"/>
+      <c r="J55" s="57"/>
+      <c r="K55" s="59"/>
+      <c r="L55" s="59"/>
+      <c r="M55" s="59"/>
+      <c r="N55" s="59"/>
+      <c r="O55" s="59"/>
+      <c r="P55" s="59"/>
+      <c r="Q55" s="59"/>
+      <c r="R55" s="59"/>
+      <c r="S55" s="59"/>
+      <c r="T55" s="59"/>
+      <c r="U55" s="59"/>
+      <c r="V55" s="59"/>
+      <c r="W55" s="59"/>
+      <c r="X55" s="59"/>
+      <c r="Y55" s="59"/>
+      <c r="Z55" s="59"/>
+      <c r="AA55" s="59"/>
+      <c r="AB55" s="57"/>
+      <c r="AC55" s="57"/>
+      <c r="AD55" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB55,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE55" s="68"/>
-      <c r="AF55" s="68"/>
-      <c r="AG55" s="71"/>
-      <c r="AH55" s="68"/>
-      <c r="AI55" s="72"/>
-      <c r="AJ55" s="73" t="str">
+      <c r="AE55" s="57"/>
+      <c r="AF55" s="57"/>
+      <c r="AG55" s="60"/>
+      <c r="AH55" s="57"/>
+      <c r="AI55" s="61"/>
+      <c r="AJ55" s="62" t="str">
         <f>IF(COUNTA(C55,D55,E55,F55,H55,I55,L55,M55,N55,P55,Q55,R55,S55,T55,U55,X55,Y55,Z55,AB55,AC55,AH55)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C55=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D55=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E55=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F55=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G55=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H55=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I55=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L55=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M55=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N55=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P55=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q55=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R55=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S55=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T55=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U55=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X55=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y55=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z55=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB55=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC55=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH55=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C55=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D55=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E55=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F55=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G55=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H55=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I55=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L55=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M55=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N55=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P55=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q55=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R55=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S55=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T55=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U55=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X55=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y55=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z55=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB55=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC55=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH55=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK55" s="63"/>
-    </row>
-    <row r="56" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A56" s="40"/>
-      <c r="B56" s="67">
+      <c r="AK55" s="52"/>
+    </row>
+    <row r="56" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A56" s="31"/>
+      <c r="B56" s="56">
         <v>35</v>
       </c>
-      <c r="C56" s="68"/>
-      <c r="D56" s="68"/>
-      <c r="E56" s="68"/>
-      <c r="F56" s="68"/>
-      <c r="G56" s="69" t="str">
+      <c r="C56" s="57"/>
+      <c r="D56" s="57"/>
+      <c r="E56" s="57"/>
+      <c r="F56" s="57"/>
+      <c r="G56" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F56,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H56" s="68"/>
-      <c r="I56" s="70"/>
-      <c r="J56" s="68"/>
-      <c r="K56" s="70"/>
-      <c r="L56" s="70"/>
-      <c r="M56" s="70"/>
-      <c r="N56" s="70"/>
-      <c r="O56" s="70"/>
-      <c r="P56" s="70"/>
-      <c r="Q56" s="70"/>
-      <c r="R56" s="70"/>
-      <c r="S56" s="70"/>
-      <c r="T56" s="70"/>
-      <c r="U56" s="70"/>
-      <c r="V56" s="70"/>
-      <c r="W56" s="70"/>
-      <c r="X56" s="70"/>
-      <c r="Y56" s="70"/>
-      <c r="Z56" s="70"/>
-      <c r="AA56" s="70"/>
-      <c r="AB56" s="68"/>
-      <c r="AC56" s="68"/>
-      <c r="AD56" s="69" t="str">
+      <c r="H56" s="57"/>
+      <c r="I56" s="59"/>
+      <c r="J56" s="57"/>
+      <c r="K56" s="59"/>
+      <c r="L56" s="59"/>
+      <c r="M56" s="59"/>
+      <c r="N56" s="59"/>
+      <c r="O56" s="59"/>
+      <c r="P56" s="59"/>
+      <c r="Q56" s="59"/>
+      <c r="R56" s="59"/>
+      <c r="S56" s="59"/>
+      <c r="T56" s="59"/>
+      <c r="U56" s="59"/>
+      <c r="V56" s="59"/>
+      <c r="W56" s="59"/>
+      <c r="X56" s="59"/>
+      <c r="Y56" s="59"/>
+      <c r="Z56" s="59"/>
+      <c r="AA56" s="59"/>
+      <c r="AB56" s="57"/>
+      <c r="AC56" s="57"/>
+      <c r="AD56" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB56,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE56" s="68"/>
-      <c r="AF56" s="68"/>
-      <c r="AG56" s="71"/>
-      <c r="AH56" s="68"/>
-      <c r="AI56" s="72"/>
-      <c r="AJ56" s="73" t="str">
+      <c r="AE56" s="57"/>
+      <c r="AF56" s="57"/>
+      <c r="AG56" s="60"/>
+      <c r="AH56" s="57"/>
+      <c r="AI56" s="61"/>
+      <c r="AJ56" s="62" t="str">
         <f>IF(COUNTA(C56,D56,E56,F56,H56,I56,L56,M56,N56,P56,Q56,R56,S56,T56,U56,X56,Y56,Z56,AB56,AC56,AH56)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C56=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D56=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E56=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F56=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G56=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H56=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I56=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L56=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M56=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N56=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P56=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q56=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R56=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S56=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T56=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U56=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X56=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y56=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z56=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB56=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC56=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH56=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C56=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D56=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E56=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F56=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G56=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H56=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I56=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L56=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M56=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N56=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P56=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q56=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R56=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S56=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T56=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U56=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X56=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y56=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z56=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB56=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC56=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH56=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK56" s="63"/>
-    </row>
-    <row r="57" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="40"/>
-      <c r="B57" s="67">
+      <c r="AK56" s="52"/>
+    </row>
+    <row r="57" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A57" s="31"/>
+      <c r="B57" s="56">
         <v>36</v>
       </c>
-      <c r="C57" s="68"/>
-      <c r="D57" s="68"/>
-      <c r="E57" s="68"/>
-      <c r="F57" s="68"/>
-      <c r="G57" s="69" t="str">
+      <c r="C57" s="57"/>
+      <c r="D57" s="57"/>
+      <c r="E57" s="57"/>
+      <c r="F57" s="57"/>
+      <c r="G57" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F57,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H57" s="68"/>
-      <c r="I57" s="70"/>
-      <c r="J57" s="68"/>
-      <c r="K57" s="70"/>
-      <c r="L57" s="70"/>
-      <c r="M57" s="70"/>
-      <c r="N57" s="70"/>
-      <c r="O57" s="70"/>
-      <c r="P57" s="70"/>
-      <c r="Q57" s="70"/>
-      <c r="R57" s="70"/>
-      <c r="S57" s="70"/>
-      <c r="T57" s="70"/>
-      <c r="U57" s="70"/>
-      <c r="V57" s="70"/>
-      <c r="W57" s="70"/>
-      <c r="X57" s="70"/>
-      <c r="Y57" s="70"/>
-      <c r="Z57" s="70"/>
-      <c r="AA57" s="70"/>
-      <c r="AB57" s="68"/>
-      <c r="AC57" s="68"/>
-      <c r="AD57" s="69" t="str">
+      <c r="H57" s="57"/>
+      <c r="I57" s="59"/>
+      <c r="J57" s="57"/>
+      <c r="K57" s="59"/>
+      <c r="L57" s="59"/>
+      <c r="M57" s="59"/>
+      <c r="N57" s="59"/>
+      <c r="O57" s="59"/>
+      <c r="P57" s="59"/>
+      <c r="Q57" s="59"/>
+      <c r="R57" s="59"/>
+      <c r="S57" s="59"/>
+      <c r="T57" s="59"/>
+      <c r="U57" s="59"/>
+      <c r="V57" s="59"/>
+      <c r="W57" s="59"/>
+      <c r="X57" s="59"/>
+      <c r="Y57" s="59"/>
+      <c r="Z57" s="59"/>
+      <c r="AA57" s="59"/>
+      <c r="AB57" s="57"/>
+      <c r="AC57" s="57"/>
+      <c r="AD57" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB57,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE57" s="68"/>
-      <c r="AF57" s="68"/>
-      <c r="AG57" s="71"/>
-      <c r="AH57" s="68"/>
-      <c r="AI57" s="72"/>
-      <c r="AJ57" s="73" t="str">
+      <c r="AE57" s="57"/>
+      <c r="AF57" s="57"/>
+      <c r="AG57" s="60"/>
+      <c r="AH57" s="57"/>
+      <c r="AI57" s="61"/>
+      <c r="AJ57" s="62" t="str">
         <f>IF(COUNTA(C57,D57,E57,F57,H57,I57,L57,M57,N57,P57,Q57,R57,S57,T57,U57,X57,Y57,Z57,AB57,AC57,AH57)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C57=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D57=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E57=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F57=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G57=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H57=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I57=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L57=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M57=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N57=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P57=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q57=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R57=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S57=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T57=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U57=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X57=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y57=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z57=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB57=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC57=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH57=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C57=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D57=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E57=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F57=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G57=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H57=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I57=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L57=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M57=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N57=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P57=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q57=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R57=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S57=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T57=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U57=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X57=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y57=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z57=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB57=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC57=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH57=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK57" s="63"/>
-    </row>
-    <row r="58" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="40"/>
-      <c r="B58" s="67">
+      <c r="AK57" s="52"/>
+    </row>
+    <row r="58" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" s="31"/>
+      <c r="B58" s="56">
         <v>37</v>
       </c>
-      <c r="C58" s="68"/>
-      <c r="D58" s="68"/>
-      <c r="E58" s="68"/>
-      <c r="F58" s="68"/>
-      <c r="G58" s="69" t="str">
+      <c r="C58" s="57"/>
+      <c r="D58" s="57"/>
+      <c r="E58" s="57"/>
+      <c r="F58" s="57"/>
+      <c r="G58" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F58,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H58" s="68"/>
-      <c r="I58" s="70"/>
-      <c r="J58" s="68"/>
-      <c r="K58" s="70"/>
-      <c r="L58" s="70"/>
-      <c r="M58" s="70"/>
-      <c r="N58" s="70"/>
-      <c r="O58" s="70"/>
-      <c r="P58" s="70"/>
-      <c r="Q58" s="70"/>
-      <c r="R58" s="70"/>
-      <c r="S58" s="70"/>
-      <c r="T58" s="70"/>
-      <c r="U58" s="70"/>
-      <c r="V58" s="70"/>
-      <c r="W58" s="70"/>
-      <c r="X58" s="70"/>
-      <c r="Y58" s="70"/>
-      <c r="Z58" s="70"/>
-      <c r="AA58" s="70"/>
-      <c r="AB58" s="68"/>
-      <c r="AC58" s="68"/>
-      <c r="AD58" s="69" t="str">
+      <c r="H58" s="57"/>
+      <c r="I58" s="59"/>
+      <c r="J58" s="57"/>
+      <c r="K58" s="59"/>
+      <c r="L58" s="59"/>
+      <c r="M58" s="59"/>
+      <c r="N58" s="59"/>
+      <c r="O58" s="59"/>
+      <c r="P58" s="59"/>
+      <c r="Q58" s="59"/>
+      <c r="R58" s="59"/>
+      <c r="S58" s="59"/>
+      <c r="T58" s="59"/>
+      <c r="U58" s="59"/>
+      <c r="V58" s="59"/>
+      <c r="W58" s="59"/>
+      <c r="X58" s="59"/>
+      <c r="Y58" s="59"/>
+      <c r="Z58" s="59"/>
+      <c r="AA58" s="59"/>
+      <c r="AB58" s="57"/>
+      <c r="AC58" s="57"/>
+      <c r="AD58" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB58,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE58" s="68"/>
-      <c r="AF58" s="68"/>
-      <c r="AG58" s="71"/>
-      <c r="AH58" s="68"/>
-      <c r="AI58" s="72"/>
-      <c r="AJ58" s="73" t="str">
+      <c r="AE58" s="57"/>
+      <c r="AF58" s="57"/>
+      <c r="AG58" s="60"/>
+      <c r="AH58" s="57"/>
+      <c r="AI58" s="61"/>
+      <c r="AJ58" s="62" t="str">
         <f>IF(COUNTA(C58,D58,E58,F58,H58,I58,L58,M58,N58,P58,Q58,R58,S58,T58,U58,X58,Y58,Z58,AB58,AC58,AH58)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C58=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D58=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E58=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F58=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G58=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H58=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I58=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L58=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M58=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N58=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P58=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q58=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R58=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S58=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T58=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U58=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X58=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y58=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z58=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB58=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC58=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH58=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C58=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D58=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E58=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F58=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G58=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H58=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I58=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L58=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M58=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N58=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P58=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q58=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R58=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S58=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T58=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U58=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X58=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y58=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z58=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB58=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC58=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH58=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK58" s="63"/>
-    </row>
-    <row r="59" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A59" s="40"/>
-      <c r="B59" s="67">
+      <c r="AK58" s="52"/>
+    </row>
+    <row r="59" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A59" s="31"/>
+      <c r="B59" s="56">
         <v>38</v>
       </c>
-      <c r="C59" s="68"/>
-      <c r="D59" s="68"/>
-      <c r="E59" s="68"/>
-      <c r="F59" s="68"/>
-      <c r="G59" s="69" t="str">
+      <c r="C59" s="57"/>
+      <c r="D59" s="57"/>
+      <c r="E59" s="57"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F59,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H59" s="68"/>
-      <c r="I59" s="70"/>
-      <c r="J59" s="68"/>
-      <c r="K59" s="70"/>
-      <c r="L59" s="70"/>
-      <c r="M59" s="70"/>
-      <c r="N59" s="70"/>
-      <c r="O59" s="70"/>
-      <c r="P59" s="70"/>
-      <c r="Q59" s="70"/>
-      <c r="R59" s="70"/>
-      <c r="S59" s="70"/>
-      <c r="T59" s="70"/>
-      <c r="U59" s="70"/>
-      <c r="V59" s="70"/>
-      <c r="W59" s="70"/>
-      <c r="X59" s="70"/>
-      <c r="Y59" s="70"/>
-      <c r="Z59" s="70"/>
-      <c r="AA59" s="70"/>
-      <c r="AB59" s="68"/>
-      <c r="AC59" s="68"/>
-      <c r="AD59" s="69" t="str">
+      <c r="H59" s="57"/>
+      <c r="I59" s="59"/>
+      <c r="J59" s="57"/>
+      <c r="K59" s="59"/>
+      <c r="L59" s="59"/>
+      <c r="M59" s="59"/>
+      <c r="N59" s="59"/>
+      <c r="O59" s="59"/>
+      <c r="P59" s="59"/>
+      <c r="Q59" s="59"/>
+      <c r="R59" s="59"/>
+      <c r="S59" s="59"/>
+      <c r="T59" s="59"/>
+      <c r="U59" s="59"/>
+      <c r="V59" s="59"/>
+      <c r="W59" s="59"/>
+      <c r="X59" s="59"/>
+      <c r="Y59" s="59"/>
+      <c r="Z59" s="59"/>
+      <c r="AA59" s="59"/>
+      <c r="AB59" s="57"/>
+      <c r="AC59" s="57"/>
+      <c r="AD59" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB59,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE59" s="68"/>
-      <c r="AF59" s="68"/>
-      <c r="AG59" s="71"/>
-      <c r="AH59" s="68"/>
-      <c r="AI59" s="72"/>
-      <c r="AJ59" s="73" t="str">
+      <c r="AE59" s="57"/>
+      <c r="AF59" s="57"/>
+      <c r="AG59" s="60"/>
+      <c r="AH59" s="57"/>
+      <c r="AI59" s="61"/>
+      <c r="AJ59" s="62" t="str">
         <f>IF(COUNTA(C59,D59,E59,F59,H59,I59,L59,M59,N59,P59,Q59,R59,S59,T59,U59,X59,Y59,Z59,AB59,AC59,AH59)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C59=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D59=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E59=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F59=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G59=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H59=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I59=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L59=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M59=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N59=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P59=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q59=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R59=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S59=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T59=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U59=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X59=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y59=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z59=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB59=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC59=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH59=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C59=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D59=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E59=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F59=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G59=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H59=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I59=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L59=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M59=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N59=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P59=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q59=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R59=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S59=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T59=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U59=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X59=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y59=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z59=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB59=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC59=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH59=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK59" s="63"/>
-    </row>
-    <row r="60" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="40"/>
-      <c r="B60" s="67">
+      <c r="AK59" s="52"/>
+    </row>
+    <row r="60" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A60" s="31"/>
+      <c r="B60" s="56">
         <v>39</v>
       </c>
-      <c r="C60" s="68"/>
-      <c r="D60" s="68"/>
-      <c r="E60" s="68"/>
-      <c r="F60" s="68"/>
-      <c r="G60" s="69" t="str">
+      <c r="C60" s="57"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="57"/>
+      <c r="G60" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F60,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H60" s="68"/>
-      <c r="I60" s="70"/>
-      <c r="J60" s="68"/>
-      <c r="K60" s="70"/>
-      <c r="L60" s="70"/>
-      <c r="M60" s="70"/>
-      <c r="N60" s="70"/>
-      <c r="O60" s="70"/>
-      <c r="P60" s="70"/>
-      <c r="Q60" s="70"/>
-      <c r="R60" s="70"/>
-      <c r="S60" s="70"/>
-      <c r="T60" s="70"/>
-      <c r="U60" s="70"/>
-      <c r="V60" s="70"/>
-      <c r="W60" s="70"/>
-      <c r="X60" s="70"/>
-      <c r="Y60" s="70"/>
-      <c r="Z60" s="70"/>
-      <c r="AA60" s="70"/>
-      <c r="AB60" s="68"/>
-      <c r="AC60" s="68"/>
-      <c r="AD60" s="69" t="str">
+      <c r="H60" s="57"/>
+      <c r="I60" s="59"/>
+      <c r="J60" s="57"/>
+      <c r="K60" s="59"/>
+      <c r="L60" s="59"/>
+      <c r="M60" s="59"/>
+      <c r="N60" s="59"/>
+      <c r="O60" s="59"/>
+      <c r="P60" s="59"/>
+      <c r="Q60" s="59"/>
+      <c r="R60" s="59"/>
+      <c r="S60" s="59"/>
+      <c r="T60" s="59"/>
+      <c r="U60" s="59"/>
+      <c r="V60" s="59"/>
+      <c r="W60" s="59"/>
+      <c r="X60" s="59"/>
+      <c r="Y60" s="59"/>
+      <c r="Z60" s="59"/>
+      <c r="AA60" s="59"/>
+      <c r="AB60" s="57"/>
+      <c r="AC60" s="57"/>
+      <c r="AD60" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB60,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE60" s="68"/>
-      <c r="AF60" s="68"/>
-      <c r="AG60" s="71"/>
-      <c r="AH60" s="68"/>
-      <c r="AI60" s="72"/>
-      <c r="AJ60" s="73" t="str">
+      <c r="AE60" s="57"/>
+      <c r="AF60" s="57"/>
+      <c r="AG60" s="60"/>
+      <c r="AH60" s="57"/>
+      <c r="AI60" s="61"/>
+      <c r="AJ60" s="62" t="str">
         <f>IF(COUNTA(C60,D60,E60,F60,H60,I60,L60,M60,N60,P60,Q60,R60,S60,T60,U60,X60,Y60,Z60,AB60,AC60,AH60)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C60=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D60=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E60=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F60=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G60=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H60=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I60=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L60=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M60=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N60=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P60=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q60=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R60=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S60=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T60=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U60=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X60=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y60=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z60=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB60=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC60=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH60=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C60=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D60=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E60=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F60=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G60=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H60=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I60=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L60=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M60=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N60=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P60=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q60=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R60=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S60=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T60=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U60=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X60=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y60=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z60=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB60=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC60=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH60=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK60" s="63"/>
-    </row>
-    <row r="61" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A61" s="40"/>
-      <c r="B61" s="67">
+      <c r="AK60" s="52"/>
+    </row>
+    <row r="61" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A61" s="31"/>
+      <c r="B61" s="56">
         <v>40</v>
       </c>
-      <c r="C61" s="68"/>
-      <c r="D61" s="68"/>
-      <c r="E61" s="68"/>
-      <c r="F61" s="68"/>
-      <c r="G61" s="69" t="str">
+      <c r="C61" s="57"/>
+      <c r="D61" s="57"/>
+      <c r="E61" s="57"/>
+      <c r="F61" s="57"/>
+      <c r="G61" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F61,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H61" s="68"/>
-      <c r="I61" s="70"/>
-      <c r="J61" s="68"/>
-      <c r="K61" s="70"/>
-      <c r="L61" s="70"/>
-      <c r="M61" s="70"/>
-      <c r="N61" s="70"/>
-      <c r="O61" s="70"/>
-      <c r="P61" s="70"/>
-      <c r="Q61" s="70"/>
-      <c r="R61" s="70"/>
-      <c r="S61" s="70"/>
-      <c r="T61" s="70"/>
-      <c r="U61" s="70"/>
-      <c r="V61" s="70"/>
-      <c r="W61" s="70"/>
-      <c r="X61" s="70"/>
-      <c r="Y61" s="70"/>
-      <c r="Z61" s="70"/>
-      <c r="AA61" s="70"/>
-      <c r="AB61" s="68"/>
-      <c r="AC61" s="68"/>
-      <c r="AD61" s="69" t="str">
+      <c r="H61" s="57"/>
+      <c r="I61" s="59"/>
+      <c r="J61" s="57"/>
+      <c r="K61" s="59"/>
+      <c r="L61" s="59"/>
+      <c r="M61" s="59"/>
+      <c r="N61" s="59"/>
+      <c r="O61" s="59"/>
+      <c r="P61" s="59"/>
+      <c r="Q61" s="59"/>
+      <c r="R61" s="59"/>
+      <c r="S61" s="59"/>
+      <c r="T61" s="59"/>
+      <c r="U61" s="59"/>
+      <c r="V61" s="59"/>
+      <c r="W61" s="59"/>
+      <c r="X61" s="59"/>
+      <c r="Y61" s="59"/>
+      <c r="Z61" s="59"/>
+      <c r="AA61" s="59"/>
+      <c r="AB61" s="57"/>
+      <c r="AC61" s="57"/>
+      <c r="AD61" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB61,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE61" s="68"/>
-      <c r="AF61" s="68"/>
-      <c r="AG61" s="71"/>
-      <c r="AH61" s="68"/>
-      <c r="AI61" s="72"/>
-      <c r="AJ61" s="73" t="str">
+      <c r="AE61" s="57"/>
+      <c r="AF61" s="57"/>
+      <c r="AG61" s="60"/>
+      <c r="AH61" s="57"/>
+      <c r="AI61" s="61"/>
+      <c r="AJ61" s="62" t="str">
         <f>IF(COUNTA(C61,D61,E61,F61,H61,I61,L61,M61,N61,P61,Q61,R61,S61,T61,U61,X61,Y61,Z61,AB61,AC61,AH61)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C61=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D61=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E61=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F61=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G61=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H61=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I61=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L61=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M61=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N61=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P61=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q61=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R61=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S61=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T61=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U61=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X61=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y61=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z61=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB61=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC61=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH61=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C61=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D61=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E61=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F61=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G61=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H61=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I61=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L61=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M61=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N61=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P61=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q61=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R61=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S61=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T61=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U61=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X61=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y61=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z61=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB61=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC61=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH61=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK61" s="63"/>
-    </row>
-    <row r="62" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A62" s="40"/>
-      <c r="B62" s="67">
+      <c r="AK61" s="52"/>
+    </row>
+    <row r="62" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A62" s="31"/>
+      <c r="B62" s="56">
         <v>41</v>
       </c>
-      <c r="C62" s="68"/>
-      <c r="D62" s="68"/>
-      <c r="E62" s="68"/>
-      <c r="F62" s="68"/>
-      <c r="G62" s="69" t="str">
+      <c r="C62" s="57"/>
+      <c r="D62" s="57"/>
+      <c r="E62" s="57"/>
+      <c r="F62" s="57"/>
+      <c r="G62" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F62,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H62" s="68"/>
-      <c r="I62" s="70"/>
-      <c r="J62" s="68"/>
-      <c r="K62" s="70"/>
-      <c r="L62" s="70"/>
-      <c r="M62" s="70"/>
-      <c r="N62" s="70"/>
-      <c r="O62" s="70"/>
-      <c r="P62" s="70"/>
-      <c r="Q62" s="70"/>
-      <c r="R62" s="70"/>
-      <c r="S62" s="70"/>
-      <c r="T62" s="70"/>
-      <c r="U62" s="70"/>
-      <c r="V62" s="70"/>
-      <c r="W62" s="70"/>
-      <c r="X62" s="70"/>
-      <c r="Y62" s="70"/>
-      <c r="Z62" s="70"/>
-      <c r="AA62" s="70"/>
-      <c r="AB62" s="68"/>
-      <c r="AC62" s="68"/>
-      <c r="AD62" s="69" t="str">
+      <c r="H62" s="57"/>
+      <c r="I62" s="59"/>
+      <c r="J62" s="57"/>
+      <c r="K62" s="59"/>
+      <c r="L62" s="59"/>
+      <c r="M62" s="59"/>
+      <c r="N62" s="59"/>
+      <c r="O62" s="59"/>
+      <c r="P62" s="59"/>
+      <c r="Q62" s="59"/>
+      <c r="R62" s="59"/>
+      <c r="S62" s="59"/>
+      <c r="T62" s="59"/>
+      <c r="U62" s="59"/>
+      <c r="V62" s="59"/>
+      <c r="W62" s="59"/>
+      <c r="X62" s="59"/>
+      <c r="Y62" s="59"/>
+      <c r="Z62" s="59"/>
+      <c r="AA62" s="59"/>
+      <c r="AB62" s="57"/>
+      <c r="AC62" s="57"/>
+      <c r="AD62" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB62,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE62" s="68"/>
-      <c r="AF62" s="68"/>
-      <c r="AG62" s="71"/>
-      <c r="AH62" s="68"/>
-      <c r="AI62" s="72"/>
-      <c r="AJ62" s="73" t="str">
+      <c r="AE62" s="57"/>
+      <c r="AF62" s="57"/>
+      <c r="AG62" s="60"/>
+      <c r="AH62" s="57"/>
+      <c r="AI62" s="61"/>
+      <c r="AJ62" s="62" t="str">
         <f>IF(COUNTA(C62,D62,E62,F62,H62,I62,L62,M62,N62,P62,Q62,R62,S62,T62,U62,X62,Y62,Z62,AB62,AC62,AH62)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C62=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D62=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E62=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F62=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G62=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H62=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I62=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L62=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M62=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N62=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P62=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q62=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R62=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S62=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T62=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U62=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X62=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y62=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z62=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB62=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC62=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH62=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C62=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D62=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E62=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F62=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G62=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H62=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I62=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L62=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M62=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N62=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P62=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q62=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R62=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S62=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T62=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U62=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X62=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y62=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z62=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB62=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC62=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH62=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK62" s="63"/>
-    </row>
-    <row r="63" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A63" s="40"/>
-      <c r="B63" s="67">
+      <c r="AK62" s="52"/>
+    </row>
+    <row r="63" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A63" s="31"/>
+      <c r="B63" s="56">
         <v>42</v>
       </c>
-      <c r="C63" s="68"/>
-      <c r="D63" s="68"/>
-      <c r="E63" s="68"/>
-      <c r="F63" s="68"/>
-      <c r="G63" s="69" t="str">
+      <c r="C63" s="57"/>
+      <c r="D63" s="57"/>
+      <c r="E63" s="57"/>
+      <c r="F63" s="57"/>
+      <c r="G63" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F63,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H63" s="68"/>
-      <c r="I63" s="70"/>
-      <c r="J63" s="68"/>
-      <c r="K63" s="70"/>
-      <c r="L63" s="70"/>
-      <c r="M63" s="70"/>
-      <c r="N63" s="70"/>
-      <c r="O63" s="70"/>
-      <c r="P63" s="70"/>
-      <c r="Q63" s="70"/>
-      <c r="R63" s="70"/>
-      <c r="S63" s="70"/>
-      <c r="T63" s="70"/>
-      <c r="U63" s="70"/>
-      <c r="V63" s="70"/>
-      <c r="W63" s="70"/>
-      <c r="X63" s="70"/>
-      <c r="Y63" s="70"/>
-      <c r="Z63" s="70"/>
-      <c r="AA63" s="70"/>
-      <c r="AB63" s="68"/>
-      <c r="AC63" s="68"/>
-      <c r="AD63" s="69" t="str">
+      <c r="H63" s="57"/>
+      <c r="I63" s="59"/>
+      <c r="J63" s="57"/>
+      <c r="K63" s="59"/>
+      <c r="L63" s="59"/>
+      <c r="M63" s="59"/>
+      <c r="N63" s="59"/>
+      <c r="O63" s="59"/>
+      <c r="P63" s="59"/>
+      <c r="Q63" s="59"/>
+      <c r="R63" s="59"/>
+      <c r="S63" s="59"/>
+      <c r="T63" s="59"/>
+      <c r="U63" s="59"/>
+      <c r="V63" s="59"/>
+      <c r="W63" s="59"/>
+      <c r="X63" s="59"/>
+      <c r="Y63" s="59"/>
+      <c r="Z63" s="59"/>
+      <c r="AA63" s="59"/>
+      <c r="AB63" s="57"/>
+      <c r="AC63" s="57"/>
+      <c r="AD63" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB63,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE63" s="68"/>
-      <c r="AF63" s="68"/>
-      <c r="AG63" s="71"/>
-      <c r="AH63" s="68"/>
-      <c r="AI63" s="72"/>
-      <c r="AJ63" s="73" t="str">
+      <c r="AE63" s="57"/>
+      <c r="AF63" s="57"/>
+      <c r="AG63" s="60"/>
+      <c r="AH63" s="57"/>
+      <c r="AI63" s="61"/>
+      <c r="AJ63" s="62" t="str">
         <f>IF(COUNTA(C63,D63,E63,F63,H63,I63,L63,M63,N63,P63,Q63,R63,S63,T63,U63,X63,Y63,Z63,AB63,AC63,AH63)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C63=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D63=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E63=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F63=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G63=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H63=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I63=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L63=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M63=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N63=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P63=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q63=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R63=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S63=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T63=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U63=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X63=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y63=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z63=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB63=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC63=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH63=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C63=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D63=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E63=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F63=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G63=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H63=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I63=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L63=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M63=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N63=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P63=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q63=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R63=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S63=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T63=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U63=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X63=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y63=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z63=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB63=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC63=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH63=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK63" s="63"/>
-    </row>
-    <row r="64" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A64" s="40"/>
-      <c r="B64" s="67">
+      <c r="AK63" s="52"/>
+    </row>
+    <row r="64" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A64" s="31"/>
+      <c r="B64" s="56">
         <v>43</v>
       </c>
-      <c r="C64" s="68"/>
-      <c r="D64" s="68"/>
-      <c r="E64" s="68"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="69" t="str">
+      <c r="C64" s="57"/>
+      <c r="D64" s="57"/>
+      <c r="E64" s="57"/>
+      <c r="F64" s="57"/>
+      <c r="G64" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F64,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H64" s="68"/>
-      <c r="I64" s="70"/>
-      <c r="J64" s="68"/>
-      <c r="K64" s="70"/>
-      <c r="L64" s="70"/>
-      <c r="M64" s="70"/>
-      <c r="N64" s="70"/>
-      <c r="O64" s="70"/>
-      <c r="P64" s="70"/>
-      <c r="Q64" s="70"/>
-      <c r="R64" s="70"/>
-      <c r="S64" s="70"/>
-      <c r="T64" s="70"/>
-      <c r="U64" s="70"/>
-      <c r="V64" s="70"/>
-      <c r="W64" s="70"/>
-      <c r="X64" s="70"/>
-      <c r="Y64" s="70"/>
-      <c r="Z64" s="70"/>
-      <c r="AA64" s="70"/>
-      <c r="AB64" s="68"/>
-      <c r="AC64" s="68"/>
-      <c r="AD64" s="69" t="str">
+      <c r="H64" s="57"/>
+      <c r="I64" s="59"/>
+      <c r="J64" s="57"/>
+      <c r="K64" s="59"/>
+      <c r="L64" s="59"/>
+      <c r="M64" s="59"/>
+      <c r="N64" s="59"/>
+      <c r="O64" s="59"/>
+      <c r="P64" s="59"/>
+      <c r="Q64" s="59"/>
+      <c r="R64" s="59"/>
+      <c r="S64" s="59"/>
+      <c r="T64" s="59"/>
+      <c r="U64" s="59"/>
+      <c r="V64" s="59"/>
+      <c r="W64" s="59"/>
+      <c r="X64" s="59"/>
+      <c r="Y64" s="59"/>
+      <c r="Z64" s="59"/>
+      <c r="AA64" s="59"/>
+      <c r="AB64" s="57"/>
+      <c r="AC64" s="57"/>
+      <c r="AD64" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB64,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE64" s="68"/>
-      <c r="AF64" s="68"/>
-      <c r="AG64" s="71"/>
-      <c r="AH64" s="68"/>
-      <c r="AI64" s="72"/>
-      <c r="AJ64" s="73" t="str">
+      <c r="AE64" s="57"/>
+      <c r="AF64" s="57"/>
+      <c r="AG64" s="60"/>
+      <c r="AH64" s="57"/>
+      <c r="AI64" s="61"/>
+      <c r="AJ64" s="62" t="str">
         <f>IF(COUNTA(C64,D64,E64,F64,H64,I64,L64,M64,N64,P64,Q64,R64,S64,T64,U64,X64,Y64,Z64,AB64,AC64,AH64)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C64=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D64=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E64=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F64=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G64=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H64=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I64=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L64=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M64=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N64=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P64=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q64=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R64=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S64=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T64=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U64=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X64=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y64=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z64=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB64=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC64=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH64=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C64=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D64=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E64=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F64=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G64=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H64=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I64=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L64=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M64=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N64=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P64=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q64=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R64=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S64=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T64=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U64=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X64=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y64=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z64=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB64=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC64=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH64=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK64" s="63"/>
-    </row>
-    <row r="65" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A65" s="40"/>
-      <c r="B65" s="67">
+      <c r="AK64" s="52"/>
+    </row>
+    <row r="65" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A65" s="31"/>
+      <c r="B65" s="56">
         <v>44</v>
       </c>
-      <c r="C65" s="68"/>
-      <c r="D65" s="68"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="68"/>
-      <c r="G65" s="69" t="str">
+      <c r="C65" s="57"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="57"/>
+      <c r="F65" s="57"/>
+      <c r="G65" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F65,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H65" s="68"/>
-      <c r="I65" s="70"/>
-      <c r="J65" s="68"/>
-      <c r="K65" s="70"/>
-      <c r="L65" s="70"/>
-      <c r="M65" s="70"/>
-      <c r="N65" s="70"/>
-      <c r="O65" s="70"/>
-      <c r="P65" s="70"/>
-      <c r="Q65" s="70"/>
-      <c r="R65" s="70"/>
-      <c r="S65" s="70"/>
-      <c r="T65" s="70"/>
-      <c r="U65" s="70"/>
-      <c r="V65" s="70"/>
-      <c r="W65" s="70"/>
-      <c r="X65" s="70"/>
-      <c r="Y65" s="70"/>
-      <c r="Z65" s="70"/>
-      <c r="AA65" s="70"/>
-      <c r="AB65" s="68"/>
-      <c r="AC65" s="68"/>
-      <c r="AD65" s="69" t="str">
+      <c r="H65" s="57"/>
+      <c r="I65" s="59"/>
+      <c r="J65" s="57"/>
+      <c r="K65" s="59"/>
+      <c r="L65" s="59"/>
+      <c r="M65" s="59"/>
+      <c r="N65" s="59"/>
+      <c r="O65" s="59"/>
+      <c r="P65" s="59"/>
+      <c r="Q65" s="59"/>
+      <c r="R65" s="59"/>
+      <c r="S65" s="59"/>
+      <c r="T65" s="59"/>
+      <c r="U65" s="59"/>
+      <c r="V65" s="59"/>
+      <c r="W65" s="59"/>
+      <c r="X65" s="59"/>
+      <c r="Y65" s="59"/>
+      <c r="Z65" s="59"/>
+      <c r="AA65" s="59"/>
+      <c r="AB65" s="57"/>
+      <c r="AC65" s="57"/>
+      <c r="AD65" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB65,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE65" s="68"/>
-      <c r="AF65" s="68"/>
-      <c r="AG65" s="71"/>
-      <c r="AH65" s="68"/>
-      <c r="AI65" s="72"/>
-      <c r="AJ65" s="73" t="str">
+      <c r="AE65" s="57"/>
+      <c r="AF65" s="57"/>
+      <c r="AG65" s="60"/>
+      <c r="AH65" s="57"/>
+      <c r="AI65" s="61"/>
+      <c r="AJ65" s="62" t="str">
         <f>IF(COUNTA(C65,D65,E65,F65,H65,I65,L65,M65,N65,P65,Q65,R65,S65,T65,U65,X65,Y65,Z65,AB65,AC65,AH65)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C65=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D65=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E65=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F65=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G65=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H65=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I65=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L65=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M65=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N65=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P65=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q65=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R65=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S65=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T65=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U65=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X65=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y65=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z65=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB65=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC65=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH65=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C65=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D65=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E65=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F65=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G65=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H65=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I65=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L65=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M65=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N65=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P65=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q65=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R65=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S65=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T65=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U65=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X65=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y65=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z65=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB65=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC65=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH65=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK65" s="63"/>
-    </row>
-    <row r="66" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A66" s="40"/>
-      <c r="B66" s="67">
+      <c r="AK65" s="52"/>
+    </row>
+    <row r="66" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A66" s="31"/>
+      <c r="B66" s="56">
         <v>45</v>
       </c>
-      <c r="C66" s="68"/>
-      <c r="D66" s="68"/>
-      <c r="E66" s="68"/>
-      <c r="F66" s="68"/>
-      <c r="G66" s="69" t="str">
+      <c r="C66" s="57"/>
+      <c r="D66" s="57"/>
+      <c r="E66" s="57"/>
+      <c r="F66" s="57"/>
+      <c r="G66" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F66,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H66" s="68"/>
-      <c r="I66" s="70"/>
-      <c r="J66" s="68"/>
-      <c r="K66" s="70"/>
-      <c r="L66" s="70"/>
-      <c r="M66" s="70"/>
-      <c r="N66" s="70"/>
-      <c r="O66" s="70"/>
-      <c r="P66" s="70"/>
-      <c r="Q66" s="70"/>
-      <c r="R66" s="70"/>
-      <c r="S66" s="70"/>
-      <c r="T66" s="70"/>
-      <c r="U66" s="70"/>
-      <c r="V66" s="70"/>
-      <c r="W66" s="70"/>
-      <c r="X66" s="70"/>
-      <c r="Y66" s="70"/>
-      <c r="Z66" s="70"/>
-      <c r="AA66" s="70"/>
-      <c r="AB66" s="68"/>
-      <c r="AC66" s="68"/>
-      <c r="AD66" s="69" t="str">
+      <c r="H66" s="57"/>
+      <c r="I66" s="59"/>
+      <c r="J66" s="57"/>
+      <c r="K66" s="59"/>
+      <c r="L66" s="59"/>
+      <c r="M66" s="59"/>
+      <c r="N66" s="59"/>
+      <c r="O66" s="59"/>
+      <c r="P66" s="59"/>
+      <c r="Q66" s="59"/>
+      <c r="R66" s="59"/>
+      <c r="S66" s="59"/>
+      <c r="T66" s="59"/>
+      <c r="U66" s="59"/>
+      <c r="V66" s="59"/>
+      <c r="W66" s="59"/>
+      <c r="X66" s="59"/>
+      <c r="Y66" s="59"/>
+      <c r="Z66" s="59"/>
+      <c r="AA66" s="59"/>
+      <c r="AB66" s="57"/>
+      <c r="AC66" s="57"/>
+      <c r="AD66" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB66,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE66" s="68"/>
-      <c r="AF66" s="68"/>
-      <c r="AG66" s="71"/>
-      <c r="AH66" s="68"/>
-      <c r="AI66" s="72"/>
-      <c r="AJ66" s="73" t="str">
+      <c r="AE66" s="57"/>
+      <c r="AF66" s="57"/>
+      <c r="AG66" s="60"/>
+      <c r="AH66" s="57"/>
+      <c r="AI66" s="61"/>
+      <c r="AJ66" s="62" t="str">
         <f>IF(COUNTA(C66,D66,E66,F66,H66,I66,L66,M66,N66,P66,Q66,R66,S66,T66,U66,X66,Y66,Z66,AB66,AC66,AH66)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C66=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D66=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E66=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F66=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G66=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H66=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I66=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L66=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M66=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N66=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P66=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q66=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R66=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S66=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T66=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U66=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X66=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y66=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z66=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB66=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC66=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH66=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C66=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D66=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E66=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F66=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G66=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H66=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I66=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L66=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M66=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N66=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P66=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q66=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R66=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S66=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T66=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U66=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X66=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y66=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z66=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB66=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC66=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH66=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK66" s="63"/>
-    </row>
-    <row r="67" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A67" s="40"/>
-      <c r="B67" s="67">
+      <c r="AK66" s="52"/>
+    </row>
+    <row r="67" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A67" s="31"/>
+      <c r="B67" s="56">
         <v>46</v>
       </c>
-      <c r="C67" s="68"/>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="69" t="str">
+      <c r="C67" s="57"/>
+      <c r="D67" s="57"/>
+      <c r="E67" s="57"/>
+      <c r="F67" s="57"/>
+      <c r="G67" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F67,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H67" s="68"/>
-      <c r="I67" s="70"/>
-      <c r="J67" s="68"/>
-      <c r="K67" s="70"/>
-      <c r="L67" s="70"/>
-      <c r="M67" s="70"/>
-      <c r="N67" s="70"/>
-      <c r="O67" s="70"/>
-      <c r="P67" s="70"/>
-      <c r="Q67" s="70"/>
-      <c r="R67" s="70"/>
-      <c r="S67" s="70"/>
-      <c r="T67" s="70"/>
-      <c r="U67" s="70"/>
-      <c r="V67" s="70"/>
-      <c r="W67" s="70"/>
-      <c r="X67" s="70"/>
-      <c r="Y67" s="70"/>
-      <c r="Z67" s="70"/>
-      <c r="AA67" s="70"/>
-      <c r="AB67" s="68"/>
-      <c r="AC67" s="68"/>
-      <c r="AD67" s="69" t="str">
+      <c r="H67" s="57"/>
+      <c r="I67" s="59"/>
+      <c r="J67" s="57"/>
+      <c r="K67" s="59"/>
+      <c r="L67" s="59"/>
+      <c r="M67" s="59"/>
+      <c r="N67" s="59"/>
+      <c r="O67" s="59"/>
+      <c r="P67" s="59"/>
+      <c r="Q67" s="59"/>
+      <c r="R67" s="59"/>
+      <c r="S67" s="59"/>
+      <c r="T67" s="59"/>
+      <c r="U67" s="59"/>
+      <c r="V67" s="59"/>
+      <c r="W67" s="59"/>
+      <c r="X67" s="59"/>
+      <c r="Y67" s="59"/>
+      <c r="Z67" s="59"/>
+      <c r="AA67" s="59"/>
+      <c r="AB67" s="57"/>
+      <c r="AC67" s="57"/>
+      <c r="AD67" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB67,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE67" s="68"/>
-      <c r="AF67" s="68"/>
-      <c r="AG67" s="71"/>
-      <c r="AH67" s="68"/>
-      <c r="AI67" s="72"/>
-      <c r="AJ67" s="73" t="str">
+      <c r="AE67" s="57"/>
+      <c r="AF67" s="57"/>
+      <c r="AG67" s="60"/>
+      <c r="AH67" s="57"/>
+      <c r="AI67" s="61"/>
+      <c r="AJ67" s="62" t="str">
         <f>IF(COUNTA(C67,D67,E67,F67,H67,I67,L67,M67,N67,P67,Q67,R67,S67,T67,U67,X67,Y67,Z67,AB67,AC67,AH67)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C67=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D67=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E67=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F67=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G67=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H67=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I67=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L67=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M67=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N67=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P67=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q67=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R67=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S67=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T67=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U67=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X67=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y67=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z67=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB67=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC67=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH67=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C67=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D67=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E67=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F67=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G67=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H67=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I67=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L67=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M67=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N67=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P67=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q67=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R67=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S67=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T67=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U67=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X67=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y67=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z67=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB67=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC67=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH67=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK67" s="63"/>
-    </row>
-    <row r="68" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A68" s="40"/>
-      <c r="B68" s="67">
+      <c r="AK67" s="52"/>
+    </row>
+    <row r="68" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A68" s="31"/>
+      <c r="B68" s="56">
         <v>47</v>
       </c>
-      <c r="C68" s="68"/>
-      <c r="D68" s="68"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="69" t="str">
+      <c r="C68" s="57"/>
+      <c r="D68" s="57"/>
+      <c r="E68" s="57"/>
+      <c r="F68" s="57"/>
+      <c r="G68" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F68,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H68" s="68"/>
-      <c r="I68" s="70"/>
-      <c r="J68" s="68"/>
-      <c r="K68" s="70"/>
-      <c r="L68" s="70"/>
-      <c r="M68" s="70"/>
-      <c r="N68" s="70"/>
-      <c r="O68" s="70"/>
-      <c r="P68" s="70"/>
-      <c r="Q68" s="70"/>
-      <c r="R68" s="70"/>
-      <c r="S68" s="70"/>
-      <c r="T68" s="70"/>
-      <c r="U68" s="70"/>
-      <c r="V68" s="70"/>
-      <c r="W68" s="70"/>
-      <c r="X68" s="70"/>
-      <c r="Y68" s="70"/>
-      <c r="Z68" s="70"/>
-      <c r="AA68" s="70"/>
-      <c r="AB68" s="68"/>
-      <c r="AC68" s="68"/>
-      <c r="AD68" s="69" t="str">
+      <c r="H68" s="57"/>
+      <c r="I68" s="59"/>
+      <c r="J68" s="57"/>
+      <c r="K68" s="59"/>
+      <c r="L68" s="59"/>
+      <c r="M68" s="59"/>
+      <c r="N68" s="59"/>
+      <c r="O68" s="59"/>
+      <c r="P68" s="59"/>
+      <c r="Q68" s="59"/>
+      <c r="R68" s="59"/>
+      <c r="S68" s="59"/>
+      <c r="T68" s="59"/>
+      <c r="U68" s="59"/>
+      <c r="V68" s="59"/>
+      <c r="W68" s="59"/>
+      <c r="X68" s="59"/>
+      <c r="Y68" s="59"/>
+      <c r="Z68" s="59"/>
+      <c r="AA68" s="59"/>
+      <c r="AB68" s="57"/>
+      <c r="AC68" s="57"/>
+      <c r="AD68" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB68,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE68" s="68"/>
-      <c r="AF68" s="68"/>
-      <c r="AG68" s="71"/>
-      <c r="AH68" s="68"/>
-      <c r="AI68" s="72"/>
-      <c r="AJ68" s="73" t="str">
+      <c r="AE68" s="57"/>
+      <c r="AF68" s="57"/>
+      <c r="AG68" s="60"/>
+      <c r="AH68" s="57"/>
+      <c r="AI68" s="61"/>
+      <c r="AJ68" s="62" t="str">
         <f>IF(COUNTA(C68,D68,E68,F68,H68,I68,L68,M68,N68,P68,Q68,R68,S68,T68,U68,X68,Y68,Z68,AB68,AC68,AH68)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C68=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D68=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E68=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F68=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G68=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H68=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I68=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L68=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M68=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N68=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P68=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q68=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R68=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S68=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T68=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U68=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X68=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y68=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z68=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB68=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC68=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH68=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C68=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D68=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E68=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F68=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G68=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H68=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I68=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L68=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M68=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N68=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P68=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q68=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R68=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S68=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T68=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U68=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X68=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y68=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z68=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB68=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC68=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH68=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK68" s="63"/>
-    </row>
-    <row r="69" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A69" s="40"/>
-      <c r="B69" s="67">
+      <c r="AK68" s="52"/>
+    </row>
+    <row r="69" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A69" s="31"/>
+      <c r="B69" s="56">
         <v>48</v>
       </c>
-      <c r="C69" s="68"/>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="68"/>
-      <c r="G69" s="69" t="str">
+      <c r="C69" s="57"/>
+      <c r="D69" s="57"/>
+      <c r="E69" s="57"/>
+      <c r="F69" s="57"/>
+      <c r="G69" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F69,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H69" s="68"/>
-      <c r="I69" s="70"/>
-      <c r="J69" s="68"/>
-      <c r="K69" s="70"/>
-      <c r="L69" s="70"/>
-      <c r="M69" s="70"/>
-      <c r="N69" s="70"/>
-      <c r="O69" s="70"/>
-      <c r="P69" s="70"/>
-      <c r="Q69" s="70"/>
-      <c r="R69" s="70"/>
-      <c r="S69" s="70"/>
-      <c r="T69" s="70"/>
-      <c r="U69" s="70"/>
-      <c r="V69" s="70"/>
-      <c r="W69" s="70"/>
-      <c r="X69" s="70"/>
-      <c r="Y69" s="70"/>
-      <c r="Z69" s="70"/>
-      <c r="AA69" s="70"/>
-      <c r="AB69" s="68"/>
-      <c r="AC69" s="68"/>
-      <c r="AD69" s="69" t="str">
+      <c r="H69" s="57"/>
+      <c r="I69" s="59"/>
+      <c r="J69" s="57"/>
+      <c r="K69" s="59"/>
+      <c r="L69" s="59"/>
+      <c r="M69" s="59"/>
+      <c r="N69" s="59"/>
+      <c r="O69" s="59"/>
+      <c r="P69" s="59"/>
+      <c r="Q69" s="59"/>
+      <c r="R69" s="59"/>
+      <c r="S69" s="59"/>
+      <c r="T69" s="59"/>
+      <c r="U69" s="59"/>
+      <c r="V69" s="59"/>
+      <c r="W69" s="59"/>
+      <c r="X69" s="59"/>
+      <c r="Y69" s="59"/>
+      <c r="Z69" s="59"/>
+      <c r="AA69" s="59"/>
+      <c r="AB69" s="57"/>
+      <c r="AC69" s="57"/>
+      <c r="AD69" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB69,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE69" s="68"/>
-      <c r="AF69" s="68"/>
-      <c r="AG69" s="71"/>
-      <c r="AH69" s="68"/>
-      <c r="AI69" s="72"/>
-      <c r="AJ69" s="73" t="str">
+      <c r="AE69" s="57"/>
+      <c r="AF69" s="57"/>
+      <c r="AG69" s="60"/>
+      <c r="AH69" s="57"/>
+      <c r="AI69" s="61"/>
+      <c r="AJ69" s="62" t="str">
         <f>IF(COUNTA(C69,D69,E69,F69,H69,I69,L69,M69,N69,P69,Q69,R69,S69,T69,U69,X69,Y69,Z69,AB69,AC69,AH69)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C69=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D69=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E69=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F69=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G69=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H69=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I69=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L69=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M69=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N69=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P69=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q69=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R69=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S69=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T69=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U69=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X69=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y69=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z69=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB69=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC69=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH69=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C69=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D69=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E69=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F69=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G69=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H69=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I69=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L69=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M69=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N69=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P69=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q69=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R69=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S69=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T69=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U69=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X69=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y69=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z69=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB69=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC69=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH69=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK69" s="63"/>
-    </row>
-    <row r="70" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A70" s="40"/>
-      <c r="B70" s="67">
+      <c r="AK69" s="52"/>
+    </row>
+    <row r="70" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A70" s="31"/>
+      <c r="B70" s="56">
         <v>49</v>
       </c>
-      <c r="C70" s="68"/>
-      <c r="D70" s="68"/>
-      <c r="E70" s="68"/>
-      <c r="F70" s="68"/>
-      <c r="G70" s="69" t="str">
+      <c r="C70" s="57"/>
+      <c r="D70" s="57"/>
+      <c r="E70" s="57"/>
+      <c r="F70" s="57"/>
+      <c r="G70" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F70,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H70" s="68"/>
-      <c r="I70" s="70"/>
-      <c r="J70" s="68"/>
-      <c r="K70" s="70"/>
-      <c r="L70" s="70"/>
-      <c r="M70" s="70"/>
-      <c r="N70" s="70"/>
-      <c r="O70" s="70"/>
-      <c r="P70" s="70"/>
-      <c r="Q70" s="70"/>
-      <c r="R70" s="70"/>
-      <c r="S70" s="70"/>
-      <c r="T70" s="70"/>
-      <c r="U70" s="70"/>
-      <c r="V70" s="70"/>
-      <c r="W70" s="70"/>
-      <c r="X70" s="70"/>
-      <c r="Y70" s="70"/>
-      <c r="Z70" s="70"/>
-      <c r="AA70" s="70"/>
-      <c r="AB70" s="68"/>
-      <c r="AC70" s="68"/>
-      <c r="AD70" s="69" t="str">
+      <c r="H70" s="57"/>
+      <c r="I70" s="59"/>
+      <c r="J70" s="57"/>
+      <c r="K70" s="59"/>
+      <c r="L70" s="59"/>
+      <c r="M70" s="59"/>
+      <c r="N70" s="59"/>
+      <c r="O70" s="59"/>
+      <c r="P70" s="59"/>
+      <c r="Q70" s="59"/>
+      <c r="R70" s="59"/>
+      <c r="S70" s="59"/>
+      <c r="T70" s="59"/>
+      <c r="U70" s="59"/>
+      <c r="V70" s="59"/>
+      <c r="W70" s="59"/>
+      <c r="X70" s="59"/>
+      <c r="Y70" s="59"/>
+      <c r="Z70" s="59"/>
+      <c r="AA70" s="59"/>
+      <c r="AB70" s="57"/>
+      <c r="AC70" s="57"/>
+      <c r="AD70" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB70,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE70" s="68"/>
-      <c r="AF70" s="68"/>
-      <c r="AG70" s="71"/>
-      <c r="AH70" s="68"/>
-      <c r="AI70" s="72"/>
-      <c r="AJ70" s="73" t="str">
+      <c r="AE70" s="57"/>
+      <c r="AF70" s="57"/>
+      <c r="AG70" s="60"/>
+      <c r="AH70" s="57"/>
+      <c r="AI70" s="61"/>
+      <c r="AJ70" s="62" t="str">
         <f>IF(COUNTA(C70,D70,E70,F70,H70,I70,L70,M70,N70,P70,Q70,R70,S70,T70,U70,X70,Y70,Z70,AB70,AC70,AH70)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C70=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D70=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E70=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F70=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G70=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H70=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I70=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L70=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M70=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N70=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P70=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q70=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R70=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S70=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T70=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U70=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X70=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y70=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z70=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB70=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC70=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH70=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C70=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D70=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E70=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F70=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G70=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H70=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I70=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L70=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M70=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N70=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P70=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q70=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R70=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S70=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T70=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U70=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X70=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y70=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z70=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB70=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC70=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH70=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK70" s="63"/>
-    </row>
-    <row r="71" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A71" s="40"/>
-      <c r="B71" s="67">
+      <c r="AK70" s="52"/>
+    </row>
+    <row r="71" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A71" s="31"/>
+      <c r="B71" s="56">
         <v>50</v>
       </c>
-      <c r="C71" s="68"/>
-      <c r="D71" s="68"/>
-      <c r="E71" s="68"/>
-      <c r="F71" s="68"/>
-      <c r="G71" s="69" t="str">
+      <c r="C71" s="57"/>
+      <c r="D71" s="57"/>
+      <c r="E71" s="57"/>
+      <c r="F71" s="57"/>
+      <c r="G71" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F71,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H71" s="68"/>
-      <c r="I71" s="70"/>
-      <c r="J71" s="68"/>
-      <c r="K71" s="70"/>
-      <c r="L71" s="70"/>
-      <c r="M71" s="70"/>
-      <c r="N71" s="70"/>
-      <c r="O71" s="70"/>
-      <c r="P71" s="70"/>
-      <c r="Q71" s="70"/>
-      <c r="R71" s="70"/>
-      <c r="S71" s="70"/>
-      <c r="T71" s="70"/>
-      <c r="U71" s="70"/>
-      <c r="V71" s="70"/>
-      <c r="W71" s="70"/>
-      <c r="X71" s="70"/>
-      <c r="Y71" s="70"/>
-      <c r="Z71" s="70"/>
-      <c r="AA71" s="70"/>
-      <c r="AB71" s="68"/>
-      <c r="AC71" s="68"/>
-      <c r="AD71" s="69" t="str">
+      <c r="H71" s="57"/>
+      <c r="I71" s="59"/>
+      <c r="J71" s="57"/>
+      <c r="K71" s="59"/>
+      <c r="L71" s="59"/>
+      <c r="M71" s="59"/>
+      <c r="N71" s="59"/>
+      <c r="O71" s="59"/>
+      <c r="P71" s="59"/>
+      <c r="Q71" s="59"/>
+      <c r="R71" s="59"/>
+      <c r="S71" s="59"/>
+      <c r="T71" s="59"/>
+      <c r="U71" s="59"/>
+      <c r="V71" s="59"/>
+      <c r="W71" s="59"/>
+      <c r="X71" s="59"/>
+      <c r="Y71" s="59"/>
+      <c r="Z71" s="59"/>
+      <c r="AA71" s="59"/>
+      <c r="AB71" s="57"/>
+      <c r="AC71" s="57"/>
+      <c r="AD71" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB71,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE71" s="68"/>
-      <c r="AF71" s="68"/>
-      <c r="AG71" s="71"/>
-      <c r="AH71" s="68"/>
-      <c r="AI71" s="72"/>
-      <c r="AJ71" s="73" t="str">
+      <c r="AE71" s="57"/>
+      <c r="AF71" s="57"/>
+      <c r="AG71" s="60"/>
+      <c r="AH71" s="57"/>
+      <c r="AI71" s="61"/>
+      <c r="AJ71" s="62" t="str">
         <f>IF(COUNTA(C71,D71,E71,F71,H71,I71,L71,M71,N71,P71,Q71,R71,S71,T71,U71,X71,Y71,Z71,AB71,AC71,AH71)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C71=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D71=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E71=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F71=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G71=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H71=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I71=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L71=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M71=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N71=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P71=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q71=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R71=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S71=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T71=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U71=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X71=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y71=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z71=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB71=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC71=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH71=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C71=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D71=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E71=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F71=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G71=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H71=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I71=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L71=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M71=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N71=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P71=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q71=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R71=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S71=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T71=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U71=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X71=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y71=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z71=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB71=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC71=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH71=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK71" s="63"/>
-    </row>
-    <row r="72" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A72" s="40"/>
-      <c r="B72" s="67">
+      <c r="AK71" s="52"/>
+    </row>
+    <row r="72" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A72" s="31"/>
+      <c r="B72" s="56">
         <v>51</v>
       </c>
-      <c r="C72" s="68"/>
-      <c r="D72" s="68"/>
-      <c r="E72" s="68"/>
-      <c r="F72" s="68"/>
-      <c r="G72" s="69" t="str">
+      <c r="C72" s="57"/>
+      <c r="D72" s="57"/>
+      <c r="E72" s="57"/>
+      <c r="F72" s="57"/>
+      <c r="G72" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F72,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H72" s="68"/>
-      <c r="I72" s="70"/>
-      <c r="J72" s="68"/>
-      <c r="K72" s="70"/>
-      <c r="L72" s="70"/>
-      <c r="M72" s="70"/>
-      <c r="N72" s="70"/>
-      <c r="O72" s="70"/>
-      <c r="P72" s="70"/>
-      <c r="Q72" s="70"/>
-      <c r="R72" s="70"/>
-      <c r="S72" s="70"/>
-      <c r="T72" s="70"/>
-      <c r="U72" s="70"/>
-      <c r="V72" s="70"/>
-      <c r="W72" s="70"/>
-      <c r="X72" s="70"/>
-      <c r="Y72" s="70"/>
-      <c r="Z72" s="70"/>
-      <c r="AA72" s="70"/>
-      <c r="AB72" s="68"/>
-      <c r="AC72" s="68"/>
-      <c r="AD72" s="69" t="str">
+      <c r="H72" s="57"/>
+      <c r="I72" s="59"/>
+      <c r="J72" s="57"/>
+      <c r="K72" s="59"/>
+      <c r="L72" s="59"/>
+      <c r="M72" s="59"/>
+      <c r="N72" s="59"/>
+      <c r="O72" s="59"/>
+      <c r="P72" s="59"/>
+      <c r="Q72" s="59"/>
+      <c r="R72" s="59"/>
+      <c r="S72" s="59"/>
+      <c r="T72" s="59"/>
+      <c r="U72" s="59"/>
+      <c r="V72" s="59"/>
+      <c r="W72" s="59"/>
+      <c r="X72" s="59"/>
+      <c r="Y72" s="59"/>
+      <c r="Z72" s="59"/>
+      <c r="AA72" s="59"/>
+      <c r="AB72" s="57"/>
+      <c r="AC72" s="57"/>
+      <c r="AD72" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB72,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE72" s="68"/>
-      <c r="AF72" s="68"/>
-      <c r="AG72" s="71"/>
-      <c r="AH72" s="68"/>
-      <c r="AI72" s="72"/>
-      <c r="AJ72" s="73" t="str">
+      <c r="AE72" s="57"/>
+      <c r="AF72" s="57"/>
+      <c r="AG72" s="60"/>
+      <c r="AH72" s="57"/>
+      <c r="AI72" s="61"/>
+      <c r="AJ72" s="62" t="str">
         <f>IF(COUNTA(C72,D72,E72,F72,H72,I72,L72,M72,N72,P72,Q72,R72,S72,T72,U72,X72,Y72,Z72,AB72,AC72,AH72)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C72=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D72=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E72=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F72=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G72=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H72=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I72=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L72=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M72=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N72=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P72=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q72=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R72=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S72=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T72=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U72=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X72=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y72=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z72=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB72=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC72=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH72=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C72=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D72=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E72=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F72=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G72=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H72=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I72=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L72=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M72=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N72=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P72=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q72=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R72=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S72=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T72=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U72=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X72=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y72=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z72=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB72=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC72=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH72=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK72" s="63"/>
-    </row>
-    <row r="73" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A73" s="40"/>
-      <c r="B73" s="67">
+      <c r="AK72" s="52"/>
+    </row>
+    <row r="73" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A73" s="31"/>
+      <c r="B73" s="56">
         <v>52</v>
       </c>
-      <c r="C73" s="68"/>
-      <c r="D73" s="68"/>
-      <c r="E73" s="68"/>
-      <c r="F73" s="68"/>
-      <c r="G73" s="69" t="str">
+      <c r="C73" s="57"/>
+      <c r="D73" s="57"/>
+      <c r="E73" s="57"/>
+      <c r="F73" s="57"/>
+      <c r="G73" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F73,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H73" s="68"/>
-      <c r="I73" s="70"/>
-      <c r="J73" s="68"/>
-      <c r="K73" s="70"/>
-      <c r="L73" s="70"/>
-      <c r="M73" s="70"/>
-      <c r="N73" s="70"/>
-      <c r="O73" s="70"/>
-      <c r="P73" s="70"/>
-      <c r="Q73" s="70"/>
-      <c r="R73" s="70"/>
-      <c r="S73" s="70"/>
-      <c r="T73" s="70"/>
-      <c r="U73" s="70"/>
-      <c r="V73" s="70"/>
-      <c r="W73" s="70"/>
-      <c r="X73" s="70"/>
-      <c r="Y73" s="70"/>
-      <c r="Z73" s="70"/>
-      <c r="AA73" s="70"/>
-      <c r="AB73" s="68"/>
-      <c r="AC73" s="68"/>
-      <c r="AD73" s="69" t="str">
+      <c r="H73" s="57"/>
+      <c r="I73" s="59"/>
+      <c r="J73" s="57"/>
+      <c r="K73" s="59"/>
+      <c r="L73" s="59"/>
+      <c r="M73" s="59"/>
+      <c r="N73" s="59"/>
+      <c r="O73" s="59"/>
+      <c r="P73" s="59"/>
+      <c r="Q73" s="59"/>
+      <c r="R73" s="59"/>
+      <c r="S73" s="59"/>
+      <c r="T73" s="59"/>
+      <c r="U73" s="59"/>
+      <c r="V73" s="59"/>
+      <c r="W73" s="59"/>
+      <c r="X73" s="59"/>
+      <c r="Y73" s="59"/>
+      <c r="Z73" s="59"/>
+      <c r="AA73" s="59"/>
+      <c r="AB73" s="57"/>
+      <c r="AC73" s="57"/>
+      <c r="AD73" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB73,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE73" s="68"/>
-      <c r="AF73" s="68"/>
-      <c r="AG73" s="71"/>
-      <c r="AH73" s="68"/>
-      <c r="AI73" s="72"/>
-      <c r="AJ73" s="73" t="str">
+      <c r="AE73" s="57"/>
+      <c r="AF73" s="57"/>
+      <c r="AG73" s="60"/>
+      <c r="AH73" s="57"/>
+      <c r="AI73" s="61"/>
+      <c r="AJ73" s="62" t="str">
         <f>IF(COUNTA(C73,D73,E73,F73,H73,I73,L73,M73,N73,P73,Q73,R73,S73,T73,U73,X73,Y73,Z73,AB73,AC73,AH73)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C73=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D73=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E73=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F73=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G73=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H73=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I73=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L73=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M73=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N73=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P73=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q73=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R73=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S73=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T73=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U73=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X73=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y73=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z73=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB73=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC73=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH73=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C73=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D73=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E73=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F73=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G73=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H73=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I73=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L73=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M73=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N73=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P73=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q73=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R73=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S73=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T73=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U73=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X73=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y73=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z73=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB73=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC73=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH73=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK73" s="63"/>
-    </row>
-    <row r="74" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A74" s="40"/>
-      <c r="B74" s="67">
+      <c r="AK73" s="52"/>
+    </row>
+    <row r="74" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A74" s="31"/>
+      <c r="B74" s="56">
         <v>53</v>
       </c>
-      <c r="C74" s="68"/>
-      <c r="D74" s="68"/>
-      <c r="E74" s="68"/>
-      <c r="F74" s="68"/>
-      <c r="G74" s="69" t="str">
+      <c r="C74" s="57"/>
+      <c r="D74" s="57"/>
+      <c r="E74" s="57"/>
+      <c r="F74" s="57"/>
+      <c r="G74" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F74,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H74" s="68"/>
-      <c r="I74" s="70"/>
-      <c r="J74" s="68"/>
-      <c r="K74" s="70"/>
-      <c r="L74" s="70"/>
-      <c r="M74" s="70"/>
-      <c r="N74" s="70"/>
-      <c r="O74" s="70"/>
-      <c r="P74" s="70"/>
-      <c r="Q74" s="70"/>
-      <c r="R74" s="70"/>
-      <c r="S74" s="70"/>
-      <c r="T74" s="70"/>
-      <c r="U74" s="70"/>
-      <c r="V74" s="70"/>
-      <c r="W74" s="70"/>
-      <c r="X74" s="70"/>
-      <c r="Y74" s="70"/>
-      <c r="Z74" s="70"/>
-      <c r="AA74" s="70"/>
-      <c r="AB74" s="68"/>
-      <c r="AC74" s="68"/>
-      <c r="AD74" s="69" t="str">
+      <c r="H74" s="57"/>
+      <c r="I74" s="59"/>
+      <c r="J74" s="57"/>
+      <c r="K74" s="59"/>
+      <c r="L74" s="59"/>
+      <c r="M74" s="59"/>
+      <c r="N74" s="59"/>
+      <c r="O74" s="59"/>
+      <c r="P74" s="59"/>
+      <c r="Q74" s="59"/>
+      <c r="R74" s="59"/>
+      <c r="S74" s="59"/>
+      <c r="T74" s="59"/>
+      <c r="U74" s="59"/>
+      <c r="V74" s="59"/>
+      <c r="W74" s="59"/>
+      <c r="X74" s="59"/>
+      <c r="Y74" s="59"/>
+      <c r="Z74" s="59"/>
+      <c r="AA74" s="59"/>
+      <c r="AB74" s="57"/>
+      <c r="AC74" s="57"/>
+      <c r="AD74" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB74,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE74" s="68"/>
-      <c r="AF74" s="68"/>
-      <c r="AG74" s="71"/>
-      <c r="AH74" s="68"/>
-      <c r="AI74" s="72"/>
-      <c r="AJ74" s="73" t="str">
+      <c r="AE74" s="57"/>
+      <c r="AF74" s="57"/>
+      <c r="AG74" s="60"/>
+      <c r="AH74" s="57"/>
+      <c r="AI74" s="61"/>
+      <c r="AJ74" s="62" t="str">
         <f>IF(COUNTA(C74,D74,E74,F74,H74,I74,L74,M74,N74,P74,Q74,R74,S74,T74,U74,X74,Y74,Z74,AB74,AC74,AH74)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C74=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D74=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E74=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F74=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G74=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H74=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I74=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L74=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M74=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N74=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P74=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q74=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R74=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S74=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T74=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U74=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X74=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y74=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z74=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB74=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC74=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH74=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C74=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D74=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E74=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F74=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G74=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H74=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I74=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L74=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M74=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N74=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P74=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q74=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R74=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S74=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T74=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U74=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X74=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y74=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z74=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB74=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC74=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH74=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK74" s="63"/>
-    </row>
-    <row r="75" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A75" s="40"/>
-      <c r="B75" s="67">
+      <c r="AK74" s="52"/>
+    </row>
+    <row r="75" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A75" s="31"/>
+      <c r="B75" s="56">
         <v>54</v>
       </c>
-      <c r="C75" s="68"/>
-      <c r="D75" s="68"/>
-      <c r="E75" s="68"/>
-      <c r="F75" s="68"/>
-      <c r="G75" s="69" t="str">
+      <c r="C75" s="57"/>
+      <c r="D75" s="57"/>
+      <c r="E75" s="57"/>
+      <c r="F75" s="57"/>
+      <c r="G75" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F75,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H75" s="68"/>
-      <c r="I75" s="70"/>
-      <c r="J75" s="68"/>
-      <c r="K75" s="70"/>
-      <c r="L75" s="70"/>
-      <c r="M75" s="70"/>
-      <c r="N75" s="70"/>
-      <c r="O75" s="70"/>
-      <c r="P75" s="70"/>
-      <c r="Q75" s="70"/>
-      <c r="R75" s="70"/>
-      <c r="S75" s="70"/>
-      <c r="T75" s="70"/>
-      <c r="U75" s="70"/>
-      <c r="V75" s="70"/>
-      <c r="W75" s="70"/>
-      <c r="X75" s="70"/>
-      <c r="Y75" s="70"/>
-      <c r="Z75" s="70"/>
-      <c r="AA75" s="70"/>
-      <c r="AB75" s="68"/>
-      <c r="AC75" s="68"/>
-      <c r="AD75" s="69" t="str">
+      <c r="H75" s="57"/>
+      <c r="I75" s="59"/>
+      <c r="J75" s="57"/>
+      <c r="K75" s="59"/>
+      <c r="L75" s="59"/>
+      <c r="M75" s="59"/>
+      <c r="N75" s="59"/>
+      <c r="O75" s="59"/>
+      <c r="P75" s="59"/>
+      <c r="Q75" s="59"/>
+      <c r="R75" s="59"/>
+      <c r="S75" s="59"/>
+      <c r="T75" s="59"/>
+      <c r="U75" s="59"/>
+      <c r="V75" s="59"/>
+      <c r="W75" s="59"/>
+      <c r="X75" s="59"/>
+      <c r="Y75" s="59"/>
+      <c r="Z75" s="59"/>
+      <c r="AA75" s="59"/>
+      <c r="AB75" s="57"/>
+      <c r="AC75" s="57"/>
+      <c r="AD75" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB75,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE75" s="68"/>
-      <c r="AF75" s="68"/>
-      <c r="AG75" s="71"/>
-      <c r="AH75" s="68"/>
-      <c r="AI75" s="72"/>
-      <c r="AJ75" s="73" t="str">
+      <c r="AE75" s="57"/>
+      <c r="AF75" s="57"/>
+      <c r="AG75" s="60"/>
+      <c r="AH75" s="57"/>
+      <c r="AI75" s="61"/>
+      <c r="AJ75" s="62" t="str">
         <f>IF(COUNTA(C75,D75,E75,F75,H75,I75,L75,M75,N75,P75,Q75,R75,S75,T75,U75,X75,Y75,Z75,AB75,AC75,AH75)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C75=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D75=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E75=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F75=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G75=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H75=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I75=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L75=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M75=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N75=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P75=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q75=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R75=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S75=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T75=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U75=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X75=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y75=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z75=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB75=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC75=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH75=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C75=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D75=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E75=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F75=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G75=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H75=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I75=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L75=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M75=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N75=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P75=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q75=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R75=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S75=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T75=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U75=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X75=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y75=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z75=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB75=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC75=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH75=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK75" s="63"/>
-    </row>
-    <row r="76" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A76" s="40"/>
-      <c r="B76" s="67">
+      <c r="AK75" s="52"/>
+    </row>
+    <row r="76" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A76" s="31"/>
+      <c r="B76" s="56">
         <v>55</v>
       </c>
-      <c r="C76" s="68"/>
-      <c r="D76" s="68"/>
-      <c r="E76" s="68"/>
-      <c r="F76" s="68"/>
-      <c r="G76" s="69" t="str">
+      <c r="C76" s="57"/>
+      <c r="D76" s="57"/>
+      <c r="E76" s="57"/>
+      <c r="F76" s="57"/>
+      <c r="G76" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F76,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H76" s="68"/>
-      <c r="I76" s="70"/>
-      <c r="J76" s="68"/>
-      <c r="K76" s="70"/>
-      <c r="L76" s="70"/>
-      <c r="M76" s="70"/>
-      <c r="N76" s="70"/>
-      <c r="O76" s="70"/>
-      <c r="P76" s="70"/>
-      <c r="Q76" s="70"/>
-      <c r="R76" s="70"/>
-      <c r="S76" s="70"/>
-      <c r="T76" s="70"/>
-      <c r="U76" s="70"/>
-      <c r="V76" s="70"/>
-      <c r="W76" s="70"/>
-      <c r="X76" s="70"/>
-      <c r="Y76" s="70"/>
-      <c r="Z76" s="70"/>
-      <c r="AA76" s="70"/>
-      <c r="AB76" s="68"/>
-      <c r="AC76" s="68"/>
-      <c r="AD76" s="69" t="str">
+      <c r="H76" s="57"/>
+      <c r="I76" s="59"/>
+      <c r="J76" s="57"/>
+      <c r="K76" s="59"/>
+      <c r="L76" s="59"/>
+      <c r="M76" s="59"/>
+      <c r="N76" s="59"/>
+      <c r="O76" s="59"/>
+      <c r="P76" s="59"/>
+      <c r="Q76" s="59"/>
+      <c r="R76" s="59"/>
+      <c r="S76" s="59"/>
+      <c r="T76" s="59"/>
+      <c r="U76" s="59"/>
+      <c r="V76" s="59"/>
+      <c r="W76" s="59"/>
+      <c r="X76" s="59"/>
+      <c r="Y76" s="59"/>
+      <c r="Z76" s="59"/>
+      <c r="AA76" s="59"/>
+      <c r="AB76" s="57"/>
+      <c r="AC76" s="57"/>
+      <c r="AD76" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB76,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE76" s="68"/>
-      <c r="AF76" s="68"/>
-      <c r="AG76" s="71"/>
-      <c r="AH76" s="68"/>
-      <c r="AI76" s="72"/>
-      <c r="AJ76" s="73" t="str">
+      <c r="AE76" s="57"/>
+      <c r="AF76" s="57"/>
+      <c r="AG76" s="60"/>
+      <c r="AH76" s="57"/>
+      <c r="AI76" s="61"/>
+      <c r="AJ76" s="62" t="str">
         <f>IF(COUNTA(C76,D76,E76,F76,H76,I76,L76,M76,N76,P76,Q76,R76,S76,T76,U76,X76,Y76,Z76,AB76,AC76,AH76)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C76=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D76=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E76=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F76=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G76=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H76=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I76=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L76=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M76=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N76=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P76=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q76=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R76=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S76=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T76=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U76=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X76=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y76=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z76=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB76=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC76=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH76=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C76=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D76=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E76=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F76=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G76=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H76=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I76=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L76=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M76=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N76=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P76=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q76=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R76=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S76=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T76=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U76=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X76=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y76=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z76=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB76=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC76=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH76=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK76" s="63"/>
-    </row>
-    <row r="77" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A77" s="40"/>
-      <c r="B77" s="67">
+      <c r="AK76" s="52"/>
+    </row>
+    <row r="77" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A77" s="31"/>
+      <c r="B77" s="56">
         <v>56</v>
       </c>
-      <c r="C77" s="68"/>
-      <c r="D77" s="68"/>
-      <c r="E77" s="68"/>
-      <c r="F77" s="68"/>
-      <c r="G77" s="69" t="str">
+      <c r="C77" s="57"/>
+      <c r="D77" s="57"/>
+      <c r="E77" s="57"/>
+      <c r="F77" s="57"/>
+      <c r="G77" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F77,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H77" s="68"/>
-      <c r="I77" s="70"/>
-      <c r="J77" s="68"/>
-      <c r="K77" s="70"/>
-      <c r="L77" s="70"/>
-      <c r="M77" s="70"/>
-      <c r="N77" s="70"/>
-      <c r="O77" s="70"/>
-      <c r="P77" s="70"/>
-      <c r="Q77" s="70"/>
-      <c r="R77" s="70"/>
-      <c r="S77" s="70"/>
-      <c r="T77" s="70"/>
-      <c r="U77" s="70"/>
-      <c r="V77" s="70"/>
-      <c r="W77" s="70"/>
-      <c r="X77" s="70"/>
-      <c r="Y77" s="70"/>
-      <c r="Z77" s="70"/>
-      <c r="AA77" s="70"/>
-      <c r="AB77" s="68"/>
-      <c r="AC77" s="68"/>
-      <c r="AD77" s="69" t="str">
+      <c r="H77" s="57"/>
+      <c r="I77" s="59"/>
+      <c r="J77" s="57"/>
+      <c r="K77" s="59"/>
+      <c r="L77" s="59"/>
+      <c r="M77" s="59"/>
+      <c r="N77" s="59"/>
+      <c r="O77" s="59"/>
+      <c r="P77" s="59"/>
+      <c r="Q77" s="59"/>
+      <c r="R77" s="59"/>
+      <c r="S77" s="59"/>
+      <c r="T77" s="59"/>
+      <c r="U77" s="59"/>
+      <c r="V77" s="59"/>
+      <c r="W77" s="59"/>
+      <c r="X77" s="59"/>
+      <c r="Y77" s="59"/>
+      <c r="Z77" s="59"/>
+      <c r="AA77" s="59"/>
+      <c r="AB77" s="57"/>
+      <c r="AC77" s="57"/>
+      <c r="AD77" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB77,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE77" s="68"/>
-      <c r="AF77" s="68"/>
-      <c r="AG77" s="71"/>
-      <c r="AH77" s="68"/>
-      <c r="AI77" s="72"/>
-      <c r="AJ77" s="73" t="str">
+      <c r="AE77" s="57"/>
+      <c r="AF77" s="57"/>
+      <c r="AG77" s="60"/>
+      <c r="AH77" s="57"/>
+      <c r="AI77" s="61"/>
+      <c r="AJ77" s="62" t="str">
         <f>IF(COUNTA(C77,D77,E77,F77,H77,I77,L77,M77,N77,P77,Q77,R77,S77,T77,U77,X77,Y77,Z77,AB77,AC77,AH77)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C77=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D77=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E77=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F77=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G77=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H77=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I77=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L77=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M77=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N77=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P77=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q77=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R77=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S77=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T77=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U77=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X77=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y77=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z77=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB77=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC77=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH77=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C77=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D77=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E77=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F77=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G77=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H77=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I77=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L77=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M77=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N77=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P77=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q77=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R77=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S77=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T77=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U77=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X77=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y77=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z77=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB77=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC77=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH77=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK77" s="63"/>
-    </row>
-    <row r="78" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A78" s="40"/>
-      <c r="B78" s="67">
+      <c r="AK77" s="52"/>
+    </row>
+    <row r="78" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A78" s="31"/>
+      <c r="B78" s="56">
         <v>57</v>
       </c>
-      <c r="C78" s="68"/>
-      <c r="D78" s="68"/>
-      <c r="E78" s="68"/>
-      <c r="F78" s="68"/>
-      <c r="G78" s="69" t="str">
+      <c r="C78" s="57"/>
+      <c r="D78" s="57"/>
+      <c r="E78" s="57"/>
+      <c r="F78" s="57"/>
+      <c r="G78" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F78,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H78" s="68"/>
-      <c r="I78" s="70"/>
-      <c r="J78" s="68"/>
-      <c r="K78" s="70"/>
-      <c r="L78" s="70"/>
-      <c r="M78" s="70"/>
-      <c r="N78" s="70"/>
-      <c r="O78" s="70"/>
-      <c r="P78" s="70"/>
-      <c r="Q78" s="70"/>
-      <c r="R78" s="70"/>
-      <c r="S78" s="70"/>
-      <c r="T78" s="70"/>
-      <c r="U78" s="70"/>
-      <c r="V78" s="70"/>
-      <c r="W78" s="70"/>
-      <c r="X78" s="70"/>
-      <c r="Y78" s="70"/>
-      <c r="Z78" s="70"/>
-      <c r="AA78" s="70"/>
-      <c r="AB78" s="68"/>
-      <c r="AC78" s="68"/>
-      <c r="AD78" s="69" t="str">
+      <c r="H78" s="57"/>
+      <c r="I78" s="59"/>
+      <c r="J78" s="57"/>
+      <c r="K78" s="59"/>
+      <c r="L78" s="59"/>
+      <c r="M78" s="59"/>
+      <c r="N78" s="59"/>
+      <c r="O78" s="59"/>
+      <c r="P78" s="59"/>
+      <c r="Q78" s="59"/>
+      <c r="R78" s="59"/>
+      <c r="S78" s="59"/>
+      <c r="T78" s="59"/>
+      <c r="U78" s="59"/>
+      <c r="V78" s="59"/>
+      <c r="W78" s="59"/>
+      <c r="X78" s="59"/>
+      <c r="Y78" s="59"/>
+      <c r="Z78" s="59"/>
+      <c r="AA78" s="59"/>
+      <c r="AB78" s="57"/>
+      <c r="AC78" s="57"/>
+      <c r="AD78" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB78,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE78" s="68"/>
-      <c r="AF78" s="68"/>
-      <c r="AG78" s="71"/>
-      <c r="AH78" s="68"/>
-      <c r="AI78" s="72"/>
-      <c r="AJ78" s="73" t="str">
+      <c r="AE78" s="57"/>
+      <c r="AF78" s="57"/>
+      <c r="AG78" s="60"/>
+      <c r="AH78" s="57"/>
+      <c r="AI78" s="61"/>
+      <c r="AJ78" s="62" t="str">
         <f>IF(COUNTA(C78,D78,E78,F78,H78,I78,L78,M78,N78,P78,Q78,R78,S78,T78,U78,X78,Y78,Z78,AB78,AC78,AH78)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C78=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D78=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E78=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F78=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G78=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H78=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I78=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L78=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M78=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N78=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P78=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q78=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R78=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S78=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T78=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U78=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X78=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y78=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z78=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB78=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC78=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH78=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C78=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D78=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E78=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F78=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G78=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H78=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I78=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L78=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M78=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N78=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P78=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q78=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R78=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S78=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T78=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U78=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X78=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y78=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z78=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB78=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC78=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH78=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK78" s="63"/>
-    </row>
-    <row r="79" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A79" s="40"/>
-      <c r="B79" s="67">
+      <c r="AK78" s="52"/>
+    </row>
+    <row r="79" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A79" s="31"/>
+      <c r="B79" s="56">
         <v>58</v>
       </c>
-      <c r="C79" s="68"/>
-      <c r="D79" s="68"/>
-      <c r="E79" s="68"/>
-      <c r="F79" s="68"/>
-      <c r="G79" s="69" t="str">
+      <c r="C79" s="57"/>
+      <c r="D79" s="57"/>
+      <c r="E79" s="57"/>
+      <c r="F79" s="57"/>
+      <c r="G79" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F79,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H79" s="68"/>
-      <c r="I79" s="70"/>
-      <c r="J79" s="68"/>
-      <c r="K79" s="70"/>
-      <c r="L79" s="70"/>
-      <c r="M79" s="70"/>
-      <c r="N79" s="70"/>
-      <c r="O79" s="70"/>
-      <c r="P79" s="70"/>
-      <c r="Q79" s="70"/>
-      <c r="R79" s="70"/>
-      <c r="S79" s="70"/>
-      <c r="T79" s="70"/>
-      <c r="U79" s="70"/>
-      <c r="V79" s="70"/>
-      <c r="W79" s="70"/>
-      <c r="X79" s="70"/>
-      <c r="Y79" s="70"/>
-      <c r="Z79" s="70"/>
-      <c r="AA79" s="70"/>
-      <c r="AB79" s="68"/>
-      <c r="AC79" s="68"/>
-      <c r="AD79" s="69" t="str">
+      <c r="H79" s="57"/>
+      <c r="I79" s="59"/>
+      <c r="J79" s="57"/>
+      <c r="K79" s="59"/>
+      <c r="L79" s="59"/>
+      <c r="M79" s="59"/>
+      <c r="N79" s="59"/>
+      <c r="O79" s="59"/>
+      <c r="P79" s="59"/>
+      <c r="Q79" s="59"/>
+      <c r="R79" s="59"/>
+      <c r="S79" s="59"/>
+      <c r="T79" s="59"/>
+      <c r="U79" s="59"/>
+      <c r="V79" s="59"/>
+      <c r="W79" s="59"/>
+      <c r="X79" s="59"/>
+      <c r="Y79" s="59"/>
+      <c r="Z79" s="59"/>
+      <c r="AA79" s="59"/>
+      <c r="AB79" s="57"/>
+      <c r="AC79" s="57"/>
+      <c r="AD79" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB79,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE79" s="68"/>
-      <c r="AF79" s="68"/>
-      <c r="AG79" s="71"/>
-      <c r="AH79" s="68"/>
-      <c r="AI79" s="72"/>
-      <c r="AJ79" s="73" t="str">
+      <c r="AE79" s="57"/>
+      <c r="AF79" s="57"/>
+      <c r="AG79" s="60"/>
+      <c r="AH79" s="57"/>
+      <c r="AI79" s="61"/>
+      <c r="AJ79" s="62" t="str">
         <f>IF(COUNTA(C79,D79,E79,F79,H79,I79,L79,M79,N79,P79,Q79,R79,S79,T79,U79,X79,Y79,Z79,AB79,AC79,AH79)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C79=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D79=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E79=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F79=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G79=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H79=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I79=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L79=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M79=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N79=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P79=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q79=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R79=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S79=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T79=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U79=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X79=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y79=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z79=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB79=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC79=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH79=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C79=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D79=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E79=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F79=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G79=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H79=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I79=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L79=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M79=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N79=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P79=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q79=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R79=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S79=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T79=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U79=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X79=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y79=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z79=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB79=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC79=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH79=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK79" s="63"/>
-    </row>
-    <row r="80" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A80" s="40"/>
-      <c r="B80" s="67">
+      <c r="AK79" s="52"/>
+    </row>
+    <row r="80" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A80" s="31"/>
+      <c r="B80" s="56">
         <v>59</v>
       </c>
-      <c r="C80" s="68"/>
-      <c r="D80" s="68"/>
-      <c r="E80" s="68"/>
-      <c r="F80" s="68"/>
-      <c r="G80" s="69" t="str">
+      <c r="C80" s="57"/>
+      <c r="D80" s="57"/>
+      <c r="E80" s="57"/>
+      <c r="F80" s="57"/>
+      <c r="G80" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F80,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H80" s="68"/>
-      <c r="I80" s="70"/>
-      <c r="J80" s="68"/>
-      <c r="K80" s="70"/>
-      <c r="L80" s="70"/>
-      <c r="M80" s="70"/>
-      <c r="N80" s="70"/>
-      <c r="O80" s="70"/>
-      <c r="P80" s="70"/>
-      <c r="Q80" s="70"/>
-      <c r="R80" s="70"/>
-      <c r="S80" s="70"/>
-      <c r="T80" s="70"/>
-      <c r="U80" s="70"/>
-      <c r="V80" s="70"/>
-      <c r="W80" s="70"/>
-      <c r="X80" s="70"/>
-      <c r="Y80" s="70"/>
-      <c r="Z80" s="70"/>
-      <c r="AA80" s="70"/>
-      <c r="AB80" s="68"/>
-      <c r="AC80" s="68"/>
-      <c r="AD80" s="69" t="str">
+      <c r="H80" s="57"/>
+      <c r="I80" s="59"/>
+      <c r="J80" s="57"/>
+      <c r="K80" s="59"/>
+      <c r="L80" s="59"/>
+      <c r="M80" s="59"/>
+      <c r="N80" s="59"/>
+      <c r="O80" s="59"/>
+      <c r="P80" s="59"/>
+      <c r="Q80" s="59"/>
+      <c r="R80" s="59"/>
+      <c r="S80" s="59"/>
+      <c r="T80" s="59"/>
+      <c r="U80" s="59"/>
+      <c r="V80" s="59"/>
+      <c r="W80" s="59"/>
+      <c r="X80" s="59"/>
+      <c r="Y80" s="59"/>
+      <c r="Z80" s="59"/>
+      <c r="AA80" s="59"/>
+      <c r="AB80" s="57"/>
+      <c r="AC80" s="57"/>
+      <c r="AD80" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB80,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE80" s="68"/>
-      <c r="AF80" s="68"/>
-      <c r="AG80" s="71"/>
-      <c r="AH80" s="68"/>
-      <c r="AI80" s="72"/>
-      <c r="AJ80" s="73" t="str">
+      <c r="AE80" s="57"/>
+      <c r="AF80" s="57"/>
+      <c r="AG80" s="60"/>
+      <c r="AH80" s="57"/>
+      <c r="AI80" s="61"/>
+      <c r="AJ80" s="62" t="str">
         <f>IF(COUNTA(C80,D80,E80,F80,H80,I80,L80,M80,N80,P80,Q80,R80,S80,T80,U80,X80,Y80,Z80,AB80,AC80,AH80)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C80=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D80=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E80=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F80=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G80=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H80=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I80=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L80=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M80=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N80=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P80=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q80=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R80=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S80=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T80=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U80=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X80=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y80=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z80=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB80=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC80=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH80=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C80=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D80=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E80=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F80=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G80=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H80=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I80=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L80=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M80=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N80=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P80=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q80=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R80=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S80=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T80=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U80=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X80=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y80=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z80=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB80=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC80=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH80=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK80" s="63"/>
-    </row>
-    <row r="81" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A81" s="40"/>
-      <c r="B81" s="67">
+      <c r="AK80" s="52"/>
+    </row>
+    <row r="81" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A81" s="31"/>
+      <c r="B81" s="56">
         <v>60</v>
       </c>
-      <c r="C81" s="68"/>
-      <c r="D81" s="68"/>
-      <c r="E81" s="68"/>
-      <c r="F81" s="68"/>
-      <c r="G81" s="69" t="str">
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
+      <c r="E81" s="57"/>
+      <c r="F81" s="57"/>
+      <c r="G81" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F81,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H81" s="68"/>
-      <c r="I81" s="70"/>
-      <c r="J81" s="68"/>
-      <c r="K81" s="70"/>
-      <c r="L81" s="70"/>
-      <c r="M81" s="70"/>
-      <c r="N81" s="70"/>
-      <c r="O81" s="70"/>
-      <c r="P81" s="70"/>
-      <c r="Q81" s="70"/>
-      <c r="R81" s="70"/>
-      <c r="S81" s="70"/>
-      <c r="T81" s="70"/>
-      <c r="U81" s="70"/>
-      <c r="V81" s="70"/>
-      <c r="W81" s="70"/>
-      <c r="X81" s="70"/>
-      <c r="Y81" s="70"/>
-      <c r="Z81" s="70"/>
-      <c r="AA81" s="70"/>
-      <c r="AB81" s="68"/>
-      <c r="AC81" s="68"/>
-      <c r="AD81" s="69" t="str">
+      <c r="H81" s="57"/>
+      <c r="I81" s="59"/>
+      <c r="J81" s="57"/>
+      <c r="K81" s="59"/>
+      <c r="L81" s="59"/>
+      <c r="M81" s="59"/>
+      <c r="N81" s="59"/>
+      <c r="O81" s="59"/>
+      <c r="P81" s="59"/>
+      <c r="Q81" s="59"/>
+      <c r="R81" s="59"/>
+      <c r="S81" s="59"/>
+      <c r="T81" s="59"/>
+      <c r="U81" s="59"/>
+      <c r="V81" s="59"/>
+      <c r="W81" s="59"/>
+      <c r="X81" s="59"/>
+      <c r="Y81" s="59"/>
+      <c r="Z81" s="59"/>
+      <c r="AA81" s="59"/>
+      <c r="AB81" s="57"/>
+      <c r="AC81" s="57"/>
+      <c r="AD81" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB81,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE81" s="68"/>
-      <c r="AF81" s="68"/>
-      <c r="AG81" s="71"/>
-      <c r="AH81" s="68"/>
-      <c r="AI81" s="72"/>
-      <c r="AJ81" s="73" t="str">
+      <c r="AE81" s="57"/>
+      <c r="AF81" s="57"/>
+      <c r="AG81" s="60"/>
+      <c r="AH81" s="57"/>
+      <c r="AI81" s="61"/>
+      <c r="AJ81" s="62" t="str">
         <f>IF(COUNTA(C81,D81,E81,F81,H81,I81,L81,M81,N81,P81,Q81,R81,S81,T81,U81,X81,Y81,Z81,AB81,AC81,AH81)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C81=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D81=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E81=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F81=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G81=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H81=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I81=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L81=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M81=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N81=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P81=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q81=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R81=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S81=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T81=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U81=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X81=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y81=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z81=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB81=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC81=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH81=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C81=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D81=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E81=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F81=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G81=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H81=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I81=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L81=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M81=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N81=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P81=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q81=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R81=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S81=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T81=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U81=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X81=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y81=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z81=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB81=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC81=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH81=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK81" s="63"/>
-    </row>
-    <row r="82" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A82" s="40"/>
-      <c r="B82" s="67">
+      <c r="AK81" s="52"/>
+    </row>
+    <row r="82" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A82" s="31"/>
+      <c r="B82" s="56">
         <v>61</v>
       </c>
-      <c r="C82" s="68"/>
-      <c r="D82" s="68"/>
-      <c r="E82" s="68"/>
-      <c r="F82" s="68"/>
-      <c r="G82" s="69" t="str">
+      <c r="C82" s="57"/>
+      <c r="D82" s="57"/>
+      <c r="E82" s="57"/>
+      <c r="F82" s="57"/>
+      <c r="G82" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F82,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H82" s="68"/>
-      <c r="I82" s="70"/>
-      <c r="J82" s="68"/>
-      <c r="K82" s="70"/>
-      <c r="L82" s="70"/>
-      <c r="M82" s="70"/>
-      <c r="N82" s="70"/>
-      <c r="O82" s="70"/>
-      <c r="P82" s="70"/>
-      <c r="Q82" s="70"/>
-      <c r="R82" s="70"/>
-      <c r="S82" s="70"/>
-      <c r="T82" s="70"/>
-      <c r="U82" s="70"/>
-      <c r="V82" s="70"/>
-      <c r="W82" s="70"/>
-      <c r="X82" s="70"/>
-      <c r="Y82" s="70"/>
-      <c r="Z82" s="70"/>
-      <c r="AA82" s="70"/>
-      <c r="AB82" s="68"/>
-      <c r="AC82" s="68"/>
-      <c r="AD82" s="69" t="str">
+      <c r="H82" s="57"/>
+      <c r="I82" s="59"/>
+      <c r="J82" s="57"/>
+      <c r="K82" s="59"/>
+      <c r="L82" s="59"/>
+      <c r="M82" s="59"/>
+      <c r="N82" s="59"/>
+      <c r="O82" s="59"/>
+      <c r="P82" s="59"/>
+      <c r="Q82" s="59"/>
+      <c r="R82" s="59"/>
+      <c r="S82" s="59"/>
+      <c r="T82" s="59"/>
+      <c r="U82" s="59"/>
+      <c r="V82" s="59"/>
+      <c r="W82" s="59"/>
+      <c r="X82" s="59"/>
+      <c r="Y82" s="59"/>
+      <c r="Z82" s="59"/>
+      <c r="AA82" s="59"/>
+      <c r="AB82" s="57"/>
+      <c r="AC82" s="57"/>
+      <c r="AD82" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB82,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE82" s="68"/>
-      <c r="AF82" s="68"/>
-      <c r="AG82" s="71"/>
-      <c r="AH82" s="68"/>
-      <c r="AI82" s="72"/>
-      <c r="AJ82" s="73" t="str">
+      <c r="AE82" s="57"/>
+      <c r="AF82" s="57"/>
+      <c r="AG82" s="60"/>
+      <c r="AH82" s="57"/>
+      <c r="AI82" s="61"/>
+      <c r="AJ82" s="62" t="str">
         <f>IF(COUNTA(C82,D82,E82,F82,H82,I82,L82,M82,N82,P82,Q82,R82,S82,T82,U82,X82,Y82,Z82,AB82,AC82,AH82)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C82=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D82=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E82=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F82=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G82=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H82=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I82=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L82=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M82=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N82=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P82=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q82=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R82=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S82=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T82=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U82=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X82=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y82=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z82=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB82=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC82=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH82=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C82=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D82=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E82=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F82=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G82=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H82=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I82=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L82=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M82=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N82=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P82=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q82=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R82=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S82=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T82=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U82=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X82=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y82=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z82=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB82=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC82=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH82=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK82" s="63"/>
-    </row>
-    <row r="83" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A83" s="40"/>
-      <c r="B83" s="67">
+      <c r="AK82" s="52"/>
+    </row>
+    <row r="83" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A83" s="31"/>
+      <c r="B83" s="56">
         <v>62</v>
       </c>
-      <c r="C83" s="68"/>
-      <c r="D83" s="68"/>
-      <c r="E83" s="68"/>
-      <c r="F83" s="68"/>
-      <c r="G83" s="69" t="str">
+      <c r="C83" s="57"/>
+      <c r="D83" s="57"/>
+      <c r="E83" s="57"/>
+      <c r="F83" s="57"/>
+      <c r="G83" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F83,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H83" s="68"/>
-      <c r="I83" s="70"/>
-      <c r="J83" s="68"/>
-      <c r="K83" s="70"/>
-      <c r="L83" s="70"/>
-      <c r="M83" s="70"/>
-      <c r="N83" s="70"/>
-      <c r="O83" s="70"/>
-      <c r="P83" s="70"/>
-      <c r="Q83" s="70"/>
-      <c r="R83" s="70"/>
-      <c r="S83" s="70"/>
-      <c r="T83" s="70"/>
-      <c r="U83" s="70"/>
-      <c r="V83" s="70"/>
-      <c r="W83" s="70"/>
-      <c r="X83" s="70"/>
-      <c r="Y83" s="70"/>
-      <c r="Z83" s="70"/>
-      <c r="AA83" s="70"/>
-      <c r="AB83" s="68"/>
-      <c r="AC83" s="68"/>
-      <c r="AD83" s="69" t="str">
+      <c r="H83" s="57"/>
+      <c r="I83" s="59"/>
+      <c r="J83" s="57"/>
+      <c r="K83" s="59"/>
+      <c r="L83" s="59"/>
+      <c r="M83" s="59"/>
+      <c r="N83" s="59"/>
+      <c r="O83" s="59"/>
+      <c r="P83" s="59"/>
+      <c r="Q83" s="59"/>
+      <c r="R83" s="59"/>
+      <c r="S83" s="59"/>
+      <c r="T83" s="59"/>
+      <c r="U83" s="59"/>
+      <c r="V83" s="59"/>
+      <c r="W83" s="59"/>
+      <c r="X83" s="59"/>
+      <c r="Y83" s="59"/>
+      <c r="Z83" s="59"/>
+      <c r="AA83" s="59"/>
+      <c r="AB83" s="57"/>
+      <c r="AC83" s="57"/>
+      <c r="AD83" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB83,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE83" s="68"/>
-      <c r="AF83" s="68"/>
-      <c r="AG83" s="71"/>
-      <c r="AH83" s="68"/>
-      <c r="AI83" s="72"/>
-      <c r="AJ83" s="73" t="str">
+      <c r="AE83" s="57"/>
+      <c r="AF83" s="57"/>
+      <c r="AG83" s="60"/>
+      <c r="AH83" s="57"/>
+      <c r="AI83" s="61"/>
+      <c r="AJ83" s="62" t="str">
         <f>IF(COUNTA(C83,D83,E83,F83,H83,I83,L83,M83,N83,P83,Q83,R83,S83,T83,U83,X83,Y83,Z83,AB83,AC83,AH83)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C83=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D83=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E83=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F83=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G83=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H83=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I83=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L83=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M83=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N83=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P83=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q83=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R83=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S83=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T83=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U83=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X83=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y83=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z83=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB83=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC83=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH83=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C83=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D83=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E83=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F83=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G83=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H83=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I83=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L83=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M83=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N83=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P83=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q83=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R83=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S83=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T83=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U83=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X83=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y83=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z83=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB83=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC83=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH83=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK83" s="63"/>
-    </row>
-    <row r="84" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A84" s="40"/>
-      <c r="B84" s="67">
+      <c r="AK83" s="52"/>
+    </row>
+    <row r="84" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A84" s="31"/>
+      <c r="B84" s="56">
         <v>63</v>
       </c>
-      <c r="C84" s="68"/>
-      <c r="D84" s="68"/>
-      <c r="E84" s="68"/>
-      <c r="F84" s="68"/>
-      <c r="G84" s="69" t="str">
+      <c r="C84" s="57"/>
+      <c r="D84" s="57"/>
+      <c r="E84" s="57"/>
+      <c r="F84" s="57"/>
+      <c r="G84" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F84,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H84" s="68"/>
-      <c r="I84" s="70"/>
-      <c r="J84" s="68"/>
-      <c r="K84" s="70"/>
-      <c r="L84" s="70"/>
-      <c r="M84" s="70"/>
-      <c r="N84" s="70"/>
-      <c r="O84" s="70"/>
-      <c r="P84" s="70"/>
-      <c r="Q84" s="70"/>
-      <c r="R84" s="70"/>
-      <c r="S84" s="70"/>
-      <c r="T84" s="70"/>
-      <c r="U84" s="70"/>
-      <c r="V84" s="70"/>
-      <c r="W84" s="70"/>
-      <c r="X84" s="70"/>
-      <c r="Y84" s="70"/>
-      <c r="Z84" s="70"/>
-      <c r="AA84" s="70"/>
-      <c r="AB84" s="68"/>
-      <c r="AC84" s="68"/>
-      <c r="AD84" s="69" t="str">
+      <c r="H84" s="57"/>
+      <c r="I84" s="59"/>
+      <c r="J84" s="57"/>
+      <c r="K84" s="59"/>
+      <c r="L84" s="59"/>
+      <c r="M84" s="59"/>
+      <c r="N84" s="59"/>
+      <c r="O84" s="59"/>
+      <c r="P84" s="59"/>
+      <c r="Q84" s="59"/>
+      <c r="R84" s="59"/>
+      <c r="S84" s="59"/>
+      <c r="T84" s="59"/>
+      <c r="U84" s="59"/>
+      <c r="V84" s="59"/>
+      <c r="W84" s="59"/>
+      <c r="X84" s="59"/>
+      <c r="Y84" s="59"/>
+      <c r="Z84" s="59"/>
+      <c r="AA84" s="59"/>
+      <c r="AB84" s="57"/>
+      <c r="AC84" s="57"/>
+      <c r="AD84" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB84,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE84" s="68"/>
-      <c r="AF84" s="68"/>
-      <c r="AG84" s="71"/>
-      <c r="AH84" s="68"/>
-      <c r="AI84" s="72"/>
-      <c r="AJ84" s="73" t="str">
+      <c r="AE84" s="57"/>
+      <c r="AF84" s="57"/>
+      <c r="AG84" s="60"/>
+      <c r="AH84" s="57"/>
+      <c r="AI84" s="61"/>
+      <c r="AJ84" s="62" t="str">
         <f>IF(COUNTA(C84,D84,E84,F84,H84,I84,L84,M84,N84,P84,Q84,R84,S84,T84,U84,X84,Y84,Z84,AB84,AC84,AH84)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C84=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D84=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E84=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F84=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G84=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H84=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I84=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L84=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M84=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N84=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P84=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q84=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R84=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S84=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T84=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U84=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X84=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y84=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z84=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB84=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC84=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH84=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C84=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D84=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E84=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F84=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G84=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H84=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I84=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L84=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M84=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N84=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P84=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q84=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R84=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S84=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T84=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U84=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X84=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y84=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z84=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB84=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC84=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH84=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK84" s="63"/>
-    </row>
-    <row r="85" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A85" s="40"/>
-      <c r="B85" s="67">
-        <v>64</v>
-      </c>
-      <c r="C85" s="68"/>
-      <c r="D85" s="68"/>
-      <c r="E85" s="68"/>
-      <c r="F85" s="68"/>
-      <c r="G85" s="69" t="str">
+      <c r="AK84" s="52"/>
+    </row>
+    <row r="85" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A85" s="31"/>
+      <c r="B85" s="56">
+        <v>64</v>
+      </c>
+      <c r="C85" s="57"/>
+      <c r="D85" s="57"/>
+      <c r="E85" s="57"/>
+      <c r="F85" s="57"/>
+      <c r="G85" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F85,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H85" s="68"/>
-      <c r="I85" s="70"/>
-      <c r="J85" s="68"/>
-      <c r="K85" s="70"/>
-      <c r="L85" s="70"/>
-      <c r="M85" s="70"/>
-      <c r="N85" s="70"/>
-      <c r="O85" s="70"/>
-      <c r="P85" s="70"/>
-      <c r="Q85" s="70"/>
-      <c r="R85" s="70"/>
-      <c r="S85" s="70"/>
-      <c r="T85" s="70"/>
-      <c r="U85" s="70"/>
-      <c r="V85" s="70"/>
-      <c r="W85" s="70"/>
-      <c r="X85" s="70"/>
-      <c r="Y85" s="70"/>
-      <c r="Z85" s="70"/>
-      <c r="AA85" s="70"/>
-      <c r="AB85" s="68"/>
-      <c r="AC85" s="68"/>
-      <c r="AD85" s="69" t="str">
+      <c r="H85" s="57"/>
+      <c r="I85" s="59"/>
+      <c r="J85" s="57"/>
+      <c r="K85" s="59"/>
+      <c r="L85" s="59"/>
+      <c r="M85" s="59"/>
+      <c r="N85" s="59"/>
+      <c r="O85" s="59"/>
+      <c r="P85" s="59"/>
+      <c r="Q85" s="59"/>
+      <c r="R85" s="59"/>
+      <c r="S85" s="59"/>
+      <c r="T85" s="59"/>
+      <c r="U85" s="59"/>
+      <c r="V85" s="59"/>
+      <c r="W85" s="59"/>
+      <c r="X85" s="59"/>
+      <c r="Y85" s="59"/>
+      <c r="Z85" s="59"/>
+      <c r="AA85" s="59"/>
+      <c r="AB85" s="57"/>
+      <c r="AC85" s="57"/>
+      <c r="AD85" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB85,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE85" s="68"/>
-      <c r="AF85" s="68"/>
-      <c r="AG85" s="71"/>
-      <c r="AH85" s="68"/>
-      <c r="AI85" s="72"/>
-      <c r="AJ85" s="73" t="str">
+      <c r="AE85" s="57"/>
+      <c r="AF85" s="57"/>
+      <c r="AG85" s="60"/>
+      <c r="AH85" s="57"/>
+      <c r="AI85" s="61"/>
+      <c r="AJ85" s="62" t="str">
         <f>IF(COUNTA(C85,D85,E85,F85,H85,I85,L85,M85,N85,P85,Q85,R85,S85,T85,U85,X85,Y85,Z85,AB85,AC85,AH85)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C85=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D85=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E85=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F85=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G85=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H85=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I85=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L85=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M85=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N85=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P85=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q85=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R85=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S85=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T85=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U85=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X85=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y85=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z85=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB85=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC85=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH85=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C85=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D85=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E85=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F85=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G85=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H85=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I85=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L85=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M85=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N85=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P85=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q85=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R85=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S85=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T85=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U85=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X85=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y85=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z85=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB85=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC85=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH85=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK85" s="63"/>
-    </row>
-    <row r="86" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A86" s="40"/>
-      <c r="B86" s="67">
+      <c r="AK85" s="52"/>
+    </row>
+    <row r="86" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A86" s="31"/>
+      <c r="B86" s="56">
         <v>65</v>
       </c>
-      <c r="C86" s="68"/>
-      <c r="D86" s="68"/>
-      <c r="E86" s="68"/>
-      <c r="F86" s="68"/>
-      <c r="G86" s="69" t="str">
+      <c r="C86" s="57"/>
+      <c r="D86" s="57"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="57"/>
+      <c r="G86" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F86,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H86" s="68"/>
-      <c r="I86" s="70"/>
-      <c r="J86" s="68"/>
-      <c r="K86" s="70"/>
-      <c r="L86" s="70"/>
-      <c r="M86" s="70"/>
-      <c r="N86" s="70"/>
-      <c r="O86" s="70"/>
-      <c r="P86" s="70"/>
-      <c r="Q86" s="70"/>
-      <c r="R86" s="70"/>
-      <c r="S86" s="70"/>
-      <c r="T86" s="70"/>
-      <c r="U86" s="70"/>
-      <c r="V86" s="70"/>
-      <c r="W86" s="70"/>
-      <c r="X86" s="70"/>
-      <c r="Y86" s="70"/>
-      <c r="Z86" s="70"/>
-      <c r="AA86" s="70"/>
-      <c r="AB86" s="68"/>
-      <c r="AC86" s="68"/>
-      <c r="AD86" s="69" t="str">
+      <c r="H86" s="57"/>
+      <c r="I86" s="59"/>
+      <c r="J86" s="57"/>
+      <c r="K86" s="59"/>
+      <c r="L86" s="59"/>
+      <c r="M86" s="59"/>
+      <c r="N86" s="59"/>
+      <c r="O86" s="59"/>
+      <c r="P86" s="59"/>
+      <c r="Q86" s="59"/>
+      <c r="R86" s="59"/>
+      <c r="S86" s="59"/>
+      <c r="T86" s="59"/>
+      <c r="U86" s="59"/>
+      <c r="V86" s="59"/>
+      <c r="W86" s="59"/>
+      <c r="X86" s="59"/>
+      <c r="Y86" s="59"/>
+      <c r="Z86" s="59"/>
+      <c r="AA86" s="59"/>
+      <c r="AB86" s="57"/>
+      <c r="AC86" s="57"/>
+      <c r="AD86" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB86,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE86" s="68"/>
-      <c r="AF86" s="68"/>
-      <c r="AG86" s="71"/>
-      <c r="AH86" s="68"/>
-      <c r="AI86" s="72"/>
-      <c r="AJ86" s="73" t="str">
+      <c r="AE86" s="57"/>
+      <c r="AF86" s="57"/>
+      <c r="AG86" s="60"/>
+      <c r="AH86" s="57"/>
+      <c r="AI86" s="61"/>
+      <c r="AJ86" s="62" t="str">
         <f>IF(COUNTA(C86,D86,E86,F86,H86,I86,L86,M86,N86,P86,Q86,R86,S86,T86,U86,X86,Y86,Z86,AB86,AC86,AH86)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C86=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D86=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E86=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F86=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G86=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H86=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I86=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L86=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M86=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N86=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P86=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q86=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R86=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S86=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T86=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U86=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X86=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y86=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z86=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB86=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC86=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH86=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C86=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D86=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E86=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F86=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G86=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H86=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I86=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L86=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M86=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N86=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P86=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q86=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R86=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S86=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T86=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U86=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X86=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y86=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z86=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB86=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC86=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH86=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK86" s="63"/>
-    </row>
-    <row r="87" spans="1:37" s="46" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A87" s="40"/>
-      <c r="B87" s="67">
+      <c r="AK86" s="52"/>
+    </row>
+    <row r="87" spans="1:37" s="37" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A87" s="31"/>
+      <c r="B87" s="56">
         <v>66</v>
       </c>
-      <c r="C87" s="68"/>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="69" t="str">
+      <c r="C87" s="57"/>
+      <c r="D87" s="57"/>
+      <c r="E87" s="57"/>
+      <c r="F87" s="57"/>
+      <c r="G87" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(F87,Clase!$C$2:$C$292,Clase!$B$2:$B$292,""),"")</f>
         <v/>
       </c>
-      <c r="H87" s="68"/>
-      <c r="I87" s="70"/>
-      <c r="J87" s="68"/>
-      <c r="K87" s="70"/>
-      <c r="L87" s="70"/>
-      <c r="M87" s="70"/>
-      <c r="N87" s="70"/>
-      <c r="O87" s="70"/>
-      <c r="P87" s="70"/>
-      <c r="Q87" s="70"/>
-      <c r="R87" s="70"/>
-      <c r="S87" s="70"/>
-      <c r="T87" s="70"/>
-      <c r="U87" s="70"/>
-      <c r="V87" s="70"/>
-      <c r="W87" s="70"/>
-      <c r="X87" s="70"/>
-      <c r="Y87" s="70"/>
-      <c r="Z87" s="70"/>
-      <c r="AA87" s="70"/>
-      <c r="AB87" s="68"/>
-      <c r="AC87" s="68"/>
-      <c r="AD87" s="69" t="str">
+      <c r="H87" s="57"/>
+      <c r="I87" s="59"/>
+      <c r="J87" s="57"/>
+      <c r="K87" s="59"/>
+      <c r="L87" s="59"/>
+      <c r="M87" s="59"/>
+      <c r="N87" s="59"/>
+      <c r="O87" s="59"/>
+      <c r="P87" s="59"/>
+      <c r="Q87" s="59"/>
+      <c r="R87" s="59"/>
+      <c r="S87" s="59"/>
+      <c r="T87" s="59"/>
+      <c r="U87" s="59"/>
+      <c r="V87" s="59"/>
+      <c r="W87" s="59"/>
+      <c r="X87" s="59"/>
+      <c r="Y87" s="59"/>
+      <c r="Z87" s="59"/>
+      <c r="AA87" s="59"/>
+      <c r="AB87" s="57"/>
+      <c r="AC87" s="57"/>
+      <c r="AD87" s="58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(AB87,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
         <v/>
       </c>
-      <c r="AE87" s="68"/>
-      <c r="AF87" s="68"/>
-      <c r="AG87" s="71"/>
-      <c r="AH87" s="68"/>
-      <c r="AI87" s="72"/>
-      <c r="AJ87" s="73" t="str">
+      <c r="AE87" s="57"/>
+      <c r="AF87" s="57"/>
+      <c r="AG87" s="60"/>
+      <c r="AH87" s="57"/>
+      <c r="AI87" s="61"/>
+      <c r="AJ87" s="62" t="str">
         <f>IF(COUNTA(C87,D87,E87,F87,H87,I87,L87,M87,N87,P87,Q87,R87,S87,T87,U87,X87,Y87,Z87,AB87,AC87,AH87)=0,"",IF(LEN(_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C87=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D87=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E87=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F87=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G87=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H87=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I87=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L87=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M87=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N87=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P87=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q87=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R87=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S87=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T87=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U87=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X87=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y87=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z87=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB87=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC87=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH87=""),"Valor Unitario","")))&gt;0,"⚠️ Faltan: "&amp;_xlfn.TEXTJOIN(", ",TRUE,IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$B$10:$B$20,"")="SI",C87=""),"Orden de Inversión",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$C$10:$C$20,"")="SI",D87=""),"Elemento PEP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$D$10:$D$20,"")="SI",E87=""),"Pedido",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$E$10:$E$20,"")="SI",F87=""),"Descripción Activo SAP",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$F$10:$F$20,"")="SI",G87=""),"Clase",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$G$10:$G$20,"")="SI",H87=""),"Cantidad",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$H$10:$H$20,"")="SI",I87=""),"Nombre principal AF",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$I$10:$I$20,"")="SI",L87=""),"Fabricante",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$J$10:$J$20,"")="SI",M87=""),"Nit Proveedor",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$K$10:$K$20,"")="SI",N87=""),"Serie",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$L$10:$L$20,"")="SI",P87=""),"Criterio Clas. 1",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$M$10:$M$20,"")="SI",Q87=""),"Criterio Clas. 2",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$N$10:$N$20,"")="SI",R87=""),"Criterio Clas. 3",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$O$10:$O$20,"")="SI",S87=""),"Criterio Clas. 4",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$P$10:$P$20,"")="SI",T87=""),"Criterio Clas. 5",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$Q$10:$Q$20,"")="SI",U87=""),"Ubicación técnica",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$R$10:$R$20,"")="SI",X87=""),"Centro",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$S$10:$S$20,"")="SI",Y87=""),"Código País",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$T$10:$T$20,"")="SI",Z87=""),"Emplazamiento",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$U$10:$U$20,"")="SI",AB87=""),"Centro de Costo",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$V$10:$V$20,"")="SI",AC87=""),"Número de personal",""),IF(AND(_xlfn.XLOOKUP($C$14,_Requeridos!$A$10:$A$20,_Requeridos!$W$10:$W$20,"")="SI",AH87=""),"Valor Unitario","")),"✅ Completo"))</f>
         <v/>
       </c>
-      <c r="AK87" s="63"/>
-    </row>
-    <row r="88" spans="1:37" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="40"/>
-      <c r="B88" s="67">
+      <c r="AK87" s="52"/>
+    </row>
+    <row r="88" spans="1:37" s="37" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="31"/>
+      <c r="B88" s="56">
         <v>67</v>
       </c>
-      <c r="C88" s="68"/>
-      <c r="D88" s="68"/>
-      <c r="E88" s="68"/>
-      <c r="F88" s="68"/>
-      <c r="G88" s="69"/>
-      <c r="H88" s="68"/>
-      <c r="I88" s="70"/>
-      <c r="J88" s="68"/>
-      <c r="K88" s="70"/>
-      <c r="L88" s="70"/>
-      <c r="M88" s="70"/>
-      <c r="N88" s="70"/>
-      <c r="O88" s="70"/>
-      <c r="P88" s="70"/>
-      <c r="Q88" s="70"/>
-      <c r="R88" s="70"/>
-      <c r="S88" s="70"/>
-      <c r="T88" s="70"/>
-      <c r="U88" s="70"/>
-      <c r="V88" s="70"/>
-      <c r="W88" s="70"/>
-      <c r="X88" s="70"/>
-      <c r="Y88" s="70"/>
-      <c r="Z88" s="70"/>
-      <c r="AA88" s="70"/>
-      <c r="AB88" s="68"/>
-      <c r="AC88" s="68"/>
-      <c r="AD88" s="69"/>
-      <c r="AE88" s="68"/>
-      <c r="AF88" s="68"/>
-      <c r="AG88" s="71"/>
-      <c r="AH88" s="68"/>
-      <c r="AI88" s="72"/>
-      <c r="AJ88" s="73"/>
-      <c r="AK88" s="63"/>
-    </row>
-    <row r="89" spans="1:37" s="46" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="40"/>
-      <c r="B89" s="67">
+      <c r="C88" s="57"/>
+      <c r="D88" s="57"/>
+      <c r="E88" s="57"/>
+      <c r="F88" s="57"/>
+      <c r="G88" s="58"/>
+      <c r="H88" s="57"/>
+      <c r="I88" s="59"/>
+      <c r="J88" s="57"/>
+      <c r="K88" s="59"/>
+      <c r="L88" s="59"/>
+      <c r="M88" s="59"/>
+      <c r="N88" s="59"/>
+      <c r="O88" s="59"/>
+      <c r="P88" s="59"/>
+      <c r="Q88" s="59"/>
+      <c r="R88" s="59"/>
+      <c r="S88" s="59"/>
+      <c r="T88" s="59"/>
+      <c r="U88" s="59"/>
+      <c r="V88" s="59"/>
+      <c r="W88" s="59"/>
+      <c r="X88" s="59"/>
+      <c r="Y88" s="59"/>
+      <c r="Z88" s="59"/>
+      <c r="AA88" s="59"/>
+      <c r="AB88" s="57"/>
+      <c r="AC88" s="57"/>
+      <c r="AD88" s="58"/>
+      <c r="AE88" s="57"/>
+      <c r="AF88" s="57"/>
+      <c r="AG88" s="60"/>
+      <c r="AH88" s="57"/>
+      <c r="AI88" s="61"/>
+      <c r="AJ88" s="62"/>
+      <c r="AK88" s="52"/>
+    </row>
+    <row r="89" spans="1:37" s="37" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="31"/>
+      <c r="B89" s="56">
         <v>68</v>
       </c>
-      <c r="C89" s="68"/>
-      <c r="D89" s="68"/>
-      <c r="E89" s="68"/>
-      <c r="F89" s="68"/>
-      <c r="G89" s="69"/>
-      <c r="H89" s="68"/>
-      <c r="I89" s="70"/>
-      <c r="J89" s="68"/>
-      <c r="K89" s="70"/>
-      <c r="L89" s="70"/>
-      <c r="M89" s="70"/>
-      <c r="N89" s="70"/>
-      <c r="O89" s="70"/>
-      <c r="P89" s="70"/>
-      <c r="Q89" s="70"/>
-      <c r="R89" s="70"/>
-      <c r="S89" s="70"/>
-      <c r="T89" s="70"/>
-      <c r="U89" s="70"/>
-      <c r="V89" s="70"/>
-      <c r="W89" s="70"/>
-      <c r="X89" s="70"/>
-      <c r="Y89" s="70"/>
-      <c r="Z89" s="70"/>
-      <c r="AA89" s="70"/>
-      <c r="AB89" s="68"/>
-      <c r="AC89" s="68"/>
-      <c r="AD89" s="69"/>
-      <c r="AE89" s="68"/>
-      <c r="AF89" s="68"/>
-      <c r="AG89" s="71"/>
-      <c r="AH89" s="68"/>
-      <c r="AI89" s="72"/>
-      <c r="AJ89" s="73"/>
-      <c r="AK89" s="63"/>
+      <c r="C89" s="57"/>
+      <c r="D89" s="57"/>
+      <c r="E89" s="57"/>
+      <c r="F89" s="57"/>
+      <c r="G89" s="58"/>
+      <c r="H89" s="57"/>
+      <c r="I89" s="59"/>
+      <c r="J89" s="57"/>
+      <c r="K89" s="59"/>
+      <c r="L89" s="59"/>
+      <c r="M89" s="59"/>
+      <c r="N89" s="59"/>
+      <c r="O89" s="59"/>
+      <c r="P89" s="59"/>
+      <c r="Q89" s="59"/>
+      <c r="R89" s="59"/>
+      <c r="S89" s="59"/>
+      <c r="T89" s="59"/>
+      <c r="U89" s="59"/>
+      <c r="V89" s="59"/>
+      <c r="W89" s="59"/>
+      <c r="X89" s="59"/>
+      <c r="Y89" s="59"/>
+      <c r="Z89" s="59"/>
+      <c r="AA89" s="59"/>
+      <c r="AB89" s="57"/>
+      <c r="AC89" s="57"/>
+      <c r="AD89" s="58"/>
+      <c r="AE89" s="57"/>
+      <c r="AF89" s="57"/>
+      <c r="AG89" s="60"/>
+      <c r="AH89" s="57"/>
+      <c r="AI89" s="61"/>
+      <c r="AJ89" s="62"/>
+      <c r="AK89" s="52"/>
     </row>
     <row r="90" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A90" s="37"/>
-      <c r="B90" s="37"/>
-      <c r="C90" s="37"/>
-      <c r="D90" s="37"/>
-      <c r="E90" s="37"/>
-      <c r="F90" s="37"/>
-      <c r="G90" s="37"/>
-      <c r="H90" s="37"/>
-      <c r="I90" s="37"/>
-      <c r="J90" s="37"/>
-      <c r="K90" s="37"/>
-      <c r="L90" s="37"/>
-      <c r="M90" s="37"/>
-      <c r="N90" s="37"/>
-      <c r="O90" s="37"/>
-      <c r="P90" s="37"/>
-      <c r="Q90" s="37"/>
-      <c r="R90" s="37"/>
-      <c r="S90" s="37"/>
-      <c r="T90" s="37"/>
-      <c r="U90" s="37"/>
-      <c r="V90" s="37"/>
-      <c r="W90" s="37"/>
-      <c r="X90" s="37"/>
-      <c r="Y90" s="37"/>
-      <c r="Z90" s="37"/>
-      <c r="AA90" s="37"/>
-      <c r="AB90" s="37"/>
-      <c r="AC90" s="37"/>
-      <c r="AD90" s="37"/>
-      <c r="AE90" s="37"/>
-      <c r="AF90" s="37"/>
-      <c r="AG90" s="37"/>
-      <c r="AH90" s="37"/>
-      <c r="AI90" s="37"/>
+      <c r="A90" s="28"/>
+      <c r="B90" s="28"/>
+      <c r="C90" s="28"/>
+      <c r="D90" s="28"/>
+      <c r="E90" s="28"/>
+      <c r="F90" s="28"/>
+      <c r="G90" s="28"/>
+      <c r="H90" s="28"/>
+      <c r="I90" s="28"/>
+      <c r="J90" s="28"/>
+      <c r="K90" s="28"/>
+      <c r="L90" s="28"/>
+      <c r="M90" s="28"/>
+      <c r="N90" s="28"/>
+      <c r="O90" s="28"/>
+      <c r="P90" s="28"/>
+      <c r="Q90" s="28"/>
+      <c r="R90" s="28"/>
+      <c r="S90" s="28"/>
+      <c r="T90" s="28"/>
+      <c r="U90" s="28"/>
+      <c r="V90" s="28"/>
+      <c r="W90" s="28"/>
+      <c r="X90" s="28"/>
+      <c r="Y90" s="28"/>
+      <c r="Z90" s="28"/>
+      <c r="AA90" s="28"/>
+      <c r="AB90" s="28"/>
+      <c r="AC90" s="28"/>
+      <c r="AD90" s="28"/>
+      <c r="AE90" s="28"/>
+      <c r="AF90" s="28"/>
+      <c r="AG90" s="28"/>
+      <c r="AH90" s="28"/>
+      <c r="AI90" s="28"/>
     </row>
     <row r="91" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A91" s="37"/>
-      <c r="B91" s="37"/>
-      <c r="C91" s="37"/>
-      <c r="D91" s="37"/>
-      <c r="E91" s="37"/>
-      <c r="F91" s="37"/>
-      <c r="G91" s="37"/>
-      <c r="H91" s="37"/>
-      <c r="I91" s="37"/>
-      <c r="J91" s="37"/>
-      <c r="K91" s="37"/>
-      <c r="L91" s="37"/>
-      <c r="M91" s="37"/>
-      <c r="N91" s="37"/>
-      <c r="O91" s="37"/>
-      <c r="P91" s="37"/>
-      <c r="Q91" s="37"/>
-      <c r="R91" s="37"/>
-      <c r="S91" s="37"/>
-      <c r="T91" s="37"/>
-      <c r="U91" s="37"/>
-      <c r="V91" s="37"/>
-      <c r="W91" s="37"/>
-      <c r="X91" s="37"/>
-      <c r="Y91" s="37"/>
-      <c r="Z91" s="37"/>
-      <c r="AA91" s="37"/>
-      <c r="AB91" s="37"/>
-      <c r="AC91" s="37"/>
-      <c r="AD91" s="37"/>
-      <c r="AE91" s="37"/>
-      <c r="AF91" s="37"/>
-      <c r="AG91" s="37"/>
-      <c r="AH91" s="37"/>
-      <c r="AI91" s="37"/>
+      <c r="A91" s="28"/>
+      <c r="B91" s="28"/>
+      <c r="C91" s="28"/>
+      <c r="D91" s="28"/>
+      <c r="E91" s="28"/>
+      <c r="F91" s="28"/>
+      <c r="G91" s="28"/>
+      <c r="H91" s="28"/>
+      <c r="I91" s="28"/>
+      <c r="J91" s="28"/>
+      <c r="K91" s="28"/>
+      <c r="L91" s="28"/>
+      <c r="M91" s="28"/>
+      <c r="N91" s="28"/>
+      <c r="O91" s="28"/>
+      <c r="P91" s="28"/>
+      <c r="Q91" s="28"/>
+      <c r="R91" s="28"/>
+      <c r="S91" s="28"/>
+      <c r="T91" s="28"/>
+      <c r="U91" s="28"/>
+      <c r="V91" s="28"/>
+      <c r="W91" s="28"/>
+      <c r="X91" s="28"/>
+      <c r="Y91" s="28"/>
+      <c r="Z91" s="28"/>
+      <c r="AA91" s="28"/>
+      <c r="AB91" s="28"/>
+      <c r="AC91" s="28"/>
+      <c r="AD91" s="28"/>
+      <c r="AE91" s="28"/>
+      <c r="AF91" s="28"/>
+      <c r="AG91" s="28"/>
+      <c r="AH91" s="28"/>
+      <c r="AI91" s="28"/>
     </row>
     <row r="92" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A92" s="37"/>
-      <c r="B92" s="37"/>
-      <c r="C92" s="37"/>
-      <c r="D92" s="37"/>
-      <c r="E92" s="37"/>
-      <c r="F92" s="37"/>
-      <c r="G92" s="37"/>
-      <c r="H92" s="37"/>
-      <c r="I92" s="37"/>
-      <c r="J92" s="37"/>
-      <c r="K92" s="37"/>
-      <c r="L92" s="37"/>
-      <c r="M92" s="37"/>
-      <c r="N92" s="37"/>
-      <c r="O92" s="37"/>
-      <c r="P92" s="37"/>
-      <c r="Q92" s="37"/>
-      <c r="R92" s="37"/>
-      <c r="S92" s="37"/>
-      <c r="T92" s="37"/>
-      <c r="U92" s="37"/>
-      <c r="V92" s="37"/>
-      <c r="W92" s="37"/>
-      <c r="X92" s="37"/>
-      <c r="Y92" s="37"/>
-      <c r="Z92" s="37"/>
-      <c r="AA92" s="37"/>
-      <c r="AB92" s="37"/>
-      <c r="AC92" s="37"/>
-      <c r="AD92" s="37"/>
-      <c r="AE92" s="37"/>
-      <c r="AF92" s="37"/>
-      <c r="AG92" s="37"/>
-      <c r="AH92" s="37"/>
-      <c r="AI92" s="37"/>
+      <c r="A92" s="28"/>
+      <c r="B92" s="28"/>
+      <c r="C92" s="28"/>
+      <c r="D92" s="28"/>
+      <c r="E92" s="28"/>
+      <c r="F92" s="28"/>
+      <c r="G92" s="28"/>
+      <c r="H92" s="28"/>
+      <c r="I92" s="28"/>
+      <c r="J92" s="28"/>
+      <c r="K92" s="28"/>
+      <c r="L92" s="28"/>
+      <c r="M92" s="28"/>
+      <c r="N92" s="28"/>
+      <c r="O92" s="28"/>
+      <c r="P92" s="28"/>
+      <c r="Q92" s="28"/>
+      <c r="R92" s="28"/>
+      <c r="S92" s="28"/>
+      <c r="T92" s="28"/>
+      <c r="U92" s="28"/>
+      <c r="V92" s="28"/>
+      <c r="W92" s="28"/>
+      <c r="X92" s="28"/>
+      <c r="Y92" s="28"/>
+      <c r="Z92" s="28"/>
+      <c r="AA92" s="28"/>
+      <c r="AB92" s="28"/>
+      <c r="AC92" s="28"/>
+      <c r="AD92" s="28"/>
+      <c r="AE92" s="28"/>
+      <c r="AF92" s="28"/>
+      <c r="AG92" s="28"/>
+      <c r="AH92" s="28"/>
+      <c r="AI92" s="28"/>
     </row>
     <row r="93" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A93" s="37"/>
-      <c r="B93" s="37"/>
-      <c r="C93" s="37"/>
-      <c r="D93" s="37"/>
-      <c r="E93" s="37"/>
-      <c r="F93" s="37"/>
-      <c r="G93" s="37"/>
-      <c r="H93" s="37"/>
-      <c r="I93" s="37"/>
-      <c r="J93" s="37"/>
-      <c r="K93" s="37"/>
-      <c r="L93" s="37"/>
-      <c r="M93" s="37"/>
-      <c r="N93" s="37"/>
-      <c r="O93" s="37"/>
-      <c r="P93" s="37"/>
-      <c r="Q93" s="37"/>
-      <c r="R93" s="37"/>
-      <c r="S93" s="37"/>
-      <c r="T93" s="37"/>
-      <c r="U93" s="37"/>
-      <c r="V93" s="37"/>
-      <c r="W93" s="37"/>
-      <c r="X93" s="37"/>
-      <c r="Y93" s="37"/>
-      <c r="Z93" s="37"/>
-      <c r="AA93" s="37"/>
-      <c r="AB93" s="37"/>
-      <c r="AC93" s="37"/>
-      <c r="AD93" s="37"/>
-      <c r="AE93" s="37"/>
-      <c r="AF93" s="37"/>
-      <c r="AG93" s="37"/>
-      <c r="AH93" s="37"/>
-      <c r="AI93" s="37"/>
-    </row>
-    <row r="97" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="98" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="99" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="100" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="101" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="102" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="103" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="104" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="105" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="106" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="107" s="38" customFormat="1" x14ac:dyDescent="0.2"/>
+      <c r="A93" s="28"/>
+      <c r="B93" s="28"/>
+      <c r="C93" s="28"/>
+      <c r="D93" s="28"/>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="28"/>
+      <c r="H93" s="28"/>
+      <c r="I93" s="28"/>
+      <c r="J93" s="28"/>
+      <c r="K93" s="28"/>
+      <c r="L93" s="28"/>
+      <c r="M93" s="28"/>
+      <c r="N93" s="28"/>
+      <c r="O93" s="28"/>
+      <c r="P93" s="28"/>
+      <c r="Q93" s="28"/>
+      <c r="R93" s="28"/>
+      <c r="S93" s="28"/>
+      <c r="T93" s="28"/>
+      <c r="U93" s="28"/>
+      <c r="V93" s="28"/>
+      <c r="W93" s="28"/>
+      <c r="X93" s="28"/>
+      <c r="Y93" s="28"/>
+      <c r="Z93" s="28"/>
+      <c r="AA93" s="28"/>
+      <c r="AB93" s="28"/>
+      <c r="AC93" s="28"/>
+      <c r="AD93" s="28"/>
+      <c r="AE93" s="28"/>
+      <c r="AF93" s="28"/>
+      <c r="AG93" s="28"/>
+      <c r="AH93" s="28"/>
+      <c r="AI93" s="28"/>
+    </row>
+    <row r="97" s="29" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="98" s="29" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="99" s="29" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="100" s="29" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="101" s="29" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="102" s="29" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="103" s="29" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="104" s="29" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="105" s="29" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="106" s="29" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="107" s="29" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="3">
@@ -49997,10 +49778,10 @@
     <mergeCell ref="B11:AJ12"/>
   </mergeCells>
   <conditionalFormatting sqref="AJ22:AJ89">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Faltan">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Faltan">
       <formula>NOT(ISERROR(SEARCH("Faltan",AJ22)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Completo">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Completo">
       <formula>NOT(ISERROR(SEARCH("Completo",AJ22)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/resources/Formato_Dinamico_.xlsx
+++ b/resources/Formato_Dinamico_.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1017209574\Desktop\Digital\activos-propios-py\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C05D545-BAE6-4207-9E60-7E8AB25627B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A14991-CB10-4DBE-BC0E-E8834908FBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{CA7242B3-F58B-4D52-905C-F122405A1A29}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="8" xr2:uid="{CA7242B3-F58B-4D52-905C-F122405A1A29}"/>
   </bookViews>
   <sheets>
     <sheet name="Sociedades" sheetId="7" r:id="rId1"/>
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7718" uniqueCount="1518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7718" uniqueCount="1519">
   <si>
     <t xml:space="preserve">Sociedad </t>
   </si>
@@ -4787,6 +4787,9 @@
   </si>
   <si>
     <t>Controlador campo - Prueba 3</t>
+  </si>
+  <si>
+    <t>Controlador campo - Prueba 100</t>
   </si>
 </sst>
 </file>
@@ -5521,18 +5524,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -5564,6 +5555,18 @@
     <xf numFmtId="0" fontId="35" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6430,7 +6433,7 @@
       </c>
       <c r="E2" t="str">
         <f>Formato!I22</f>
-        <v>Controlador campo - Prueba 3</v>
+        <v>Controlador campo - Prueba 100</v>
       </c>
       <c r="F2" t="str">
         <f>Formato!J22</f>
@@ -45813,8 +45816,8 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.35">
       <c r="F6" s="21"/>
@@ -45825,22 +45828,22 @@
       <c r="G7" s="21"/>
     </row>
     <row r="8" spans="2:7" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="83" t="s">
         <v>1470</v>
       </c>
-      <c r="C8" s="76"/>
+      <c r="C8" s="84"/>
     </row>
     <row r="11" spans="2:7" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="77" t="s">
+      <c r="B11" s="85" t="s">
         <v>1475</v>
       </c>
-      <c r="C11" s="77"/>
+      <c r="C11" s="85"/>
     </row>
     <row r="12" spans="2:7" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="B12" s="77" t="s">
+      <c r="B12" s="85" t="s">
         <v>1474</v>
       </c>
-      <c r="C12" s="77"/>
+      <c r="C12" s="85"/>
     </row>
     <row r="13" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -45919,10 +45922,10 @@
     </row>
     <row r="26" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="27" spans="2:3" ht="21.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="75" t="s">
+      <c r="B27" s="83" t="s">
         <v>1507</v>
       </c>
-      <c r="C27" s="76"/>
+      <c r="C27" s="84"/>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B28" s="38" t="s">
@@ -46114,81 +46117,81 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="30"/>
-      <c r="B11" s="80" t="s">
+      <c r="B11" s="76" t="s">
         <v>1328</v>
       </c>
-      <c r="C11" s="81"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="81"/>
-      <c r="K11" s="81"/>
-      <c r="L11" s="81"/>
-      <c r="M11" s="81"/>
-      <c r="N11" s="81"/>
-      <c r="O11" s="81"/>
-      <c r="P11" s="81"/>
-      <c r="Q11" s="81"/>
-      <c r="R11" s="81"/>
-      <c r="S11" s="81"/>
-      <c r="T11" s="81"/>
-      <c r="U11" s="81"/>
-      <c r="V11" s="81"/>
-      <c r="W11" s="81"/>
-      <c r="X11" s="81"/>
-      <c r="Y11" s="81"/>
-      <c r="Z11" s="81"/>
-      <c r="AA11" s="81"/>
-      <c r="AB11" s="81"/>
-      <c r="AC11" s="81"/>
-      <c r="AD11" s="81"/>
-      <c r="AE11" s="81"/>
-      <c r="AF11" s="81"/>
-      <c r="AG11" s="81"/>
-      <c r="AH11" s="81"/>
-      <c r="AI11" s="81"/>
-      <c r="AJ11" s="82"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="77"/>
+      <c r="M11" s="77"/>
+      <c r="N11" s="77"/>
+      <c r="O11" s="77"/>
+      <c r="P11" s="77"/>
+      <c r="Q11" s="77"/>
+      <c r="R11" s="77"/>
+      <c r="S11" s="77"/>
+      <c r="T11" s="77"/>
+      <c r="U11" s="77"/>
+      <c r="V11" s="77"/>
+      <c r="W11" s="77"/>
+      <c r="X11" s="77"/>
+      <c r="Y11" s="77"/>
+      <c r="Z11" s="77"/>
+      <c r="AA11" s="77"/>
+      <c r="AB11" s="77"/>
+      <c r="AC11" s="77"/>
+      <c r="AD11" s="77"/>
+      <c r="AE11" s="77"/>
+      <c r="AF11" s="77"/>
+      <c r="AG11" s="77"/>
+      <c r="AH11" s="77"/>
+      <c r="AI11" s="77"/>
+      <c r="AJ11" s="78"/>
     </row>
     <row r="12" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="31"/>
-      <c r="B12" s="83"/>
-      <c r="C12" s="84"/>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="84"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="84"/>
-      <c r="J12" s="84"/>
-      <c r="K12" s="84"/>
-      <c r="L12" s="84"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="84"/>
-      <c r="O12" s="84"/>
-      <c r="P12" s="84"/>
-      <c r="Q12" s="84"/>
-      <c r="R12" s="84"/>
-      <c r="S12" s="84"/>
-      <c r="T12" s="84"/>
-      <c r="U12" s="84"/>
-      <c r="V12" s="84"/>
-      <c r="W12" s="84"/>
-      <c r="X12" s="84"/>
-      <c r="Y12" s="84"/>
-      <c r="Z12" s="84"/>
-      <c r="AA12" s="84"/>
-      <c r="AB12" s="84"/>
-      <c r="AC12" s="84"/>
-      <c r="AD12" s="84"/>
-      <c r="AE12" s="84"/>
-      <c r="AF12" s="84"/>
-      <c r="AG12" s="84"/>
-      <c r="AH12" s="84"/>
-      <c r="AI12" s="84"/>
-      <c r="AJ12" s="85"/>
+      <c r="B12" s="79"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="80"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="80"/>
+      <c r="L12" s="80"/>
+      <c r="M12" s="80"/>
+      <c r="N12" s="80"/>
+      <c r="O12" s="80"/>
+      <c r="P12" s="80"/>
+      <c r="Q12" s="80"/>
+      <c r="R12" s="80"/>
+      <c r="S12" s="80"/>
+      <c r="T12" s="80"/>
+      <c r="U12" s="80"/>
+      <c r="V12" s="80"/>
+      <c r="W12" s="80"/>
+      <c r="X12" s="80"/>
+      <c r="Y12" s="80"/>
+      <c r="Z12" s="80"/>
+      <c r="AA12" s="80"/>
+      <c r="AB12" s="80"/>
+      <c r="AC12" s="80"/>
+      <c r="AD12" s="80"/>
+      <c r="AE12" s="80"/>
+      <c r="AF12" s="80"/>
+      <c r="AG12" s="80"/>
+      <c r="AH12" s="80"/>
+      <c r="AI12" s="80"/>
+      <c r="AJ12" s="81"/>
     </row>
     <row r="13" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="64"/>
@@ -46236,9 +46239,9 @@
       <c r="C14" s="63" t="s">
         <v>162</v>
       </c>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
       <c r="G14" s="45"/>
       <c r="H14" s="49"/>
       <c r="I14" s="49"/>
@@ -46276,9 +46279,9 @@
         <v>1330</v>
       </c>
       <c r="C15" s="45"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
       <c r="G15" s="45"/>
       <c r="H15" s="49"/>
       <c r="I15" s="49"/>
@@ -46316,9 +46319,9 @@
         <v>1331</v>
       </c>
       <c r="C16" s="46"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
       <c r="G16" s="50"/>
       <c r="H16" s="49"/>
       <c r="I16" s="49"/>
@@ -46356,9 +46359,9 @@
         <v>1332</v>
       </c>
       <c r="C17" s="48"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
       <c r="G17" s="50"/>
       <c r="H17" s="49"/>
       <c r="I17" s="49"/>
@@ -46396,9 +46399,9 @@
         <v>1333</v>
       </c>
       <c r="C18" s="48"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
       <c r="G18" s="50"/>
       <c r="H18" s="49"/>
       <c r="I18" s="49"/>
@@ -46436,9 +46439,9 @@
         <v>1334</v>
       </c>
       <c r="C19" s="48"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
       <c r="G19" s="50"/>
       <c r="H19" s="49"/>
       <c r="I19" s="49"/>
@@ -46503,11 +46506,11 @@
       <c r="AD20" s="28"/>
       <c r="AE20" s="28"/>
       <c r="AF20" s="28"/>
-      <c r="AG20" s="79" t="s">
+      <c r="AG20" s="75" t="s">
         <v>1335</v>
       </c>
-      <c r="AH20" s="79"/>
-      <c r="AI20" s="79"/>
+      <c r="AH20" s="75"/>
+      <c r="AI20" s="75"/>
     </row>
     <row r="21" spans="1:37" s="36" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="34"/>
@@ -46639,7 +46642,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="69" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="J22" s="69" t="s">
         <v>1517</v>

--- a/resources/Formato_Dinamico_.xlsx
+++ b/resources/Formato_Dinamico_.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1017209574\Desktop\Digital\activos-propios-py\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A14991-CB10-4DBE-BC0E-E8834908FBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BC101D-0F83-4FF7-BF36-7E5EA2A9DFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="8" xr2:uid="{CA7242B3-F58B-4D52-905C-F122405A1A29}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{CA7242B3-F58B-4D52-905C-F122405A1A29}"/>
   </bookViews>
   <sheets>
     <sheet name="Sociedades" sheetId="7" r:id="rId1"/>
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7718" uniqueCount="1519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7717" uniqueCount="1518">
   <si>
     <t xml:space="preserve">Sociedad </t>
   </si>
@@ -4778,9 +4778,6 @@
   </si>
   <si>
     <t>SIEMENS</t>
-  </si>
-  <si>
-    <t>ISCA2M03ME</t>
   </si>
   <si>
     <t>05649</t>
@@ -6468,13 +6465,13 @@
       <c r="S2" s="73">
         <v>3208</v>
       </c>
-      <c r="T2" t="str">
+      <c r="T2">
         <f>Formato!AB22</f>
-        <v>ISCA2M03ME</v>
-      </c>
-      <c r="U2" t="str">
+        <v>10004</v>
+      </c>
+      <c r="U2">
         <f>Formato!AD22</f>
-        <v/>
+        <v>10004</v>
       </c>
       <c r="W2" t="str">
         <f>Formato!X22</f>
@@ -6485,7 +6482,7 @@
         <v/>
       </c>
       <c r="Z2" s="72" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="AB2">
         <f>Formato!W22</f>
@@ -46642,13 +46639,13 @@
         <v>1</v>
       </c>
       <c r="I22" s="69" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="J22" s="69" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="K22" s="69" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="L22" s="69" t="s">
         <v>1514</v>
@@ -46682,13 +46679,13 @@
         <v>5603</v>
       </c>
       <c r="AA22" s="59"/>
-      <c r="AB22" s="57" t="s">
-        <v>1515</v>
+      <c r="AB22" s="57">
+        <v>10004</v>
       </c>
       <c r="AC22" s="57"/>
-      <c r="AD22" s="58" t="str">
+      <c r="AD22" s="58">
         <f>IFERROR(_xlfn.XLOOKUP(AB22,Ceco!$B$2:$B$901,Ceco!$C$2:$C$901,""),"")</f>
-        <v/>
+        <v>10004</v>
       </c>
       <c r="AE22" s="57"/>
       <c r="AF22" s="57"/>
